--- a/data/tip/Tip.xlsx
+++ b/data/tip/Tip.xlsx
@@ -1020,7 +1020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C325"/>
+  <dimension ref="A1:C336"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="8" customWidth="1" style="2" min="3" max="3"/>
@@ -4359,146 +4359,279 @@
         <v>1</v>
       </c>
     </row>
+    <row r="313"/>
     <row r="314">
-      <c r="A314" t="inlineStr">
+      <c r="A314" s="0" t="inlineStr">
         <is>
           <t>//equip_error base=28000 width=1000</t>
         </is>
       </c>
     </row>
     <row r="315">
-      <c r="A315" t="inlineStr">
+      <c r="A315" s="0" t="inlineStr">
         <is>
           <t>EquipItemNotFound</t>
         </is>
       </c>
-      <c r="B315" t="inlineStr">
+      <c r="B315" s="0" t="inlineStr">
         <is>
           <t>物品不存在</t>
         </is>
       </c>
     </row>
     <row r="316">
-      <c r="A316" t="inlineStr">
+      <c r="A316" s="0" t="inlineStr">
         <is>
           <t>EquipNotEquipment</t>
         </is>
       </c>
-      <c r="B316" t="inlineStr">
+      <c r="B316" s="0" t="inlineStr">
         <is>
           <t>该物品不是装备</t>
         </is>
       </c>
     </row>
     <row r="317">
-      <c r="A317" t="inlineStr">
+      <c r="A317" s="0" t="inlineStr">
         <is>
           <t>EquipLevelNotEnough</t>
         </is>
       </c>
-      <c r="B317" t="inlineStr">
+      <c r="B317" s="0" t="inlineStr">
         <is>
           <t>等级不足,无法装备</t>
         </is>
       </c>
     </row>
     <row r="318">
-      <c r="A318" t="inlineStr">
+      <c r="A318" s="0" t="inlineStr">
         <is>
           <t>EquipClassMismatch</t>
         </is>
       </c>
-      <c r="B318" t="inlineStr">
+      <c r="B318" s="0" t="inlineStr">
         <is>
           <t>职业不符,无法装备</t>
         </is>
       </c>
     </row>
     <row r="319">
-      <c r="A319" t="inlineStr">
+      <c r="A319" s="0" t="inlineStr">
         <is>
           <t>EquipNoSlot</t>
         </is>
       </c>
-      <c r="B319" t="inlineStr">
+      <c r="B319" s="0" t="inlineStr">
         <is>
           <t>没有可用的装备栏位</t>
         </is>
       </c>
     </row>
     <row r="320">
-      <c r="A320" t="inlineStr">
+      <c r="A320" s="0" t="inlineStr">
         <is>
           <t>EquipNotEquipped</t>
         </is>
       </c>
-      <c r="B320" t="inlineStr">
+      <c r="B320" s="0" t="inlineStr">
         <is>
           <t>该装备未穿戴</t>
         </is>
       </c>
     </row>
     <row r="321">
-      <c r="A321" t="inlineStr">
+      <c r="A321" s="0" t="inlineStr">
         <is>
           <t>EquipBagFull</t>
         </is>
       </c>
-      <c r="B321" t="inlineStr">
+      <c r="B321" s="0" t="inlineStr">
         <is>
           <t>背包已满,无法卸下</t>
         </is>
       </c>
     </row>
     <row r="322">
-      <c r="A322" t="inlineStr">
+      <c r="A322" s="0" t="inlineStr">
         <is>
           <t>EquipInBattle</t>
         </is>
       </c>
-      <c r="B322" t="inlineStr">
+      <c r="B322" s="0" t="inlineStr">
         <is>
           <t>战斗中无法更换装备</t>
         </is>
       </c>
     </row>
     <row r="323">
-      <c r="A323" t="inlineStr">
+      <c r="A323" s="0" t="inlineStr">
         <is>
           <t>EquipFrozen</t>
         </is>
       </c>
-      <c r="B323" t="inlineStr">
+      <c r="B323" s="0" t="inlineStr">
         <is>
           <t>当前状态无法更换装备</t>
         </is>
       </c>
     </row>
     <row r="324">
-      <c r="A324" t="inlineStr">
+      <c r="A324" s="0" t="inlineStr">
         <is>
           <t>EquipGrantInvalid</t>
         </is>
       </c>
-      <c r="B324" t="inlineStr">
+      <c r="B324" s="0" t="inlineStr">
         <is>
           <t>发放参数无效</t>
         </is>
       </c>
     </row>
     <row r="325">
-      <c r="A325" t="inlineStr">
+      <c r="A325" s="0" t="inlineStr">
         <is>
           <t>EquipInternalError</t>
         </is>
       </c>
-      <c r="B325" t="inlineStr">
+      <c r="B325" s="0" t="inlineStr">
         <is>
           <t>装备操作失败,请稍后再试</t>
         </is>
       </c>
-      <c r="C325" t="n">
+      <c r="C325" s="0" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>EquipEnhanceUnavailable</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>该装备无法强化</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>EquipEnhanceMaxLevel</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>已强化到最高等级</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>EquipEnhanceMaterialNotEnough</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>强化材料不足</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>EquipEnhanceGoldNotEnough</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>金币不足,无法强化</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>EquipGemNotGem</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>该物品不是宝石</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>EquipGemNotOwned</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>背包里没有这颗宝石</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>EquipGemSocketInvalid</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>该装备没有这个宝石孔</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>EquipGemSocketOccupied</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>该孔位已镶有宝石,请先取下</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>EquipGemSocketEmpty</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>该孔位没有宝石</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>EquipGemTypeMismatch</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>宝石类型与孔位不符</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>EquipGemBagFull</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>背包已满,无法取下宝石</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/data/tip/Tip.xlsx
+++ b/data/tip/Tip.xlsx
@@ -1020,7 +1020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C336"/>
+  <dimension ref="A1:C353"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="8" customWidth="1" style="2" min="3" max="3"/>
@@ -4503,135 +4503,325 @@
       </c>
     </row>
     <row r="326">
-      <c r="A326" t="inlineStr">
+      <c r="A326" s="0" t="inlineStr">
         <is>
           <t>EquipEnhanceUnavailable</t>
         </is>
       </c>
-      <c r="B326" t="inlineStr">
+      <c r="B326" s="0" t="inlineStr">
         <is>
           <t>该装备无法强化</t>
         </is>
       </c>
     </row>
     <row r="327">
-      <c r="A327" t="inlineStr">
+      <c r="A327" s="0" t="inlineStr">
         <is>
           <t>EquipEnhanceMaxLevel</t>
         </is>
       </c>
-      <c r="B327" t="inlineStr">
+      <c r="B327" s="0" t="inlineStr">
         <is>
           <t>已强化到最高等级</t>
         </is>
       </c>
     </row>
     <row r="328">
-      <c r="A328" t="inlineStr">
+      <c r="A328" s="0" t="inlineStr">
         <is>
           <t>EquipEnhanceMaterialNotEnough</t>
         </is>
       </c>
-      <c r="B328" t="inlineStr">
+      <c r="B328" s="0" t="inlineStr">
         <is>
           <t>强化材料不足</t>
         </is>
       </c>
     </row>
     <row r="329">
-      <c r="A329" t="inlineStr">
+      <c r="A329" s="0" t="inlineStr">
         <is>
           <t>EquipEnhanceGoldNotEnough</t>
         </is>
       </c>
-      <c r="B329" t="inlineStr">
+      <c r="B329" s="0" t="inlineStr">
         <is>
           <t>金币不足,无法强化</t>
         </is>
       </c>
     </row>
     <row r="330">
-      <c r="A330" t="inlineStr">
+      <c r="A330" s="0" t="inlineStr">
         <is>
           <t>EquipGemNotGem</t>
         </is>
       </c>
-      <c r="B330" t="inlineStr">
+      <c r="B330" s="0" t="inlineStr">
         <is>
           <t>该物品不是宝石</t>
         </is>
       </c>
     </row>
     <row r="331">
-      <c r="A331" t="inlineStr">
+      <c r="A331" s="0" t="inlineStr">
         <is>
           <t>EquipGemNotOwned</t>
         </is>
       </c>
-      <c r="B331" t="inlineStr">
+      <c r="B331" s="0" t="inlineStr">
         <is>
           <t>背包里没有这颗宝石</t>
         </is>
       </c>
     </row>
     <row r="332">
-      <c r="A332" t="inlineStr">
+      <c r="A332" s="0" t="inlineStr">
         <is>
           <t>EquipGemSocketInvalid</t>
         </is>
       </c>
-      <c r="B332" t="inlineStr">
+      <c r="B332" s="0" t="inlineStr">
         <is>
           <t>该装备没有这个宝石孔</t>
         </is>
       </c>
     </row>
     <row r="333">
-      <c r="A333" t="inlineStr">
+      <c r="A333" s="0" t="inlineStr">
         <is>
           <t>EquipGemSocketOccupied</t>
         </is>
       </c>
-      <c r="B333" t="inlineStr">
+      <c r="B333" s="0" t="inlineStr">
         <is>
           <t>该孔位已镶有宝石,请先取下</t>
         </is>
       </c>
     </row>
     <row r="334">
-      <c r="A334" t="inlineStr">
+      <c r="A334" s="0" t="inlineStr">
         <is>
           <t>EquipGemSocketEmpty</t>
         </is>
       </c>
-      <c r="B334" t="inlineStr">
+      <c r="B334" s="0" t="inlineStr">
         <is>
           <t>该孔位没有宝石</t>
         </is>
       </c>
     </row>
     <row r="335">
-      <c r="A335" t="inlineStr">
+      <c r="A335" s="0" t="inlineStr">
         <is>
           <t>EquipGemTypeMismatch</t>
         </is>
       </c>
-      <c r="B335" t="inlineStr">
+      <c r="B335" s="0" t="inlineStr">
         <is>
           <t>宝石类型与孔位不符</t>
         </is>
       </c>
     </row>
     <row r="336">
-      <c r="A336" t="inlineStr">
+      <c r="A336" s="0" t="inlineStr">
         <is>
           <t>EquipGemBagFull</t>
         </is>
       </c>
-      <c r="B336" t="inlineStr">
+      <c r="B336" s="0" t="inlineStr">
         <is>
           <t>背包已满,无法取下宝石</t>
         </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>//player_inbox_error base=29000 width=1000</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>PlayerInboxDisabled</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>该类收件箱消息暂未开放</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>PlayerInboxUnknownType</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>未知的收件箱消息类型</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>PlayerInboxPlayerNotFound</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>玩家不存在</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>PlayerInboxPayloadInvalid</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>收件箱消息内容无效</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>PlayerInboxPayloadTooLarge</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>收件箱消息内容过大</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>PlayerInboxTextTooLong</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>操作人、理由或备注过长</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>PlayerInboxIssuedOutOfWindow</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>签发时间超出允许范围</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>PlayerInboxFull</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>该玩家的收件箱已满</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>PlayerInboxIdempotencyConflict</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>请求号已被不同内容使用</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>PlayerInboxStaleOwner</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>场景归属已过期</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>PlayerInboxEpochRequired</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>缺少场景归属代际</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>PlayerInboxEpochAhead</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>场景归属代际超前</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>PlayerInboxItemNotFound</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>收件箱条目不存在</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>PlayerInboxItemStateConflict</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>收件箱条目当前状态不允许该操作</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>PlayerInboxStoreUnavailable</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>收件箱服务暂不可用,请稍后再试</t>
+        </is>
+      </c>
+      <c r="C353" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/data/tip/Tip.xlsx
+++ b/data/tip/Tip.xlsx
@@ -1020,7 +1020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C353"/>
+  <dimension ref="A1:C367"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="8" customWidth="1" style="2" min="3" max="3"/>
@@ -4634,193 +4634,348 @@
         </is>
       </c>
     </row>
+    <row r="337"/>
     <row r="338">
-      <c r="A338" t="inlineStr">
+      <c r="A338" s="0" t="inlineStr">
         <is>
           <t>//player_inbox_error base=29000 width=1000</t>
         </is>
       </c>
     </row>
     <row r="339">
-      <c r="A339" t="inlineStr">
+      <c r="A339" s="0" t="inlineStr">
         <is>
           <t>PlayerInboxDisabled</t>
         </is>
       </c>
-      <c r="B339" t="inlineStr">
+      <c r="B339" s="0" t="inlineStr">
         <is>
           <t>该类收件箱消息暂未开放</t>
         </is>
       </c>
     </row>
     <row r="340">
-      <c r="A340" t="inlineStr">
+      <c r="A340" s="0" t="inlineStr">
         <is>
           <t>PlayerInboxUnknownType</t>
         </is>
       </c>
-      <c r="B340" t="inlineStr">
+      <c r="B340" s="0" t="inlineStr">
         <is>
           <t>未知的收件箱消息类型</t>
         </is>
       </c>
     </row>
     <row r="341">
-      <c r="A341" t="inlineStr">
+      <c r="A341" s="0" t="inlineStr">
         <is>
           <t>PlayerInboxPlayerNotFound</t>
         </is>
       </c>
-      <c r="B341" t="inlineStr">
+      <c r="B341" s="0" t="inlineStr">
         <is>
           <t>玩家不存在</t>
         </is>
       </c>
     </row>
     <row r="342">
-      <c r="A342" t="inlineStr">
+      <c r="A342" s="0" t="inlineStr">
         <is>
           <t>PlayerInboxPayloadInvalid</t>
         </is>
       </c>
-      <c r="B342" t="inlineStr">
+      <c r="B342" s="0" t="inlineStr">
         <is>
           <t>收件箱消息内容无效</t>
         </is>
       </c>
     </row>
     <row r="343">
-      <c r="A343" t="inlineStr">
+      <c r="A343" s="0" t="inlineStr">
         <is>
           <t>PlayerInboxPayloadTooLarge</t>
         </is>
       </c>
-      <c r="B343" t="inlineStr">
+      <c r="B343" s="0" t="inlineStr">
         <is>
           <t>收件箱消息内容过大</t>
         </is>
       </c>
     </row>
     <row r="344">
-      <c r="A344" t="inlineStr">
+      <c r="A344" s="0" t="inlineStr">
         <is>
           <t>PlayerInboxTextTooLong</t>
         </is>
       </c>
-      <c r="B344" t="inlineStr">
+      <c r="B344" s="0" t="inlineStr">
         <is>
           <t>操作人、理由或备注过长</t>
         </is>
       </c>
     </row>
     <row r="345">
-      <c r="A345" t="inlineStr">
+      <c r="A345" s="0" t="inlineStr">
         <is>
           <t>PlayerInboxIssuedOutOfWindow</t>
         </is>
       </c>
-      <c r="B345" t="inlineStr">
+      <c r="B345" s="0" t="inlineStr">
         <is>
           <t>签发时间超出允许范围</t>
         </is>
       </c>
     </row>
     <row r="346">
-      <c r="A346" t="inlineStr">
+      <c r="A346" s="0" t="inlineStr">
         <is>
           <t>PlayerInboxFull</t>
         </is>
       </c>
-      <c r="B346" t="inlineStr">
+      <c r="B346" s="0" t="inlineStr">
         <is>
           <t>该玩家的收件箱已满</t>
         </is>
       </c>
     </row>
     <row r="347">
-      <c r="A347" t="inlineStr">
+      <c r="A347" s="0" t="inlineStr">
         <is>
           <t>PlayerInboxIdempotencyConflict</t>
         </is>
       </c>
-      <c r="B347" t="inlineStr">
+      <c r="B347" s="0" t="inlineStr">
         <is>
           <t>请求号已被不同内容使用</t>
         </is>
       </c>
     </row>
     <row r="348">
-      <c r="A348" t="inlineStr">
+      <c r="A348" s="0" t="inlineStr">
         <is>
           <t>PlayerInboxStaleOwner</t>
         </is>
       </c>
-      <c r="B348" t="inlineStr">
+      <c r="B348" s="0" t="inlineStr">
         <is>
           <t>场景归属已过期</t>
         </is>
       </c>
     </row>
     <row r="349">
-      <c r="A349" t="inlineStr">
+      <c r="A349" s="0" t="inlineStr">
         <is>
           <t>PlayerInboxEpochRequired</t>
         </is>
       </c>
-      <c r="B349" t="inlineStr">
+      <c r="B349" s="0" t="inlineStr">
         <is>
           <t>缺少场景归属代际</t>
         </is>
       </c>
     </row>
     <row r="350">
-      <c r="A350" t="inlineStr">
+      <c r="A350" s="0" t="inlineStr">
         <is>
           <t>PlayerInboxEpochAhead</t>
         </is>
       </c>
-      <c r="B350" t="inlineStr">
+      <c r="B350" s="0" t="inlineStr">
         <is>
           <t>场景归属代际超前</t>
         </is>
       </c>
     </row>
     <row r="351">
-      <c r="A351" t="inlineStr">
+      <c r="A351" s="0" t="inlineStr">
         <is>
           <t>PlayerInboxItemNotFound</t>
         </is>
       </c>
-      <c r="B351" t="inlineStr">
+      <c r="B351" s="0" t="inlineStr">
         <is>
           <t>收件箱条目不存在</t>
         </is>
       </c>
     </row>
     <row r="352">
-      <c r="A352" t="inlineStr">
+      <c r="A352" s="0" t="inlineStr">
         <is>
           <t>PlayerInboxItemStateConflict</t>
         </is>
       </c>
-      <c r="B352" t="inlineStr">
+      <c r="B352" s="0" t="inlineStr">
         <is>
           <t>收件箱条目当前状态不允许该操作</t>
         </is>
       </c>
     </row>
     <row r="353">
-      <c r="A353" t="inlineStr">
+      <c r="A353" s="0" t="inlineStr">
         <is>
           <t>PlayerInboxStoreUnavailable</t>
         </is>
       </c>
-      <c r="B353" t="inlineStr">
+      <c r="B353" s="0" t="inlineStr">
         <is>
           <t>收件箱服务暂不可用,请稍后再试</t>
         </is>
       </c>
-      <c r="C353" t="n">
+      <c r="C353" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>//mystery_merchant_error base=30000 width=1000</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>MysteryMerchantNotPresent</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>神秘商人现在不在,请留意下次出现的公告</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>MysteryMerchantNotHere</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>神秘商人不在这条线上</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>MysteryMerchantTooFar</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>离神秘商人太远了,走近一些再买</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>MysteryMerchantShelfChanged</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>货架已经更新,请重新查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>MysteryMerchantLimitReached</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>这件商品本轮已达限购数量</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>MysteryMerchantCurrencyNotEnough</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>货币不足,无法购买</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>MysteryMerchantBagFull</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>背包已满,无法购买</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>MysteryMerchantInBattle</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>战斗中不能购买</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>MysteryMerchantFrozen</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>角色正在跨区传送,暂时不能购买</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>MysteryMerchantInvalidCount</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>购买数量无效</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>MysteryMerchantItemBlocked</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>这件商品暂时无法购买</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>MysteryMerchantInternalError</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>神秘商人暂时无法交易,请稍后再试</t>
+        </is>
+      </c>
+      <c r="C367" t="n">
         <v>1</v>
       </c>
     </row>

--- a/data/tip/Tip.xlsx
+++ b/data/tip/Tip.xlsx
@@ -1020,7 +1020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C353"/>
+  <dimension ref="A1:C363"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="8" customWidth="1" style="2" min="3" max="3"/>
@@ -3764,7 +3764,7 @@
     <row r="258">
       <c r="A258" s="0" t="inlineStr">
         <is>
-          <t>//   mail_error 17000 / chat_error 18000 / auction_error 19000</t>
+          <t>//   chat_error 18000 / auction_error 19000(mail_error 17000 已建组,在表尾)</t>
         </is>
       </c>
     </row>
@@ -4634,194 +4634,298 @@
         </is>
       </c>
     </row>
+    <row r="337"/>
     <row r="338">
-      <c r="A338" t="inlineStr">
+      <c r="A338" s="0" t="inlineStr">
         <is>
           <t>//player_inbox_error base=29000 width=1000</t>
         </is>
       </c>
     </row>
     <row r="339">
-      <c r="A339" t="inlineStr">
+      <c r="A339" s="0" t="inlineStr">
         <is>
           <t>PlayerInboxDisabled</t>
         </is>
       </c>
-      <c r="B339" t="inlineStr">
+      <c r="B339" s="0" t="inlineStr">
         <is>
           <t>该类收件箱消息暂未开放</t>
         </is>
       </c>
     </row>
     <row r="340">
-      <c r="A340" t="inlineStr">
+      <c r="A340" s="0" t="inlineStr">
         <is>
           <t>PlayerInboxUnknownType</t>
         </is>
       </c>
-      <c r="B340" t="inlineStr">
+      <c r="B340" s="0" t="inlineStr">
         <is>
           <t>未知的收件箱消息类型</t>
         </is>
       </c>
     </row>
     <row r="341">
-      <c r="A341" t="inlineStr">
+      <c r="A341" s="0" t="inlineStr">
         <is>
           <t>PlayerInboxPlayerNotFound</t>
         </is>
       </c>
-      <c r="B341" t="inlineStr">
+      <c r="B341" s="0" t="inlineStr">
         <is>
           <t>玩家不存在</t>
         </is>
       </c>
     </row>
     <row r="342">
-      <c r="A342" t="inlineStr">
+      <c r="A342" s="0" t="inlineStr">
         <is>
           <t>PlayerInboxPayloadInvalid</t>
         </is>
       </c>
-      <c r="B342" t="inlineStr">
+      <c r="B342" s="0" t="inlineStr">
         <is>
           <t>收件箱消息内容无效</t>
         </is>
       </c>
     </row>
     <row r="343">
-      <c r="A343" t="inlineStr">
+      <c r="A343" s="0" t="inlineStr">
         <is>
           <t>PlayerInboxPayloadTooLarge</t>
         </is>
       </c>
-      <c r="B343" t="inlineStr">
+      <c r="B343" s="0" t="inlineStr">
         <is>
           <t>收件箱消息内容过大</t>
         </is>
       </c>
     </row>
     <row r="344">
-      <c r="A344" t="inlineStr">
+      <c r="A344" s="0" t="inlineStr">
         <is>
           <t>PlayerInboxTextTooLong</t>
         </is>
       </c>
-      <c r="B344" t="inlineStr">
+      <c r="B344" s="0" t="inlineStr">
         <is>
           <t>操作人、理由或备注过长</t>
         </is>
       </c>
     </row>
     <row r="345">
-      <c r="A345" t="inlineStr">
+      <c r="A345" s="0" t="inlineStr">
         <is>
           <t>PlayerInboxIssuedOutOfWindow</t>
         </is>
       </c>
-      <c r="B345" t="inlineStr">
+      <c r="B345" s="0" t="inlineStr">
         <is>
           <t>签发时间超出允许范围</t>
         </is>
       </c>
     </row>
     <row r="346">
-      <c r="A346" t="inlineStr">
+      <c r="A346" s="0" t="inlineStr">
         <is>
           <t>PlayerInboxFull</t>
         </is>
       </c>
-      <c r="B346" t="inlineStr">
+      <c r="B346" s="0" t="inlineStr">
         <is>
           <t>该玩家的收件箱已满</t>
         </is>
       </c>
     </row>
     <row r="347">
-      <c r="A347" t="inlineStr">
+      <c r="A347" s="0" t="inlineStr">
         <is>
           <t>PlayerInboxIdempotencyConflict</t>
         </is>
       </c>
-      <c r="B347" t="inlineStr">
+      <c r="B347" s="0" t="inlineStr">
         <is>
           <t>请求号已被不同内容使用</t>
         </is>
       </c>
     </row>
     <row r="348">
-      <c r="A348" t="inlineStr">
+      <c r="A348" s="0" t="inlineStr">
         <is>
           <t>PlayerInboxStaleOwner</t>
         </is>
       </c>
-      <c r="B348" t="inlineStr">
+      <c r="B348" s="0" t="inlineStr">
         <is>
           <t>场景归属已过期</t>
         </is>
       </c>
     </row>
     <row r="349">
-      <c r="A349" t="inlineStr">
+      <c r="A349" s="0" t="inlineStr">
         <is>
           <t>PlayerInboxEpochRequired</t>
         </is>
       </c>
-      <c r="B349" t="inlineStr">
+      <c r="B349" s="0" t="inlineStr">
         <is>
           <t>缺少场景归属代际</t>
         </is>
       </c>
     </row>
     <row r="350">
-      <c r="A350" t="inlineStr">
+      <c r="A350" s="0" t="inlineStr">
         <is>
           <t>PlayerInboxEpochAhead</t>
         </is>
       </c>
-      <c r="B350" t="inlineStr">
+      <c r="B350" s="0" t="inlineStr">
         <is>
           <t>场景归属代际超前</t>
         </is>
       </c>
     </row>
     <row r="351">
-      <c r="A351" t="inlineStr">
+      <c r="A351" s="0" t="inlineStr">
         <is>
           <t>PlayerInboxItemNotFound</t>
         </is>
       </c>
-      <c r="B351" t="inlineStr">
+      <c r="B351" s="0" t="inlineStr">
         <is>
           <t>收件箱条目不存在</t>
         </is>
       </c>
     </row>
     <row r="352">
-      <c r="A352" t="inlineStr">
+      <c r="A352" s="0" t="inlineStr">
         <is>
           <t>PlayerInboxItemStateConflict</t>
         </is>
       </c>
-      <c r="B352" t="inlineStr">
+      <c r="B352" s="0" t="inlineStr">
         <is>
           <t>收件箱条目当前状态不允许该操作</t>
         </is>
       </c>
     </row>
     <row r="353">
-      <c r="A353" t="inlineStr">
+      <c r="A353" s="0" t="inlineStr">
         <is>
           <t>PlayerInboxStoreUnavailable</t>
         </is>
       </c>
-      <c r="B353" t="inlineStr">
+      <c r="B353" s="0" t="inlineStr">
         <is>
           <t>收件箱服务暂不可用,请稍后再试</t>
         </is>
       </c>
-      <c r="C353" t="n">
+      <c r="C353" s="0" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>//mail_error base=17000 width=1000</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>MailClaimNotOpen</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>附件领取暂未开放</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>MailNotFound</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>邮件不存在或已删除</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>MailExpired</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>邮件已过期</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>MailRecipientBoxFull</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>收件人邮箱已满</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>MailAttachmentNotOpen</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>当前环境不允许发送带附件的邮件</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>MailAttachmentInvalid</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>邮件附件不合法</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>MailRequestConflict</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>发件请求编号重复但内容不同</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>MailSystemMailLimit</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>有效系统邮件数量已达上限</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/data/tip/Tip.xlsx
+++ b/data/tip/Tip.xlsx
@@ -1020,7 +1020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C353"/>
+  <dimension ref="A1:C382"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="8" customWidth="1" style="2" min="3" max="3"/>
@@ -3833,997 +3833,1314 @@
     </row>
     <row r="266"/>
     <row r="267">
-      <c r="A267" s="0" t="inlineStr">
-        <is>
-          <t>//attribute_error base=25000 width=1000</t>
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>TradeOrderNotFound</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>交易订单不存在</t>
         </is>
       </c>
     </row>
     <row r="268">
-      <c r="A268" s="0" t="inlineStr">
-        <is>
-          <t>AttributePoolNotFound</t>
-        </is>
-      </c>
-      <c r="B268" s="0" t="inlineStr">
-        <is>
-          <t>属性池不存在</t>
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>TradeOrderStateConflict</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>订单状态已变化，请刷新</t>
         </is>
       </c>
     </row>
     <row r="269">
-      <c r="A269" s="0" t="inlineStr">
-        <is>
-          <t>AttributePoolLocked</t>
-        </is>
-      </c>
-      <c r="B269" s="0" t="inlineStr">
-        <is>
-          <t>该属性池尚未解锁</t>
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>TradeRequestConflict</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>交易请求编号重复但内容不同</t>
         </is>
       </c>
     </row>
     <row r="270">
-      <c r="A270" s="0" t="inlineStr">
-        <is>
-          <t>AttributeDimensionNotFound</t>
-        </is>
-      </c>
-      <c r="B270" s="0" t="inlineStr">
-        <is>
-          <t>属性维度不存在</t>
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>TradeOrderLimit</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>未完成交易数量已达上限</t>
         </is>
       </c>
     </row>
     <row r="271">
-      <c r="A271" s="0" t="inlineStr">
-        <is>
-          <t>AttributePointsNotEnough</t>
-        </is>
-      </c>
-      <c r="B271" s="0" t="inlineStr">
-        <is>
-          <t>剩余点数不足</t>
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>TradeCannotTradeSelf</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>不能与自己交易</t>
         </is>
       </c>
     </row>
     <row r="272">
-      <c r="A272" s="0" t="inlineStr">
-        <is>
-          <t>AttributePointsCannotDecrease</t>
-        </is>
-      </c>
-      <c r="B272" s="0" t="inlineStr">
-        <is>
-          <t>已分配的点数不能减少,请使用重置</t>
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>TradeCounterpartyUnknown</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>交易对方不存在</t>
         </is>
       </c>
     </row>
     <row r="273">
-      <c r="A273" s="0" t="inlineStr">
-        <is>
-          <t>AttributeDimensionCapExceeded</t>
-        </is>
-      </c>
-      <c r="B273" s="0" t="inlineStr">
-        <is>
-          <t>超过单项可分配上限</t>
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>TradeInsufficientAsset</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>可交易资产不足</t>
         </is>
       </c>
     </row>
     <row r="274">
-      <c r="A274" s="0" t="inlineStr">
-        <is>
-          <t>AttributeSchemeNotFound</t>
-        </is>
-      </c>
-      <c r="B274" s="0" t="inlineStr">
-        <is>
-          <t>加点方案不存在</t>
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>TradeBidTooLow</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>出价低于当前最低价</t>
         </is>
       </c>
     </row>
     <row r="275">
-      <c r="A275" s="0" t="inlineStr">
-        <is>
-          <t>AttributeSchemeLimitReached</t>
-        </is>
-      </c>
-      <c r="B275" s="0" t="inlineStr">
-        <is>
-          <t>加点方案数量已达上限</t>
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>TradeAuctionEnded</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>拍卖已经结束</t>
         </is>
       </c>
     </row>
     <row r="276">
-      <c r="A276" s="0" t="inlineStr">
-        <is>
-          <t>AttributeSchemeSwitchCooldown</t>
-        </is>
-      </c>
-      <c r="B276" s="0" t="inlineStr">
-        <is>
-          <t>方案切换冷却中</t>
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>TradeAssetDeliveryPending</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>资产正在到账，请稍后刷新</t>
         </is>
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="0" t="inlineStr">
-        <is>
-          <t>AttributeSchemeNameInvalid</t>
-        </is>
-      </c>
-      <c r="B277" s="0" t="inlineStr">
-        <is>
-          <t>方案名称不合法</t>
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>TradeManualReview</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>交易需要人工核对</t>
         </is>
       </c>
     </row>
     <row r="278">
-      <c r="A278" s="0" t="inlineStr">
-        <is>
-          <t>AttributeSchemeAlreadyActive</t>
-        </is>
-      </c>
-      <c r="B278" s="0" t="inlineStr">
-        <is>
-          <t>已经是当前方案</t>
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>TradeAssetNotTradable</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>该资产不可交易</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="0" t="inlineStr">
         <is>
-          <t>AttributeInBattle</t>
-        </is>
-      </c>
-      <c r="B279" s="0" t="inlineStr">
-        <is>
-          <t>战斗中不能修改属性</t>
+          <t>//attribute_error base=25000 width=1000</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="0" t="inlineStr">
         <is>
-          <t>AttributeGoldNotEnough</t>
+          <t>AttributePoolNotFound</t>
         </is>
       </c>
       <c r="B280" s="0" t="inlineStr">
         <is>
-          <t>金币不足</t>
+          <t>属性池不存在</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="0" t="inlineStr">
         <is>
-          <t>AttributeNoAutoPlan</t>
+          <t>AttributePoolLocked</t>
         </is>
       </c>
       <c r="B281" s="0" t="inlineStr">
         <is>
-          <t>没有可用的自动加点方案</t>
+          <t>该属性池尚未解锁</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="0" t="inlineStr">
         <is>
-          <t>AttributeNothingToChange</t>
+          <t>AttributeDimensionNotFound</t>
         </is>
       </c>
       <c r="B282" s="0" t="inlineStr">
         <is>
-          <t>属性没有变化</t>
-        </is>
-      </c>
-    </row>
-    <row r="283"/>
+          <t>属性维度不存在</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="0" t="inlineStr">
+        <is>
+          <t>AttributePointsNotEnough</t>
+        </is>
+      </c>
+      <c r="B283" s="0" t="inlineStr">
+        <is>
+          <t>剩余点数不足</t>
+        </is>
+      </c>
+    </row>
     <row r="284">
       <c r="A284" s="0" t="inlineStr">
         <is>
-          <t>//pet_error base=26000 width=1000</t>
+          <t>AttributePointsCannotDecrease</t>
+        </is>
+      </c>
+      <c r="B284" s="0" t="inlineStr">
+        <is>
+          <t>已分配的点数不能减少,请使用重置</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="0" t="inlineStr">
         <is>
-          <t>PetNotFound</t>
+          <t>AttributeDimensionCapExceeded</t>
         </is>
       </c>
       <c r="B285" s="0" t="inlineStr">
         <is>
-          <t>宝宝不存在</t>
+          <t>超过单项可分配上限</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="0" t="inlineStr">
         <is>
-          <t>PetTableRowMissing</t>
+          <t>AttributeSchemeNotFound</t>
         </is>
       </c>
       <c r="B286" s="0" t="inlineStr">
         <is>
-          <t>宝宝数据已失效,请联系客服</t>
+          <t>加点方案不存在</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="0" t="inlineStr">
         <is>
-          <t>PetSlotFull</t>
+          <t>AttributeSchemeLimitReached</t>
         </is>
       </c>
       <c r="B287" s="0" t="inlineStr">
         <is>
-          <t>可携带的宝宝数量已达上限</t>
+          <t>加点方案数量已达上限</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="0" t="inlineStr">
         <is>
-          <t>PetOwnerLevelNotEnough</t>
+          <t>AttributeSchemeSwitchCooldown</t>
         </is>
       </c>
       <c r="B288" s="0" t="inlineStr">
         <is>
-          <t>主人等级不足,还不能携带这只宝宝</t>
+          <t>方案切换冷却中</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="0" t="inlineStr">
         <is>
-          <t>PetAlreadyActive</t>
+          <t>AttributeSchemeNameInvalid</t>
         </is>
       </c>
       <c r="B289" s="0" t="inlineStr">
         <is>
-          <t>这只宝宝已经在出战中</t>
+          <t>方案名称不合法</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="0" t="inlineStr">
         <is>
-          <t>PetNotActive</t>
+          <t>AttributeSchemeAlreadyActive</t>
         </is>
       </c>
       <c r="B290" s="0" t="inlineStr">
         <is>
-          <t>当前没有出战的宝宝</t>
+          <t>已经是当前方案</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="0" t="inlineStr">
         <is>
-          <t>PetSummonCooldown</t>
+          <t>AttributeInBattle</t>
         </is>
       </c>
       <c r="B291" s="0" t="inlineStr">
         <is>
-          <t>操作太频繁,请稍后再试</t>
+          <t>战斗中不能修改属性</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="0" t="inlineStr">
         <is>
-          <t>PetNameInvalid</t>
+          <t>AttributeGoldNotEnough</t>
         </is>
       </c>
       <c r="B292" s="0" t="inlineStr">
         <is>
-          <t>宝宝名称不合法</t>
+          <t>金币不足</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="0" t="inlineStr">
         <is>
-          <t>PetInBattle</t>
+          <t>AttributeNoAutoPlan</t>
         </is>
       </c>
       <c r="B293" s="0" t="inlineStr">
         <is>
-          <t>战斗中不能操作宝宝</t>
+          <t>没有可用的自动加点方案</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="0" t="inlineStr">
         <is>
-          <t>PetPointsNotEnough</t>
+          <t>AttributeNothingToChange</t>
         </is>
       </c>
       <c r="B294" s="0" t="inlineStr">
         <is>
-          <t>宝宝剩余点数不足</t>
-        </is>
-      </c>
-    </row>
-    <row r="295">
-      <c r="A295" s="0" t="inlineStr">
-        <is>
-          <t>PetPointsCannotDecrease</t>
-        </is>
-      </c>
-      <c r="B295" s="0" t="inlineStr">
-        <is>
-          <t>已分配的点数不能减少,请使用洗点</t>
-        </is>
-      </c>
-    </row>
+          <t>属性没有变化</t>
+        </is>
+      </c>
+    </row>
+    <row r="295"/>
     <row r="296">
       <c r="A296" s="0" t="inlineStr">
         <is>
-          <t>PetDimensionCapExceeded</t>
-        </is>
-      </c>
-      <c r="B296" s="0" t="inlineStr">
-        <is>
-          <t>超过单项可分配上限</t>
+          <t>//pet_error base=26000 width=1000</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="0" t="inlineStr">
         <is>
-          <t>PetDimensionNotFound</t>
+          <t>PetNotFound</t>
         </is>
       </c>
       <c r="B297" s="0" t="inlineStr">
         <is>
-          <t>宝宝属性维度不存在</t>
+          <t>宝宝不存在</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="0" t="inlineStr">
         <is>
-          <t>PetGoldNotEnough</t>
+          <t>PetTableRowMissing</t>
         </is>
       </c>
       <c r="B298" s="0" t="inlineStr">
         <is>
-          <t>金币不足</t>
+          <t>宝宝数据已失效,请联系客服</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="0" t="inlineStr">
         <is>
-          <t>PetNoAutoPlan</t>
+          <t>PetSlotFull</t>
         </is>
       </c>
       <c r="B299" s="0" t="inlineStr">
         <is>
-          <t>没有可用的自动加点方案</t>
+          <t>可携带的宝宝数量已达上限</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="0" t="inlineStr">
         <is>
-          <t>PetNothingToChange</t>
+          <t>PetOwnerLevelNotEnough</t>
         </is>
       </c>
       <c r="B300" s="0" t="inlineStr">
         <is>
-          <t>宝宝属性没有变化</t>
+          <t>主人等级不足,还不能携带这只宝宝</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="0" t="inlineStr">
         <is>
-          <t>PetIdGenerateFailed</t>
+          <t>PetAlreadyActive</t>
         </is>
       </c>
       <c r="B301" s="0" t="inlineStr">
         <is>
-          <t>宝宝创建失败,请稍后再试</t>
-        </is>
-      </c>
-      <c r="C301" s="0" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="302"/>
+          <t>这只宝宝已经在出战中</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="0" t="inlineStr">
+        <is>
+          <t>PetNotActive</t>
+        </is>
+      </c>
+      <c r="B302" s="0" t="inlineStr">
+        <is>
+          <t>当前没有出战的宝宝</t>
+        </is>
+      </c>
+    </row>
     <row r="303">
       <c r="A303" s="0" t="inlineStr">
         <is>
-          <t>//asset_error base=27000 width=1000</t>
+          <t>PetSummonCooldown</t>
+        </is>
+      </c>
+      <c r="B303" s="0" t="inlineStr">
+        <is>
+          <t>操作太频繁,请稍后再试</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="0" t="inlineStr">
         <is>
-          <t>AssetCurrencyInsufficient</t>
+          <t>PetNameInvalid</t>
         </is>
       </c>
       <c r="B304" s="0" t="inlineStr">
         <is>
-          <t>货币不足</t>
+          <t>宝宝名称不合法</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="0" t="inlineStr">
         <is>
-          <t>AssetBagFull</t>
+          <t>PetInBattle</t>
         </is>
       </c>
       <c r="B305" s="0" t="inlineStr">
         <is>
-          <t>背包已满，请腾出空间，之后会重试发放；超过时限可能取消</t>
+          <t>战斗中不能操作宝宝</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="0" t="inlineStr">
         <is>
-          <t>AssetInBattle</t>
+          <t>PetPointsNotEnough</t>
         </is>
       </c>
       <c r="B306" s="0" t="inlineStr">
         <is>
-          <t>战斗中暂不结算，稍后自动重试；超过时限可能取消</t>
+          <t>宝宝剩余点数不足</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="0" t="inlineStr">
         <is>
-          <t>AssetFrozen</t>
+          <t>PetPointsCannotDecrease</t>
         </is>
       </c>
       <c r="B307" s="0" t="inlineStr">
         <is>
-          <t>角色迁移中，稍后自动重试；超过时限可能取消</t>
+          <t>已分配的点数不能减少,请使用洗点</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="0" t="inlineStr">
         <is>
-          <t>AssetInvalidBundle</t>
+          <t>PetDimensionCapExceeded</t>
         </is>
       </c>
       <c r="B308" s="0" t="inlineStr">
         <is>
-          <t>资产指令无效</t>
-        </is>
-      </c>
-      <c r="C308" s="0" t="n">
-        <v>1</v>
+          <t>超过单项可分配上限</t>
+        </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="0" t="inlineStr">
         <is>
-          <t>AssetBlocked</t>
+          <t>PetDimensionNotFound</t>
         </is>
       </c>
       <c r="B309" s="0" t="inlineStr">
         <is>
-          <t>该资产当前被禁止获取</t>
+          <t>宝宝属性维度不存在</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="0" t="inlineStr">
         <is>
-          <t>AssetPlayerNotHere</t>
+          <t>PetGoldNotEnough</t>
         </is>
       </c>
       <c r="B310" s="0" t="inlineStr">
         <is>
-          <t>角色不在线，上线后重试；超过时限可能取消</t>
+          <t>金币不足</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="0" t="inlineStr">
         <is>
-          <t>AssetPartialApplied</t>
+          <t>PetNoAutoPlan</t>
         </is>
       </c>
       <c r="B311" s="0" t="inlineStr">
         <is>
-          <t>资产只发放了一部分，已记录，将由客服补偿</t>
-        </is>
-      </c>
-      <c r="C311" s="0" t="n">
-        <v>1</v>
+          <t>没有可用的自动加点方案</t>
+        </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="0" t="inlineStr">
         <is>
-          <t>AssetAuthFailed</t>
+          <t>PetNothingToChange</t>
         </is>
       </c>
       <c r="B312" s="0" t="inlineStr">
         <is>
-          <t>资产指令校验失败</t>
-        </is>
-      </c>
-      <c r="C312" s="0" t="n">
+          <t>宝宝属性没有变化</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="0" t="inlineStr">
+        <is>
+          <t>PetIdGenerateFailed</t>
+        </is>
+      </c>
+      <c r="B313" s="0" t="inlineStr">
+        <is>
+          <t>宝宝创建失败,请稍后再试</t>
+        </is>
+      </c>
+      <c r="C313" s="0" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="313"/>
-    <row r="314">
-      <c r="A314" s="0" t="inlineStr">
-        <is>
-          <t>//equip_error base=28000 width=1000</t>
-        </is>
-      </c>
-    </row>
+    <row r="314"/>
     <row r="315">
       <c r="A315" s="0" t="inlineStr">
         <is>
-          <t>EquipItemNotFound</t>
-        </is>
-      </c>
-      <c r="B315" s="0" t="inlineStr">
-        <is>
-          <t>物品不存在</t>
+          <t>//asset_error base=27000 width=1000</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="0" t="inlineStr">
         <is>
-          <t>EquipNotEquipment</t>
+          <t>AssetCurrencyInsufficient</t>
         </is>
       </c>
       <c r="B316" s="0" t="inlineStr">
         <is>
-          <t>该物品不是装备</t>
+          <t>货币不足</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="0" t="inlineStr">
         <is>
-          <t>EquipLevelNotEnough</t>
+          <t>AssetBagFull</t>
         </is>
       </c>
       <c r="B317" s="0" t="inlineStr">
         <is>
-          <t>等级不足,无法装备</t>
+          <t>背包已满，请腾出空间，之后会重试发放；超过时限可能取消</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="0" t="inlineStr">
         <is>
-          <t>EquipClassMismatch</t>
+          <t>AssetInBattle</t>
         </is>
       </c>
       <c r="B318" s="0" t="inlineStr">
         <is>
-          <t>职业不符,无法装备</t>
+          <t>战斗中暂不结算，稍后自动重试；超过时限可能取消</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="0" t="inlineStr">
         <is>
-          <t>EquipNoSlot</t>
+          <t>AssetFrozen</t>
         </is>
       </c>
       <c r="B319" s="0" t="inlineStr">
         <is>
-          <t>没有可用的装备栏位</t>
+          <t>角色迁移中，稍后自动重试；超过时限可能取消</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="0" t="inlineStr">
         <is>
-          <t>EquipNotEquipped</t>
+          <t>AssetInvalidBundle</t>
         </is>
       </c>
       <c r="B320" s="0" t="inlineStr">
         <is>
-          <t>该装备未穿戴</t>
-        </is>
+          <t>资产指令无效</t>
+        </is>
+      </c>
+      <c r="C320" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="0" t="inlineStr">
         <is>
-          <t>EquipBagFull</t>
+          <t>AssetBlocked</t>
         </is>
       </c>
       <c r="B321" s="0" t="inlineStr">
         <is>
-          <t>背包已满,无法卸下</t>
+          <t>该资产当前被禁止获取</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="0" t="inlineStr">
         <is>
-          <t>EquipInBattle</t>
+          <t>AssetPlayerNotHere</t>
         </is>
       </c>
       <c r="B322" s="0" t="inlineStr">
         <is>
-          <t>战斗中无法更换装备</t>
+          <t>角色不在线，上线后重试；超过时限可能取消</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="0" t="inlineStr">
         <is>
-          <t>EquipFrozen</t>
+          <t>AssetPartialApplied</t>
         </is>
       </c>
       <c r="B323" s="0" t="inlineStr">
         <is>
-          <t>当前状态无法更换装备</t>
-        </is>
+          <t>资产只发放了一部分，已记录，将由客服补偿</t>
+        </is>
+      </c>
+      <c r="C323" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="0" t="inlineStr">
         <is>
-          <t>EquipGrantInvalid</t>
+          <t>AssetAuthFailed</t>
         </is>
       </c>
       <c r="B324" s="0" t="inlineStr">
         <is>
-          <t>发放参数无效</t>
-        </is>
-      </c>
-    </row>
-    <row r="325">
-      <c r="A325" s="0" t="inlineStr">
-        <is>
-          <t>EquipInternalError</t>
-        </is>
-      </c>
-      <c r="B325" s="0" t="inlineStr">
-        <is>
-          <t>装备操作失败,请稍后再试</t>
-        </is>
-      </c>
-      <c r="C325" s="0" t="n">
+          <t>资产指令校验失败</t>
+        </is>
+      </c>
+      <c r="C324" s="0" t="n">
         <v>1</v>
       </c>
     </row>
+    <row r="325"/>
     <row r="326">
       <c r="A326" s="0" t="inlineStr">
         <is>
-          <t>EquipEnhanceUnavailable</t>
-        </is>
-      </c>
-      <c r="B326" s="0" t="inlineStr">
-        <is>
-          <t>该装备无法强化</t>
+          <t>//equip_error base=28000 width=1000</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="0" t="inlineStr">
         <is>
-          <t>EquipEnhanceMaxLevel</t>
+          <t>EquipItemNotFound</t>
         </is>
       </c>
       <c r="B327" s="0" t="inlineStr">
         <is>
-          <t>已强化到最高等级</t>
+          <t>物品不存在</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="0" t="inlineStr">
         <is>
-          <t>EquipEnhanceMaterialNotEnough</t>
+          <t>EquipNotEquipment</t>
         </is>
       </c>
       <c r="B328" s="0" t="inlineStr">
         <is>
-          <t>强化材料不足</t>
+          <t>该物品不是装备</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="0" t="inlineStr">
         <is>
-          <t>EquipEnhanceGoldNotEnough</t>
+          <t>EquipLevelNotEnough</t>
         </is>
       </c>
       <c r="B329" s="0" t="inlineStr">
         <is>
-          <t>金币不足,无法强化</t>
+          <t>等级不足,无法装备</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="0" t="inlineStr">
         <is>
-          <t>EquipGemNotGem</t>
+          <t>EquipClassMismatch</t>
         </is>
       </c>
       <c r="B330" s="0" t="inlineStr">
         <is>
-          <t>该物品不是宝石</t>
+          <t>职业不符,无法装备</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="0" t="inlineStr">
         <is>
-          <t>EquipGemNotOwned</t>
+          <t>EquipNoSlot</t>
         </is>
       </c>
       <c r="B331" s="0" t="inlineStr">
         <is>
-          <t>背包里没有这颗宝石</t>
+          <t>没有可用的装备栏位</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="0" t="inlineStr">
         <is>
-          <t>EquipGemSocketInvalid</t>
+          <t>EquipNotEquipped</t>
         </is>
       </c>
       <c r="B332" s="0" t="inlineStr">
         <is>
-          <t>该装备没有这个宝石孔</t>
+          <t>该装备未穿戴</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="0" t="inlineStr">
         <is>
-          <t>EquipGemSocketOccupied</t>
+          <t>EquipBagFull</t>
         </is>
       </c>
       <c r="B333" s="0" t="inlineStr">
         <is>
-          <t>该孔位已镶有宝石,请先取下</t>
+          <t>背包已满,无法卸下</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="0" t="inlineStr">
         <is>
-          <t>EquipGemSocketEmpty</t>
+          <t>EquipInBattle</t>
         </is>
       </c>
       <c r="B334" s="0" t="inlineStr">
         <is>
-          <t>该孔位没有宝石</t>
+          <t>战斗中无法更换装备</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="0" t="inlineStr">
         <is>
-          <t>EquipGemTypeMismatch</t>
+          <t>EquipFrozen</t>
         </is>
       </c>
       <c r="B335" s="0" t="inlineStr">
         <is>
-          <t>宝石类型与孔位不符</t>
+          <t>当前状态无法更换装备</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="0" t="inlineStr">
         <is>
+          <t>EquipGrantInvalid</t>
+        </is>
+      </c>
+      <c r="B336" s="0" t="inlineStr">
+        <is>
+          <t>发放参数无效</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="0" t="inlineStr">
+        <is>
+          <t>EquipInternalError</t>
+        </is>
+      </c>
+      <c r="B337" s="0" t="inlineStr">
+        <is>
+          <t>装备操作失败,请稍后再试</t>
+        </is>
+      </c>
+      <c r="C337" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="0" t="inlineStr">
+        <is>
+          <t>EquipEnhanceUnavailable</t>
+        </is>
+      </c>
+      <c r="B338" s="0" t="inlineStr">
+        <is>
+          <t>该装备无法强化</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="0" t="inlineStr">
+        <is>
+          <t>EquipEnhanceMaxLevel</t>
+        </is>
+      </c>
+      <c r="B339" s="0" t="inlineStr">
+        <is>
+          <t>已强化到最高等级</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="0" t="inlineStr">
+        <is>
+          <t>EquipEnhanceMaterialNotEnough</t>
+        </is>
+      </c>
+      <c r="B340" s="0" t="inlineStr">
+        <is>
+          <t>强化材料不足</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="0" t="inlineStr">
+        <is>
+          <t>EquipEnhanceGoldNotEnough</t>
+        </is>
+      </c>
+      <c r="B341" s="0" t="inlineStr">
+        <is>
+          <t>金币不足,无法强化</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="0" t="inlineStr">
+        <is>
+          <t>EquipGemNotGem</t>
+        </is>
+      </c>
+      <c r="B342" s="0" t="inlineStr">
+        <is>
+          <t>该物品不是宝石</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="0" t="inlineStr">
+        <is>
+          <t>EquipGemNotOwned</t>
+        </is>
+      </c>
+      <c r="B343" s="0" t="inlineStr">
+        <is>
+          <t>背包里没有这颗宝石</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="0" t="inlineStr">
+        <is>
+          <t>EquipGemSocketInvalid</t>
+        </is>
+      </c>
+      <c r="B344" s="0" t="inlineStr">
+        <is>
+          <t>该装备没有这个宝石孔</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="0" t="inlineStr">
+        <is>
+          <t>EquipGemSocketOccupied</t>
+        </is>
+      </c>
+      <c r="B345" s="0" t="inlineStr">
+        <is>
+          <t>该孔位已镶有宝石,请先取下</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="0" t="inlineStr">
+        <is>
+          <t>EquipGemSocketEmpty</t>
+        </is>
+      </c>
+      <c r="B346" s="0" t="inlineStr">
+        <is>
+          <t>该孔位没有宝石</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="0" t="inlineStr">
+        <is>
+          <t>EquipGemTypeMismatch</t>
+        </is>
+      </c>
+      <c r="B347" s="0" t="inlineStr">
+        <is>
+          <t>宝石类型与孔位不符</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="0" t="inlineStr">
+        <is>
           <t>EquipGemBagFull</t>
         </is>
       </c>
-      <c r="B336" s="0" t="inlineStr">
+      <c r="B348" s="0" t="inlineStr">
         <is>
           <t>背包已满,无法取下宝石</t>
         </is>
       </c>
     </row>
-    <row r="338">
-      <c r="A338" t="inlineStr">
+    <row r="349"/>
+    <row r="350">
+      <c r="A350" s="0" t="inlineStr">
         <is>
           <t>//player_inbox_error base=29000 width=1000</t>
         </is>
       </c>
     </row>
-    <row r="339">
-      <c r="A339" t="inlineStr">
+    <row r="351">
+      <c r="A351" s="0" t="inlineStr">
         <is>
           <t>PlayerInboxDisabled</t>
         </is>
       </c>
-      <c r="B339" t="inlineStr">
+      <c r="B351" s="0" t="inlineStr">
         <is>
           <t>该类收件箱消息暂未开放</t>
         </is>
       </c>
     </row>
-    <row r="340">
-      <c r="A340" t="inlineStr">
+    <row r="352">
+      <c r="A352" s="0" t="inlineStr">
         <is>
           <t>PlayerInboxUnknownType</t>
         </is>
       </c>
-      <c r="B340" t="inlineStr">
+      <c r="B352" s="0" t="inlineStr">
         <is>
           <t>未知的收件箱消息类型</t>
         </is>
       </c>
     </row>
-    <row r="341">
-      <c r="A341" t="inlineStr">
+    <row r="353">
+      <c r="A353" s="0" t="inlineStr">
         <is>
           <t>PlayerInboxPlayerNotFound</t>
         </is>
       </c>
-      <c r="B341" t="inlineStr">
+      <c r="B353" s="0" t="inlineStr">
         <is>
           <t>玩家不存在</t>
         </is>
       </c>
     </row>
-    <row r="342">
-      <c r="A342" t="inlineStr">
+    <row r="354">
+      <c r="A354" s="0" t="inlineStr">
         <is>
           <t>PlayerInboxPayloadInvalid</t>
         </is>
       </c>
-      <c r="B342" t="inlineStr">
+      <c r="B354" s="0" t="inlineStr">
         <is>
           <t>收件箱消息内容无效</t>
         </is>
       </c>
     </row>
-    <row r="343">
-      <c r="A343" t="inlineStr">
+    <row r="355">
+      <c r="A355" s="0" t="inlineStr">
         <is>
           <t>PlayerInboxPayloadTooLarge</t>
         </is>
       </c>
-      <c r="B343" t="inlineStr">
+      <c r="B355" s="0" t="inlineStr">
         <is>
           <t>收件箱消息内容过大</t>
         </is>
       </c>
     </row>
-    <row r="344">
-      <c r="A344" t="inlineStr">
+    <row r="356">
+      <c r="A356" s="0" t="inlineStr">
         <is>
           <t>PlayerInboxTextTooLong</t>
         </is>
       </c>
-      <c r="B344" t="inlineStr">
+      <c r="B356" s="0" t="inlineStr">
         <is>
           <t>操作人、理由或备注过长</t>
         </is>
       </c>
     </row>
-    <row r="345">
-      <c r="A345" t="inlineStr">
+    <row r="357">
+      <c r="A357" s="0" t="inlineStr">
         <is>
           <t>PlayerInboxIssuedOutOfWindow</t>
         </is>
       </c>
-      <c r="B345" t="inlineStr">
+      <c r="B357" s="0" t="inlineStr">
         <is>
           <t>签发时间超出允许范围</t>
         </is>
       </c>
     </row>
-    <row r="346">
-      <c r="A346" t="inlineStr">
+    <row r="358">
+      <c r="A358" s="0" t="inlineStr">
         <is>
           <t>PlayerInboxFull</t>
         </is>
       </c>
-      <c r="B346" t="inlineStr">
+      <c r="B358" s="0" t="inlineStr">
         <is>
           <t>该玩家的收件箱已满</t>
         </is>
       </c>
     </row>
-    <row r="347">
-      <c r="A347" t="inlineStr">
+    <row r="359">
+      <c r="A359" s="0" t="inlineStr">
         <is>
           <t>PlayerInboxIdempotencyConflict</t>
         </is>
       </c>
-      <c r="B347" t="inlineStr">
+      <c r="B359" s="0" t="inlineStr">
         <is>
           <t>请求号已被不同内容使用</t>
         </is>
       </c>
     </row>
-    <row r="348">
-      <c r="A348" t="inlineStr">
+    <row r="360">
+      <c r="A360" s="0" t="inlineStr">
         <is>
           <t>PlayerInboxStaleOwner</t>
         </is>
       </c>
-      <c r="B348" t="inlineStr">
+      <c r="B360" s="0" t="inlineStr">
         <is>
           <t>场景归属已过期</t>
         </is>
       </c>
     </row>
-    <row r="349">
-      <c r="A349" t="inlineStr">
+    <row r="361">
+      <c r="A361" s="0" t="inlineStr">
         <is>
           <t>PlayerInboxEpochRequired</t>
         </is>
       </c>
-      <c r="B349" t="inlineStr">
+      <c r="B361" s="0" t="inlineStr">
         <is>
           <t>缺少场景归属代际</t>
         </is>
       </c>
     </row>
-    <row r="350">
-      <c r="A350" t="inlineStr">
+    <row r="362">
+      <c r="A362" s="0" t="inlineStr">
         <is>
           <t>PlayerInboxEpochAhead</t>
         </is>
       </c>
-      <c r="B350" t="inlineStr">
+      <c r="B362" s="0" t="inlineStr">
         <is>
           <t>场景归属代际超前</t>
         </is>
       </c>
     </row>
-    <row r="351">
-      <c r="A351" t="inlineStr">
+    <row r="363">
+      <c r="A363" s="0" t="inlineStr">
         <is>
           <t>PlayerInboxItemNotFound</t>
         </is>
       </c>
-      <c r="B351" t="inlineStr">
+      <c r="B363" s="0" t="inlineStr">
         <is>
           <t>收件箱条目不存在</t>
         </is>
       </c>
     </row>
-    <row r="352">
-      <c r="A352" t="inlineStr">
+    <row r="364">
+      <c r="A364" s="0" t="inlineStr">
         <is>
           <t>PlayerInboxItemStateConflict</t>
         </is>
       </c>
-      <c r="B352" t="inlineStr">
+      <c r="B364" s="0" t="inlineStr">
         <is>
           <t>收件箱条目当前状态不允许该操作</t>
         </is>
       </c>
     </row>
-    <row r="353">
-      <c r="A353" t="inlineStr">
+    <row r="365">
+      <c r="A365" s="0" t="inlineStr">
         <is>
           <t>PlayerInboxStoreUnavailable</t>
         </is>
       </c>
-      <c r="B353" t="inlineStr">
+      <c r="B365" s="0" t="inlineStr">
         <is>
           <t>收件箱服务暂不可用,请稍后再试</t>
         </is>
       </c>
-      <c r="C353" t="n">
+      <c r="C365" s="0" t="n">
         <v>1</v>
       </c>
     </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>//mail_error base=17000 width=1000</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>MailNotFound</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>邮件不存在或已删除</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>MailExpired</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>邮件已过期</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>MailRecipientBoxFull</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>收件人邮箱已满</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>MailAttachmentInvalid</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>邮件附件不合法</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>MailRequestConflict</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>发件请求编号重复但内容不同</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>MailSystemMailLimit</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>有效系统邮件数量已达上限</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>MailClaimPending</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>附件正在到账，请稍后刷新</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>MailClaimManual</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>附件到账需人工核对</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>MailAttachmentProtected</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>该邮件仍有待处理附件，暂不能删除</t>
+        </is>
+      </c>
+    </row>
+    <row r="376"/>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>//rank_error base=21000 width=1000</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>RankBoardNotFound</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>排行榜不存在</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>RankGenerationClosed</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>排行榜本期已封榜</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>RankRequestConflict</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>排行榜请求编号重复但内容不同</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>RankSettlementPending</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>排行榜结算处理中</t>
+        </is>
+      </c>
+    </row>
+    <row r="382"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/tip/Tip.xlsx
+++ b/data/tip/Tip.xlsx
@@ -1020,7 +1020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C382"/>
+  <dimension ref="A1:C383"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="8" customWidth="1" style="2" min="3" max="3"/>
@@ -1754,91 +1754,105 @@
       <c r="C73" s="0" t="n"/>
     </row>
     <row r="74" ht="20" customHeight="1" s="2">
-      <c r="A74" s="0" t="inlineStr">
-        <is>
-          <t>//scene_error base=3000 width=1000</t>
-        </is>
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>LoginAuthProviderUnavailable</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>登录渠道暂时不可用，请稍后重试</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="75" ht="20" customHeight="1" s="2">
-      <c r="A75" s="0" t="inlineStr">
-        <is>
-          <t>EnterSceneNotFound</t>
-        </is>
-      </c>
-      <c r="B75" s="0" t="inlineStr">
-        <is>
-          <t>想进入的场景未找到</t>
-        </is>
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>LoginTokenIssueFailed</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>登录凭证签发失败，请稍后重试</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="76" ht="20" customHeight="1" s="2">
       <c r="A76" s="0" t="inlineStr">
         <is>
-          <t>EnterSceneNotFull</t>
-        </is>
-      </c>
-      <c r="B76" s="0" t="inlineStr"/>
+          <t>//scene_error base=3000 width=1000</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="0" t="inlineStr">
         <is>
-          <t>EnterSceneMainFull</t>
+          <t>EnterSceneNotFound</t>
         </is>
       </c>
       <c r="B77" s="0" t="inlineStr">
         <is>
-          <t>主场景已经满了</t>
+          <t>想进入的场景未找到</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="0" t="inlineStr">
         <is>
-          <t>EnterNodeUnavailable</t>
-        </is>
-      </c>
-      <c r="B78" s="0" t="inlineStr">
-        <is>
-          <t>进入的游戏节点已不可用了</t>
-        </is>
-      </c>
-      <c r="C78" s="0" t="n">
-        <v>1</v>
-      </c>
+          <t>EnterSceneNotFull</t>
+        </is>
+      </c>
+      <c r="B78" s="0" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="0" t="inlineStr">
         <is>
-          <t>EnterSceneServerType</t>
+          <t>EnterSceneMainFull</t>
         </is>
       </c>
       <c r="B79" s="0" t="inlineStr">
         <is>
-          <t>服务器未找到</t>
+          <t>主场景已经满了</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="0" t="inlineStr">
         <is>
-          <t>EnterSceneParamError</t>
-        </is>
-      </c>
-      <c r="B80" s="0" t="inlineStr"/>
+          <t>EnterNodeUnavailable</t>
+        </is>
+      </c>
+      <c r="B80" s="0" t="inlineStr">
+        <is>
+          <t>进入的游戏节点已不可用了</t>
+        </is>
+      </c>
+      <c r="C80" s="0" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="0" t="inlineStr">
         <is>
-          <t>EnterSceneSceneFull</t>
-        </is>
-      </c>
-      <c r="B81" s="0" t="inlineStr"/>
+          <t>EnterSceneServerType</t>
+        </is>
+      </c>
+      <c r="B81" s="0" t="inlineStr">
+        <is>
+          <t>服务器未找到</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="0" t="inlineStr">
         <is>
-          <t>EnterSceneSceneNotFound</t>
+          <t>EnterSceneParamError</t>
         </is>
       </c>
       <c r="B82" s="0" t="inlineStr"/>
@@ -1846,7 +1860,7 @@
     <row r="83">
       <c r="A83" s="0" t="inlineStr">
         <is>
-          <t>EnterSceneYouInCurrentScene</t>
+          <t>EnterSceneSceneFull</t>
         </is>
       </c>
       <c r="B83" s="0" t="inlineStr"/>
@@ -1854,7 +1868,7 @@
     <row r="84">
       <c r="A84" s="0" t="inlineStr">
         <is>
-          <t>EnterSceneEnterCrossRoomScene</t>
+          <t>EnterSceneSceneNotFound</t>
         </is>
       </c>
       <c r="B84" s="0" t="inlineStr"/>
@@ -1862,18 +1876,15 @@
     <row r="85">
       <c r="A85" s="0" t="inlineStr">
         <is>
-          <t>EnterSceneGsInfoNull</t>
+          <t>EnterSceneYouInCurrentScene</t>
         </is>
       </c>
       <c r="B85" s="0" t="inlineStr"/>
-      <c r="C85" s="0" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="86">
       <c r="A86" s="0" t="inlineStr">
         <is>
-          <t>EnterSceneGsFull</t>
+          <t>EnterSceneEnterCrossRoomScene</t>
         </is>
       </c>
       <c r="B86" s="0" t="inlineStr"/>
@@ -1881,7 +1892,7 @@
     <row r="87">
       <c r="A87" s="0" t="inlineStr">
         <is>
-          <t>EnterSceneYourSceneIsNull</t>
+          <t>EnterSceneGsInfoNull</t>
         </is>
       </c>
       <c r="B87" s="0" t="inlineStr"/>
@@ -1892,7 +1903,7 @@
     <row r="88">
       <c r="A88" s="0" t="inlineStr">
         <is>
-          <t>EnterSceneChangeSceneOffLine</t>
+          <t>EnterSceneGsFull</t>
         </is>
       </c>
       <c r="B88" s="0" t="inlineStr"/>
@@ -1900,15 +1911,18 @@
     <row r="89">
       <c r="A89" s="0" t="inlineStr">
         <is>
-          <t>EnterSceneChangingScene</t>
+          <t>EnterSceneYourSceneIsNull</t>
         </is>
       </c>
       <c r="B89" s="0" t="inlineStr"/>
+      <c r="C89" s="0" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="0" t="inlineStr">
         <is>
-          <t>EnterSceneChangingGs</t>
+          <t>EnterSceneChangeSceneOffLine</t>
         </is>
       </c>
       <c r="B90" s="0" t="inlineStr"/>
@@ -1916,18 +1930,15 @@
     <row r="91">
       <c r="A91" s="0" t="inlineStr">
         <is>
-          <t>ChangeScenePlayerQueueNotFound</t>
+          <t>EnterSceneChangingScene</t>
         </is>
       </c>
       <c r="B91" s="0" t="inlineStr"/>
-      <c r="C91" s="0" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="92">
       <c r="A92" s="0" t="inlineStr">
         <is>
-          <t>ChangeScenePlayerQueueFull</t>
+          <t>EnterSceneChangingGs</t>
         </is>
       </c>
       <c r="B92" s="0" t="inlineStr"/>
@@ -1935,7 +1946,7 @@
     <row r="93">
       <c r="A93" s="0" t="inlineStr">
         <is>
-          <t>ChangeScenePlayerQueueComponentGsNull</t>
+          <t>ChangeScenePlayerQueueNotFound</t>
         </is>
       </c>
       <c r="B93" s="0" t="inlineStr"/>
@@ -1946,34 +1957,37 @@
     <row r="94">
       <c r="A94" s="0" t="inlineStr">
         <is>
-          <t>ChangeScenePlayerQueueComponentEmpty</t>
+          <t>ChangeScenePlayerQueueFull</t>
         </is>
       </c>
       <c r="B94" s="0" t="inlineStr"/>
-      <c r="C94" s="0" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="95">
       <c r="A95" s="0" t="inlineStr">
         <is>
-          <t>ChangeSceneEnQueueNotSameGs</t>
+          <t>ChangeScenePlayerQueueComponentGsNull</t>
         </is>
       </c>
       <c r="B95" s="0" t="inlineStr"/>
+      <c r="C95" s="0" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="0" t="inlineStr">
         <is>
-          <t>InvalidEnterSceneParameters</t>
+          <t>ChangeScenePlayerQueueComponentEmpty</t>
         </is>
       </c>
       <c r="B96" s="0" t="inlineStr"/>
+      <c r="C96" s="0" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="0" t="inlineStr">
         <is>
-          <t>CheckEnterSceneCreator</t>
+          <t>ChangeSceneEnQueueNotSameGs</t>
         </is>
       </c>
       <c r="B97" s="0" t="inlineStr"/>
@@ -1981,49 +1995,39 @@
     <row r="98">
       <c r="A98" s="0" t="inlineStr">
         <is>
-          <t>EnterSceneFailed</t>
+          <t>InvalidEnterSceneParameters</t>
         </is>
       </c>
       <c r="B98" s="0" t="inlineStr"/>
-      <c r="C98" s="0" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="99">
       <c r="A99" s="0" t="inlineStr">
         <is>
-          <t>ZoneTravelTargetZoneNotFound</t>
-        </is>
-      </c>
-      <c r="B99" s="0" t="inlineStr">
-        <is>
-          <t>目标区服不存在</t>
-        </is>
-      </c>
-      <c r="C99" s="0" t="n"/>
+          <t>CheckEnterSceneCreator</t>
+        </is>
+      </c>
+      <c r="B99" s="0" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="0" t="inlineStr">
         <is>
-          <t>ZoneTravelInBattle</t>
-        </is>
-      </c>
-      <c r="B100" s="0" t="inlineStr">
-        <is>
-          <t>战斗中不能传送</t>
-        </is>
-      </c>
-      <c r="C100" s="0" t="n"/>
+          <t>EnterSceneFailed</t>
+        </is>
+      </c>
+      <c r="B100" s="0" t="inlineStr"/>
+      <c r="C100" s="0" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="0" t="inlineStr">
         <is>
-          <t>ZoneTravelInTeam</t>
+          <t>ZoneTravelTargetZoneNotFound</t>
         </is>
       </c>
       <c r="B101" s="0" t="inlineStr">
         <is>
-          <t>组队中不能传送</t>
+          <t>目标区服不存在</t>
         </is>
       </c>
       <c r="C101" s="0" t="n"/>
@@ -2031,12 +2035,12 @@
     <row r="102">
       <c r="A102" s="0" t="inlineStr">
         <is>
-          <t>ZoneTravelTargetBusy</t>
+          <t>ZoneTravelInBattle</t>
         </is>
       </c>
       <c r="B102" s="0" t="inlineStr">
         <is>
-          <t>目标区服繁忙,请稍后再试</t>
+          <t>战斗中不能传送</t>
         </is>
       </c>
       <c r="C102" s="0" t="n"/>
@@ -2044,173 +2048,175 @@
     <row r="103">
       <c r="A103" s="0" t="inlineStr">
         <is>
-          <t>EnterSceneServerBusy</t>
+          <t>ZoneTravelInTeam</t>
         </is>
       </c>
       <c r="B103" s="0" t="inlineStr">
         <is>
-          <t>服务器繁忙,请稍后再试</t>
-        </is>
-      </c>
-      <c r="C103" s="0" t="n">
-        <v>1</v>
-      </c>
+          <t>组队中不能传送</t>
+        </is>
+      </c>
+      <c r="C103" s="0" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="0" t="inlineStr">
         <is>
-          <t>//team_error base=4000 width=1000</t>
-        </is>
-      </c>
+          <t>ZoneTravelTargetBusy</t>
+        </is>
+      </c>
+      <c r="B104" s="0" t="inlineStr">
+        <is>
+          <t>目标区服繁忙,请稍后再试</t>
+        </is>
+      </c>
+      <c r="C104" s="0" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="0" t="inlineStr">
         <is>
-          <t>TeamNotInApplicants</t>
+          <t>EnterSceneServerBusy</t>
         </is>
       </c>
       <c r="B105" s="0" t="inlineStr">
         <is>
-          <t>(保留)</t>
-        </is>
+          <t>服务器繁忙,请稍后再试</t>
+        </is>
+      </c>
+      <c r="C105" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="0" t="inlineStr">
         <is>
-          <t>TeamPlayerId</t>
-        </is>
-      </c>
-      <c r="B106" s="0" t="inlineStr">
-        <is>
-          <t>玩家 ID 无效</t>
+          <t>//team_error base=4000 width=1000</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="0" t="inlineStr">
         <is>
-          <t>TeamMembersFull</t>
+          <t>TeamNotInApplicants</t>
         </is>
       </c>
       <c r="B107" s="0" t="inlineStr">
         <is>
-          <t>队伍人数已满</t>
+          <t>(保留)</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="0" t="inlineStr">
         <is>
-          <t>TeamMemberInTeam</t>
+          <t>TeamPlayerId</t>
         </is>
       </c>
       <c r="B108" s="0" t="inlineStr">
         <is>
-          <t>对方已经在队伍中</t>
+          <t>玩家 ID 无效</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="0" t="inlineStr">
         <is>
-          <t>TeamMemberNotInTeam</t>
+          <t>TeamMembersFull</t>
         </is>
       </c>
       <c r="B109" s="0" t="inlineStr">
         <is>
-          <t>对方不在你的队伍中</t>
+          <t>队伍人数已满</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="0" t="inlineStr">
         <is>
-          <t>TeamKickSelf</t>
+          <t>TeamMemberInTeam</t>
         </is>
       </c>
       <c r="B110" s="0" t="inlineStr">
         <is>
-          <t>不能把自己踢出队伍</t>
+          <t>对方已经在队伍中</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="0" t="inlineStr">
         <is>
-          <t>TeamKickNotLeader</t>
+          <t>TeamMemberNotInTeam</t>
         </is>
       </c>
       <c r="B111" s="0" t="inlineStr">
         <is>
-          <t>只有队长可以踢人</t>
+          <t>对方不在你的队伍中</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="0" t="inlineStr">
         <is>
-          <t>TeamAppointSelf</t>
+          <t>TeamKickSelf</t>
         </is>
       </c>
       <c r="B112" s="0" t="inlineStr">
         <is>
-          <t>你已经是队长了</t>
+          <t>不能把自己踢出队伍</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="0" t="inlineStr">
         <is>
-          <t>TeamAppointLeaderNotLeader</t>
+          <t>TeamKickNotLeader</t>
         </is>
       </c>
       <c r="B113" s="0" t="inlineStr">
         <is>
-          <t>只有队长可以转让队长</t>
+          <t>只有队长可以踢人</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="0" t="inlineStr">
         <is>
-          <t>TeamFull</t>
+          <t>TeamAppointSelf</t>
         </is>
       </c>
       <c r="B114" s="0" t="inlineStr">
         <is>
-          <t>(保留)</t>
+          <t>你已经是队长了</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="0" t="inlineStr">
         <is>
-          <t>TeamInApplicantList</t>
+          <t>TeamAppointLeaderNotLeader</t>
         </is>
       </c>
       <c r="B115" s="0" t="inlineStr">
         <is>
-          <t>(保留)</t>
+          <t>只有队长可以转让队长</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="0" t="inlineStr">
         <is>
-          <t>TeamNotInApplicantList</t>
+          <t>TeamFull</t>
         </is>
       </c>
       <c r="B116" s="0" t="inlineStr">
         <is>
-          <t>该申请已失效</t>
+          <t>(保留)</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="0" t="inlineStr">
         <is>
-          <t>TeamListMaxSize</t>
+          <t>TeamInApplicantList</t>
         </is>
       </c>
       <c r="B117" s="0" t="inlineStr">
@@ -2222,249 +2228,257 @@
     <row r="118">
       <c r="A118" s="0" t="inlineStr">
         <is>
-          <t>TeamHasNotTeamId</t>
+          <t>TeamNotInApplicantList</t>
         </is>
       </c>
       <c r="B118" s="0" t="inlineStr">
         <is>
-          <t>你还没有队伍</t>
+          <t>该申请已失效</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="0" t="inlineStr">
         <is>
-          <t>TeamDismissNotLeader</t>
+          <t>TeamListMaxSize</t>
         </is>
       </c>
       <c r="B119" s="0" t="inlineStr">
         <is>
-          <t>只有队长可以解散队伍</t>
+          <t>(保留)</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="0" t="inlineStr">
         <is>
-          <t>TeamMemberListFull</t>
+          <t>TeamHasNotTeamId</t>
         </is>
       </c>
       <c r="B120" s="0" t="inlineStr">
         <is>
-          <t>(保留)</t>
+          <t>你还没有队伍</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="0" t="inlineStr">
         <is>
-          <t>TeamCreateTeamMaxMemberSize</t>
+          <t>TeamDismissNotLeader</t>
         </is>
       </c>
       <c r="B121" s="0" t="inlineStr">
         <is>
-          <t>(保留)</t>
+          <t>只有队长可以解散队伍</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="0" t="inlineStr">
         <is>
-          <t>TeamPlayerNotFound</t>
+          <t>TeamMemberListFull</t>
         </is>
       </c>
       <c r="B122" s="0" t="inlineStr">
         <is>
-          <t>找不到该玩家</t>
+          <t>(保留)</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="0" t="inlineStr">
         <is>
-          <t>TeamNotLeader</t>
+          <t>TeamCreateTeamMaxMemberSize</t>
         </is>
       </c>
       <c r="B123" s="0" t="inlineStr">
         <is>
-          <t>只有队长可以执行此操作</t>
+          <t>(保留)</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="0" t="inlineStr">
         <is>
-          <t>TeamHomeZoneUnknown</t>
+          <t>TeamPlayerNotFound</t>
         </is>
       </c>
       <c r="B124" s="0" t="inlineStr">
         <is>
-          <t>角色区服信息异常，请重新登录</t>
+          <t>找不到该玩家</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="0" t="inlineStr">
         <is>
-          <t>TeamCrossZoneDenied</t>
+          <t>TeamNotLeader</t>
         </is>
       </c>
       <c r="B125" s="0" t="inlineStr">
         <is>
-          <t>不能与其他区服的玩家组队</t>
+          <t>只有队长可以执行此操作</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="0" t="inlineStr">
         <is>
-          <t>TeamInviteNotFound</t>
+          <t>TeamHomeZoneUnknown</t>
         </is>
       </c>
       <c r="B126" s="0" t="inlineStr">
         <is>
-          <t>邀请已失效</t>
+          <t>角色区服信息异常，请重新登录</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="0" t="inlineStr">
         <is>
-          <t>TeamInviteLimit</t>
+          <t>TeamCrossZoneDenied</t>
         </is>
       </c>
       <c r="B127" s="0" t="inlineStr">
         <is>
-          <t>对方待处理的邀请过多，请稍后再试</t>
+          <t>不能与其他区服的玩家组队</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="0" t="inlineStr">
         <is>
-          <t>TeamInMatch</t>
+          <t>TeamInviteNotFound</t>
         </is>
       </c>
       <c r="B128" s="0" t="inlineStr">
         <is>
-          <t>队伍正在进入战斗，请稍候</t>
+          <t>邀请已失效</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="0" t="inlineStr">
         <is>
-          <t>TeamMemberOffline</t>
+          <t>TeamInviteLimit</t>
         </is>
       </c>
       <c r="B129" s="0" t="inlineStr">
         <is>
-          <t>有队员不在线</t>
+          <t>对方待处理的邀请过多，请稍后再试</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="0" t="inlineStr">
         <is>
-          <t>TeamMemberInBattle</t>
+          <t>TeamInMatch</t>
         </is>
       </c>
       <c r="B130" s="0" t="inlineStr">
         <is>
-          <t>有队员正在战斗中</t>
+          <t>队伍正在进入战斗，请稍候</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="0" t="inlineStr">
         <is>
-          <t>TeamMemberNotReady</t>
+          <t>TeamMemberOffline</t>
         </is>
       </c>
       <c r="B131" s="0" t="inlineStr">
         <is>
-          <t>有队员暂时无法开战</t>
+          <t>有队员不在线</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="0" t="inlineStr">
         <is>
-          <t>TeamDungeonNotOpen</t>
+          <t>TeamMemberInBattle</t>
         </is>
       </c>
       <c r="B132" s="0" t="inlineStr">
         <is>
-          <t>该副本未开放组队</t>
+          <t>有队员正在战斗中</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="0" t="inlineStr">
         <is>
-          <t>TeamSizeExceeded</t>
+          <t>TeamMemberNotReady</t>
         </is>
       </c>
       <c r="B133" s="0" t="inlineStr">
         <is>
-          <t>队伍人数超过该副本上限</t>
+          <t>有队员暂时无法开战</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="0" t="inlineStr">
         <is>
-          <t>TeamStateChanged</t>
+          <t>TeamDungeonNotOpen</t>
         </is>
       </c>
       <c r="B134" s="0" t="inlineStr">
         <is>
-          <t>队伍状态已变化，请重试</t>
+          <t>该副本未开放组队</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="0" t="inlineStr">
         <is>
-          <t>TeamInternal</t>
+          <t>TeamSizeExceeded</t>
         </is>
       </c>
       <c r="B135" s="0" t="inlineStr">
         <is>
-          <t>服务器繁忙，请稍后再试</t>
-        </is>
-      </c>
-      <c r="C135" s="0" t="n">
-        <v>1</v>
+          <t>队伍人数超过该副本上限</t>
+        </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="0" t="inlineStr">
         <is>
-          <t>//mission_error base=5000 width=1000</t>
+          <t>TeamStateChanged</t>
+        </is>
+      </c>
+      <c r="B136" s="0" t="inlineStr">
+        <is>
+          <t>队伍状态已变化，请重试</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="0" t="inlineStr">
         <is>
-          <t>MissionTypeAlreadyExists</t>
-        </is>
-      </c>
-      <c r="B137" s="0" t="inlineStr"/>
+          <t>TeamInternal</t>
+        </is>
+      </c>
+      <c r="B137" s="0" t="inlineStr">
+        <is>
+          <t>服务器繁忙，请稍后再试</t>
+        </is>
+      </c>
+      <c r="C137" s="0" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="0" t="inlineStr">
         <is>
-          <t>MissionAlreadyCompleted</t>
-        </is>
-      </c>
-      <c r="B138" s="0" t="inlineStr"/>
+          <t>//mission_error base=5000 width=1000</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="0" t="inlineStr">
         <is>
-          <t>MissionIdNotInRewardList</t>
+          <t>MissionTypeAlreadyExists</t>
         </is>
       </c>
       <c r="B139" s="0" t="inlineStr"/>
@@ -2472,18 +2486,15 @@
     <row r="140">
       <c r="A140" s="0" t="inlineStr">
         <is>
-          <t>PlayerMissionComponentNotFound</t>
+          <t>MissionAlreadyCompleted</t>
         </is>
       </c>
       <c r="B140" s="0" t="inlineStr"/>
-      <c r="C140" s="0" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="141">
       <c r="A141" s="0" t="inlineStr">
         <is>
-          <t>MissionIdRepeated</t>
+          <t>MissionIdNotInRewardList</t>
         </is>
       </c>
       <c r="B141" s="0" t="inlineStr"/>
@@ -2491,15 +2502,18 @@
     <row r="142">
       <c r="A142" s="0" t="inlineStr">
         <is>
-          <t>ConditionIdOutOfRange</t>
+          <t>PlayerMissionComponentNotFound</t>
         </is>
       </c>
       <c r="B142" s="0" t="inlineStr"/>
+      <c r="C142" s="0" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="0" t="inlineStr">
         <is>
-          <t>MissionNotInProgress</t>
+          <t>MissionIdRepeated</t>
         </is>
       </c>
       <c r="B143" s="0" t="inlineStr"/>
@@ -2507,14 +2521,15 @@
     <row r="144">
       <c r="A144" s="0" t="inlineStr">
         <is>
-          <t>//bag_error base=6000 width=1000</t>
-        </is>
-      </c>
+          <t>ConditionIdOutOfRange</t>
+        </is>
+      </c>
+      <c r="B144" s="0" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="0" t="inlineStr">
         <is>
-          <t>BagDeleteItemFindGuid</t>
+          <t>MissionNotInProgress</t>
         </is>
       </c>
       <c r="B145" s="0" t="inlineStr"/>
@@ -2522,26 +2537,22 @@
     <row r="146">
       <c r="A146" s="0" t="inlineStr">
         <is>
-          <t>BagDeleteItemAlreadyHasGuid</t>
-        </is>
-      </c>
-      <c r="B146" s="0" t="inlineStr"/>
+          <t>//bag_error base=6000 width=1000</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="0" t="inlineStr">
         <is>
-          <t>BagAddItemHasNotBaseComponent</t>
+          <t>BagDeleteItemFindGuid</t>
         </is>
       </c>
       <c r="B147" s="0" t="inlineStr"/>
-      <c r="C147" s="0" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="148">
       <c r="A148" s="0" t="inlineStr">
         <is>
-          <t>BagAddItemInvalidGuid</t>
+          <t>BagDeleteItemAlreadyHasGuid</t>
         </is>
       </c>
       <c r="B148" s="0" t="inlineStr"/>
@@ -2549,15 +2560,18 @@
     <row r="149">
       <c r="A149" s="0" t="inlineStr">
         <is>
-          <t>BagAddItemInvalidParam</t>
+          <t>BagAddItemHasNotBaseComponent</t>
         </is>
       </c>
       <c r="B149" s="0" t="inlineStr"/>
+      <c r="C149" s="0" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="0" t="inlineStr">
         <is>
-          <t>BagAddItemBagFull</t>
+          <t>BagAddItemInvalidGuid</t>
         </is>
       </c>
       <c r="B150" s="0" t="inlineStr"/>
@@ -2565,7 +2579,7 @@
     <row r="151">
       <c r="A151" s="0" t="inlineStr">
         <is>
-          <t>BagItemNotStacked</t>
+          <t>BagAddItemInvalidParam</t>
         </is>
       </c>
       <c r="B151" s="0" t="inlineStr"/>
@@ -2573,7 +2587,7 @@
     <row r="152">
       <c r="A152" s="0" t="inlineStr">
         <is>
-          <t>BagInsufficientItems</t>
+          <t>BagAddItemBagFull</t>
         </is>
       </c>
       <c r="B152" s="0" t="inlineStr"/>
@@ -2581,7 +2595,7 @@
     <row r="153">
       <c r="A153" s="0" t="inlineStr">
         <is>
-          <t>BagDelItemPos</t>
+          <t>BagItemNotStacked</t>
         </is>
       </c>
       <c r="B153" s="0" t="inlineStr"/>
@@ -2589,7 +2603,7 @@
     <row r="154">
       <c r="A154" s="0" t="inlineStr">
         <is>
-          <t>BagDelItemConfig</t>
+          <t>BagInsufficientItems</t>
         </is>
       </c>
       <c r="B154" s="0" t="inlineStr"/>
@@ -2597,7 +2611,7 @@
     <row r="155">
       <c r="A155" s="0" t="inlineStr">
         <is>
-          <t>BagDelItemGuid</t>
+          <t>BagDelItemPos</t>
         </is>
       </c>
       <c r="B155" s="0" t="inlineStr"/>
@@ -2605,7 +2619,7 @@
     <row r="156">
       <c r="A156" s="0" t="inlineStr">
         <is>
-          <t>BagDelItemFindItem</t>
+          <t>BagDelItemConfig</t>
         </is>
       </c>
       <c r="B156" s="0" t="inlineStr"/>
@@ -2613,7 +2627,7 @@
     <row r="157">
       <c r="A157" s="0" t="inlineStr">
         <is>
-          <t>BagDelItemSize</t>
+          <t>BagDelItemGuid</t>
         </is>
       </c>
       <c r="B157" s="0" t="inlineStr"/>
@@ -2621,7 +2635,7 @@
     <row r="158">
       <c r="A158" s="0" t="inlineStr">
         <is>
-          <t>BagItemDeletionSizeMismatch</t>
+          <t>BagDelItemFindItem</t>
         </is>
       </c>
       <c r="B158" s="0" t="inlineStr"/>
@@ -2629,7 +2643,7 @@
     <row r="159">
       <c r="A159" s="0" t="inlineStr">
         <is>
-          <t>BagInsufficientBagSpace</t>
+          <t>BagDelItemSize</t>
         </is>
       </c>
       <c r="B159" s="0" t="inlineStr"/>
@@ -2637,2510 +2651,2525 @@
     <row r="160">
       <c r="A160" s="0" t="inlineStr">
         <is>
-          <t>//skill_error base=7000 width=1000</t>
-        </is>
-      </c>
+          <t>BagItemDeletionSizeMismatch</t>
+        </is>
+      </c>
+      <c r="B160" s="0" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="0" t="inlineStr">
         <is>
-          <t>SkillUnInterruptible</t>
-        </is>
-      </c>
-      <c r="B161" s="0" t="inlineStr">
-        <is>
-          <t>技能不能被打断</t>
-        </is>
-      </c>
+          <t>BagInsufficientBagSpace</t>
+        </is>
+      </c>
+      <c r="B161" s="0" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="0" t="inlineStr">
         <is>
-          <t>SkillInvalidTargetId</t>
-        </is>
-      </c>
-      <c r="B162" s="0" t="inlineStr">
-        <is>
-          <t>目标id错误</t>
+          <t>//skill_error base=7000 width=1000</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="0" t="inlineStr">
         <is>
-          <t>SkillInvalidTarget</t>
+          <t>SkillUnInterruptible</t>
         </is>
       </c>
       <c r="B163" s="0" t="inlineStr">
         <is>
-          <t>未找到释放目标</t>
+          <t>技能不能被打断</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="0" t="inlineStr">
         <is>
-          <t>SkillCooldownNotReady</t>
+          <t>SkillInvalidTargetId</t>
         </is>
       </c>
       <c r="B164" s="0" t="inlineStr">
         <is>
-          <t>技能冷却尚未完成，无法使用技能</t>
+          <t>目标id错误</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="0" t="inlineStr">
         <is>
-          <t>SkillCannotBeCastInCurrentState</t>
+          <t>SkillInvalidTarget</t>
         </is>
       </c>
       <c r="B165" s="0" t="inlineStr">
         <is>
-          <t>当前状态不能释放该技能</t>
+          <t>未找到释放目标</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="0" t="inlineStr">
         <is>
-          <t>SkillCannotBeCastSilenceRestriction</t>
+          <t>SkillCooldownNotReady</t>
         </is>
       </c>
       <c r="B166" s="0" t="inlineStr">
         <is>
-          <t>当前沉默状态不能释放该技能</t>
+          <t>技能冷却尚未完成，无法使用技能</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="0" t="inlineStr">
         <is>
-          <t>SkillCannotBeCastStunRestriction</t>
+          <t>SkillCannotBeCastInCurrentState</t>
         </is>
       </c>
       <c r="B167" s="0" t="inlineStr">
         <is>
-          <t>当前眩晕状态不能释放该技能</t>
+          <t>当前状态不能释放该技能</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="0" t="inlineStr">
         <is>
-          <t>//buff_error base=8000 width=1000</t>
+          <t>SkillCannotBeCastSilenceRestriction</t>
+        </is>
+      </c>
+      <c r="B168" s="0" t="inlineStr">
+        <is>
+          <t>当前沉默状态不能释放该技能</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="0" t="inlineStr">
         <is>
-          <t>BuffMaxBuffStack</t>
+          <t>SkillCannotBeCastStunRestriction</t>
         </is>
       </c>
       <c r="B169" s="0" t="inlineStr">
         <is>
-          <t>buff层数已经最大</t>
+          <t>当前眩晕状态不能释放该技能</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="0" t="inlineStr">
         <is>
-          <t>BuffTargetImmuneToBuff</t>
-        </is>
-      </c>
-      <c r="B170" s="0" t="inlineStr">
-        <is>
-          <t>目标免疫buff</t>
+          <t>//buff_error base=8000 width=1000</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="0" t="inlineStr">
         <is>
-          <t>//entity_error base=9000 width=1000</t>
+          <t>BuffMaxBuffStack</t>
+        </is>
+      </c>
+      <c r="B171" s="0" t="inlineStr">
+        <is>
+          <t>buff层数已经最大</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="0" t="inlineStr">
         <is>
-          <t>EntityTransformNotFound</t>
+          <t>BuffTargetImmuneToBuff</t>
         </is>
       </c>
       <c r="B172" s="0" t="inlineStr">
         <is>
-          <t>未找到实体的Transfor组件</t>
-        </is>
-      </c>
-      <c r="C172" s="0" t="n">
-        <v>1</v>
+          <t>目标免疫buff</t>
+        </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="0" t="inlineStr">
         <is>
-          <t>//actor_action_error base=10000 width=1000</t>
+          <t>//entity_error base=9000 width=1000</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="0" t="inlineStr">
         <is>
-          <t>ActorActionStateActionCannotBePerformedWhileInTeamFollowMode</t>
+          <t>EntityTransformNotFound</t>
         </is>
       </c>
       <c r="B174" s="0" t="inlineStr">
         <is>
-          <t>正在组队跟随中</t>
-        </is>
+          <t>未找到实体的Transfor组件</t>
+        </is>
+      </c>
+      <c r="C174" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="0" t="inlineStr">
         <is>
-          <t>//mount_error base=11000 width=1000</t>
+          <t>//actor_action_error base=10000 width=1000</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="0" t="inlineStr">
         <is>
-          <t>MountNotMounted</t>
+          <t>ActorActionStateActionCannotBePerformedWhileInTeamFollowMode</t>
         </is>
       </c>
       <c r="B176" s="0" t="inlineStr">
         <is>
-          <t>当前不在坐骑上</t>
+          <t>正在组队跟随中</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="0" t="inlineStr">
         <is>
-          <t>//reward_error base=12000 width=1000</t>
+          <t>//mount_error base=11000 width=1000</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="0" t="inlineStr">
         <is>
-          <t>RewardAlreadyClaimed</t>
+          <t>MountNotMounted</t>
         </is>
       </c>
       <c r="B178" s="0" t="inlineStr">
         <is>
-          <t>该奖励已经领取过了</t>
+          <t>当前不在坐骑上</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="0" t="inlineStr">
         <is>
-          <t>//cross_server_error base=13000 width=1000</t>
+          <t>//reward_error base=12000 width=1000</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="0" t="inlineStr">
         <is>
-          <t>SceneTransferInProgress</t>
-        </is>
-      </c>
-      <c r="B180" s="0" t="inlineStr"/>
+          <t>RewardAlreadyClaimed</t>
+        </is>
+      </c>
+      <c r="B180" s="0" t="inlineStr">
+        <is>
+          <t>该奖励已经领取过了</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="0" t="inlineStr">
         <is>
-          <t>//guild_error base=14000 width=1000</t>
+          <t>//cross_server_error base=13000 width=1000</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="0" t="inlineStr">
         <is>
-          <t>GuildAlreadyInGuild</t>
-        </is>
-      </c>
-      <c r="B182" s="0" t="inlineStr">
-        <is>
-          <t>已加入公会</t>
-        </is>
-      </c>
+          <t>SceneTransferInProgress</t>
+        </is>
+      </c>
+      <c r="B182" s="0" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" s="0" t="inlineStr">
         <is>
-          <t>GuildNotFound</t>
-        </is>
-      </c>
-      <c r="B183" s="0" t="inlineStr">
-        <is>
-          <t>公会不存在</t>
+          <t>//guild_error base=14000 width=1000</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="0" t="inlineStr">
         <is>
-          <t>GuildNotInGuild</t>
+          <t>GuildAlreadyInGuild</t>
         </is>
       </c>
       <c r="B184" s="0" t="inlineStr">
         <is>
-          <t>尚未加入公会</t>
+          <t>已加入公会</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="0" t="inlineStr">
         <is>
-          <t>GuildFull</t>
+          <t>GuildNotFound</t>
         </is>
       </c>
       <c r="B185" s="0" t="inlineStr">
         <is>
-          <t>公会人数已满</t>
+          <t>公会不存在</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="0" t="inlineStr">
         <is>
-          <t>GuildLeaderCantLeave</t>
+          <t>GuildNotInGuild</t>
         </is>
       </c>
       <c r="B186" s="0" t="inlineStr">
         <is>
-          <t>会长不能退出公会</t>
+          <t>尚未加入公会</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="0" t="inlineStr">
         <is>
-          <t>GuildNotLeader</t>
+          <t>GuildFull</t>
         </is>
       </c>
       <c r="B187" s="0" t="inlineStr">
         <is>
-          <t>只有会长可以执行该操作</t>
+          <t>公会人数已满</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="0" t="inlineStr">
         <is>
-          <t>GuildNoPermission</t>
+          <t>GuildLeaderCantLeave</t>
         </is>
       </c>
       <c r="B188" s="0" t="inlineStr">
         <is>
-          <t>权限不足</t>
+          <t>会长不能退出公会</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="0" t="inlineStr">
         <is>
-          <t>GuildNotRanked</t>
+          <t>GuildNotLeader</t>
         </is>
       </c>
       <c r="B189" s="0" t="inlineStr">
         <is>
-          <t>暂未上榜</t>
+          <t>只有会长可以执行该操作</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="0" t="inlineStr">
         <is>
-          <t>GuildIdGenUnavailable</t>
+          <t>GuildNoPermission</t>
         </is>
       </c>
       <c r="B190" s="0" t="inlineStr">
         <is>
-          <t>服务繁忙，请稍后重试</t>
-        </is>
-      </c>
-      <c r="C190" s="0" t="n">
-        <v>1</v>
+          <t>权限不足</t>
+        </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="0" t="inlineStr">
         <is>
-          <t>GuildNameInvalid</t>
+          <t>GuildNotRanked</t>
         </is>
       </c>
       <c r="B191" s="0" t="inlineStr">
         <is>
-          <t>公会名称无效（1-24 个字，不能包含控制字符）</t>
+          <t>暂未上榜</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="0" t="inlineStr">
         <is>
-          <t>GuildNameTaken</t>
+          <t>GuildIdGenUnavailable</t>
         </is>
       </c>
       <c r="B192" s="0" t="inlineStr">
         <is>
-          <t>公会名称已被使用</t>
-        </is>
+          <t>服务繁忙，请稍后重试</t>
+        </is>
+      </c>
+      <c r="C192" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="0" t="inlineStr">
         <is>
-          <t>GuildAnnouncementTooLong</t>
+          <t>GuildNameInvalid</t>
         </is>
       </c>
       <c r="B193" s="0" t="inlineStr">
         <is>
-          <t>公会公告过长</t>
+          <t>公会名称无效（1-24 个字，不能包含控制字符）</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="0" t="inlineStr">
         <is>
-          <t>GuildHomeZoneUnknown</t>
+          <t>GuildNameTaken</t>
         </is>
       </c>
       <c r="B194" s="0" t="inlineStr">
         <is>
-          <t>角色归属区服未确认，暂时无法使用公会</t>
+          <t>公会名称已被使用</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="0" t="inlineStr">
         <is>
-          <t>GuildZoneMerging</t>
+          <t>GuildAnnouncementTooLong</t>
         </is>
       </c>
       <c r="B195" s="0" t="inlineStr">
         <is>
-          <t>区服合并维护中，帮会操作暂停，请稍后再试</t>
+          <t>公会公告过长</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="0" t="inlineStr">
         <is>
-          <t>GuildTargetNotMember</t>
+          <t>GuildHomeZoneUnknown</t>
         </is>
       </c>
       <c r="B196" s="0" t="inlineStr">
         <is>
-          <t>对方已不在本帮会</t>
+          <t>角色归属区服未确认，暂时无法使用公会</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="0" t="inlineStr">
         <is>
-          <t>GuildCannotTargetSelf</t>
+          <t>GuildZoneMerging</t>
         </is>
       </c>
       <c r="B197" s="0" t="inlineStr">
         <is>
-          <t>不能对自己执行此操作</t>
+          <t>区服合并维护中，帮会操作暂停，请稍后再试</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="0" t="inlineStr">
         <is>
-          <t>GuildRankTooLow</t>
+          <t>GuildTargetNotMember</t>
         </is>
       </c>
       <c r="B198" s="0" t="inlineStr">
         <is>
-          <t>帮会职位不足，无法执行此操作</t>
+          <t>对方已不在本帮会</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="0" t="inlineStr">
         <is>
-          <t>GuildOfficerLimit</t>
+          <t>GuildCannotTargetSelf</t>
         </is>
       </c>
       <c r="B199" s="0" t="inlineStr">
         <is>
-          <t>长老人数已达当前帮会等级上限</t>
+          <t>不能对自己执行此操作</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="0" t="inlineStr">
         <is>
-          <t>GuildApplicationNotFound</t>
+          <t>GuildRankTooLow</t>
         </is>
       </c>
       <c r="B200" s="0" t="inlineStr">
         <is>
-          <t>入帮申请不存在或已失效</t>
+          <t>帮会职位不足，无法执行此操作</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="0" t="inlineStr">
         <is>
-          <t>GuildApplicationLimit</t>
+          <t>GuildOfficerLimit</t>
         </is>
       </c>
       <c r="B201" s="0" t="inlineStr">
         <is>
-          <t>同时进行中的入帮申请已达上限</t>
+          <t>长老人数已达当前帮会等级上限</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="0" t="inlineStr">
         <is>
-          <t>GuildApplicationQueueFull</t>
+          <t>GuildApplicationNotFound</t>
         </is>
       </c>
       <c r="B202" s="0" t="inlineStr">
         <is>
-          <t>该帮会待审申请已满，请稍后再试</t>
+          <t>入帮申请不存在或已失效</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="0" t="inlineStr">
         <is>
-          <t>GuildBusyRetry</t>
+          <t>GuildApplicationLimit</t>
         </is>
       </c>
       <c r="B203" s="0" t="inlineStr">
         <is>
-          <t>帮会操作繁忙，请稍后重试</t>
+          <t>同时进行中的入帮申请已达上限</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="0" t="inlineStr">
         <is>
-          <t>GuildFundsInsufficient</t>
+          <t>GuildApplicationQueueFull</t>
         </is>
       </c>
       <c r="B204" s="0" t="inlineStr">
         <is>
-          <t>帮会资金不足</t>
+          <t>该帮会待审申请已满，请稍后再试</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="0" t="inlineStr">
         <is>
-          <t>GuildMaxLevel</t>
+          <t>GuildBusyRetry</t>
         </is>
       </c>
       <c r="B205" s="0" t="inlineStr">
         <is>
-          <t>帮会已达最高等级</t>
+          <t>帮会操作繁忙，请稍后重试</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="0" t="inlineStr">
         <is>
-          <t>GuildDonateLimit</t>
+          <t>GuildFundsInsufficient</t>
         </is>
       </c>
       <c r="B206" s="0" t="inlineStr">
         <is>
-          <t>今日该项捐献次数已用完</t>
+          <t>帮会资金不足</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="0" t="inlineStr">
         <is>
-          <t>GuildCurrencyInsufficient</t>
+          <t>GuildMaxLevel</t>
         </is>
       </c>
       <c r="B207" s="0" t="inlineStr">
         <is>
-          <t>货币不足，无法捐献</t>
+          <t>帮会已达最高等级</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="0" t="inlineStr">
         <is>
-          <t>GuildAssetPending</t>
+          <t>GuildDonateLimit</t>
         </is>
       </c>
       <c r="B208" s="0" t="inlineStr">
         <is>
-          <t>有未结算的帮会资产操作，请稍后再试</t>
+          <t>今日该项捐献次数已用完</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="0" t="inlineStr">
         <is>
-          <t>GuildAssetRejected</t>
+          <t>GuildCurrencyInsufficient</t>
         </is>
       </c>
       <c r="B209" s="0" t="inlineStr">
         <is>
-          <t>资产结算失败，本次操作已撤销</t>
+          <t>货币不足，无法捐献</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="0" t="inlineStr">
         <is>
-          <t>GuildShopGoodsNotFound</t>
+          <t>GuildAssetPending</t>
         </is>
       </c>
       <c r="B210" s="0" t="inlineStr">
         <is>
-          <t>兑换商品不存在</t>
+          <t>有未结算的帮会资产操作，请稍后再试</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="0" t="inlineStr">
         <is>
-          <t>GuildShopLevelTooLow</t>
+          <t>GuildAssetRejected</t>
         </is>
       </c>
       <c r="B211" s="0" t="inlineStr">
         <is>
-          <t>帮会等级不足</t>
+          <t>资产结算失败，本次操作已撤销</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="0" t="inlineStr">
         <is>
-          <t>GuildShopLimit</t>
+          <t>GuildShopGoodsNotFound</t>
         </is>
       </c>
       <c r="B212" s="0" t="inlineStr">
         <is>
-          <t>已达限购数量</t>
+          <t>兑换商品不存在</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="0" t="inlineStr">
         <is>
-          <t>GuildContributionInsufficient</t>
+          <t>GuildShopLevelTooLow</t>
         </is>
       </c>
       <c r="B213" s="0" t="inlineStr">
         <is>
-          <t>可用帮贡不足</t>
+          <t>帮会等级不足</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="0" t="inlineStr">
         <is>
-          <t>GuildActivityNotOpen</t>
+          <t>GuildShopLimit</t>
         </is>
       </c>
       <c r="B214" s="0" t="inlineStr">
         <is>
-          <t>该活动暂未开放</t>
+          <t>已达限购数量</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="0" t="inlineStr">
         <is>
-          <t>GuildActivityAlreadyClaimed</t>
+          <t>GuildContributionInsufficient</t>
         </is>
       </c>
       <c r="B215" s="0" t="inlineStr">
         <is>
-          <t>今日已参与，明日 5:00 后再来</t>
+          <t>可用帮贡不足</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="0" t="inlineStr">
         <is>
-          <t>GuildActivityThresholdNotReached</t>
+          <t>GuildActivityNotOpen</t>
         </is>
       </c>
       <c r="B216" s="0" t="inlineStr">
         <is>
-          <t>同时在线的帮会成员不足，请稍后再试</t>
+          <t>该活动暂未开放</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="0" t="inlineStr">
         <is>
-          <t>GuildTrialTeamInvalid</t>
+          <t>GuildActivityAlreadyClaimed</t>
         </is>
       </c>
       <c r="B217" s="0" t="inlineStr">
         <is>
-          <t>历练队伍名单无效，请刷新后重试</t>
+          <t>今日已参与，明日 5:00 后再来</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="0" t="inlineStr">
         <is>
-          <t>GuildActivityLevelTooLow</t>
+          <t>GuildActivityThresholdNotReached</t>
         </is>
       </c>
       <c r="B218" s="0" t="inlineStr">
         <is>
-          <t>帮会等级不足，暂时无法参与该活动</t>
+          <t>同时在线的帮会成员不足，请稍后再试</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="0" t="inlineStr">
         <is>
-          <t>GuildActivityJoinTooRecent</t>
+          <t>GuildTrialTeamInvalid</t>
         </is>
       </c>
       <c r="B219" s="0" t="inlineStr">
         <is>
-          <t>入帮时间不足，暂时无法参与帮会活动</t>
+          <t>历练队伍名单无效，请刷新后重试</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="0" t="inlineStr">
         <is>
-          <t>GuildTrialInviteExpired</t>
+          <t>GuildActivityLevelTooLow</t>
         </is>
       </c>
       <c r="B220" s="0" t="inlineStr">
         <is>
-          <t>历练邀请已失效</t>
+          <t>帮会等级不足，暂时无法参与该活动</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="0" t="inlineStr">
         <is>
-          <t>GuildTrialInviteDeclined</t>
+          <t>GuildActivityJoinTooRecent</t>
         </is>
       </c>
       <c r="B221" s="0" t="inlineStr">
         <is>
-          <t>有成员婉拒或发起人取消，本次历练已取消</t>
+          <t>入帮时间不足，暂时无法参与帮会活动</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="0" t="inlineStr">
         <is>
-          <t>GuildTrialInviteCooldown</t>
+          <t>GuildTrialInviteExpired</t>
         </is>
       </c>
       <c r="B222" s="0" t="inlineStr">
         <is>
-          <t>发起历练太频繁，请稍后再试</t>
+          <t>历练邀请已失效</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="0" t="inlineStr">
         <is>
-          <t>GuildTrialServiceBusy</t>
+          <t>GuildTrialInviteDeclined</t>
         </is>
       </c>
       <c r="B223" s="0" t="inlineStr">
         <is>
-          <t>历练服务繁忙，请稍后再试</t>
-        </is>
-      </c>
-      <c r="C223" s="0" t="n">
-        <v>1</v>
+          <t>有成员婉拒或发起人取消，本次历练已取消</t>
+        </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="0" t="inlineStr">
         <is>
-          <t>//friend_error base=15000 width=1000</t>
+          <t>GuildTrialInviteCooldown</t>
+        </is>
+      </c>
+      <c r="B224" s="0" t="inlineStr">
+        <is>
+          <t>发起历练太频繁，请稍后再试</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="0" t="inlineStr">
         <is>
-          <t>FriendCannotAddSelf</t>
+          <t>GuildTrialServiceBusy</t>
         </is>
       </c>
       <c r="B225" s="0" t="inlineStr">
         <is>
-          <t>不能添加自己为好友</t>
-        </is>
+          <t>历练服务繁忙，请稍后再试</t>
+        </is>
+      </c>
+      <c r="C225" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="0" t="inlineStr">
         <is>
-          <t>FriendAlreadyFriends</t>
-        </is>
-      </c>
-      <c r="B226" s="0" t="inlineStr">
-        <is>
-          <t>你们已经是好友了</t>
+          <t>//friend_error base=15000 width=1000</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="0" t="inlineStr">
         <is>
-          <t>FriendListFull</t>
+          <t>FriendCannotAddSelf</t>
         </is>
       </c>
       <c r="B227" s="0" t="inlineStr">
         <is>
-          <t>好友列表已满</t>
+          <t>不能添加自己为好友</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="0" t="inlineStr">
         <is>
-          <t>FriendRequestAlreadySent</t>
+          <t>FriendAlreadyFriends</t>
         </is>
       </c>
       <c r="B228" s="0" t="inlineStr">
         <is>
-          <t>已发送过好友申请</t>
+          <t>你们已经是好友了</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="0" t="inlineStr">
         <is>
-          <t>FriendTargetListFull</t>
+          <t>FriendListFull</t>
         </is>
       </c>
       <c r="B229" s="0" t="inlineStr">
         <is>
-          <t>对方好友列表已满</t>
+          <t>好友列表已满</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="0" t="inlineStr">
         <is>
-          <t>FriendNoPendingRequest</t>
+          <t>FriendRequestAlreadySent</t>
         </is>
       </c>
       <c r="B230" s="0" t="inlineStr">
         <is>
-          <t>没有待处理的好友申请</t>
+          <t>已发送过好友申请</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="0" t="inlineStr">
         <is>
-          <t>FriendTooManyPending</t>
+          <t>FriendTargetListFull</t>
         </is>
       </c>
       <c r="B231" s="0" t="inlineStr">
         <is>
-          <t>待处理的申请过多</t>
+          <t>对方好友列表已满</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="0" t="inlineStr">
         <is>
-          <t>FriendBlocked</t>
+          <t>FriendNoPendingRequest</t>
         </is>
       </c>
       <c r="B232" s="0" t="inlineStr">
         <is>
-          <t>无法添加该玩家为好友</t>
+          <t>没有待处理的好友申请</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="0" t="inlineStr">
         <is>
-          <t>FriendBlockListFull</t>
+          <t>FriendTooManyPending</t>
         </is>
       </c>
       <c r="B233" s="0" t="inlineStr">
         <is>
-          <t>黑名单已满</t>
+          <t>待处理的申请过多</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="0" t="inlineStr">
         <is>
-          <t>FriendTargetInboxFull</t>
+          <t>FriendBlocked</t>
         </is>
       </c>
       <c r="B234" s="0" t="inlineStr">
         <is>
-          <t>对方的好友申请已满</t>
+          <t>无法添加该玩家为好友</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="0" t="inlineStr">
         <is>
-          <t>//match_error base=16000 width=1000</t>
+          <t>FriendBlockListFull</t>
+        </is>
+      </c>
+      <c r="B235" s="0" t="inlineStr">
+        <is>
+          <t>黑名单已满</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="0" t="inlineStr">
         <is>
-          <t>MatchInBattle</t>
+          <t>FriendTargetInboxFull</t>
         </is>
       </c>
       <c r="B236" s="0" t="inlineStr">
         <is>
-          <t>你正在战斗中</t>
+          <t>对方的好友申请已满</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="0" t="inlineStr">
         <is>
-          <t>MatchAlreadyQueued</t>
-        </is>
-      </c>
-      <c r="B237" s="0" t="inlineStr">
-        <is>
-          <t>已在匹配队列中</t>
+          <t>//match_error base=16000 width=1000</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="0" t="inlineStr">
         <is>
-          <t>MatchModeNotOpen</t>
+          <t>MatchInBattle</t>
         </is>
       </c>
       <c r="B238" s="0" t="inlineStr">
         <is>
-          <t>该匹配模式暂未开放</t>
+          <t>你正在战斗中</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="0" t="inlineStr">
         <is>
-          <t>MatchTeamSizeNotConfigured</t>
+          <t>MatchAlreadyQueued</t>
         </is>
       </c>
       <c r="B239" s="0" t="inlineStr">
         <is>
-          <t>队伍人数未配置</t>
+          <t>已在匹配队列中</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="0" t="inlineStr">
         <is>
-          <t>MatchInternal</t>
+          <t>MatchModeNotOpen</t>
         </is>
       </c>
       <c r="B240" s="0" t="inlineStr">
         <is>
-          <t>服务繁忙，请稍后重试</t>
-        </is>
-      </c>
-      <c r="C240" s="0" t="n"/>
+          <t>该匹配模式暂未开放</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="0" t="inlineStr">
         <is>
-          <t>MatchTicketMismatch</t>
+          <t>MatchTeamSizeNotConfigured</t>
         </is>
       </c>
       <c r="B241" s="0" t="inlineStr">
         <is>
-          <t>匹配凭据不匹配</t>
+          <t>队伍人数未配置</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="0" t="inlineStr">
         <is>
-          <t>MatchCancelTooLate</t>
+          <t>MatchInternal</t>
         </is>
       </c>
       <c r="B242" s="0" t="inlineStr">
         <is>
-          <t>匹配已开始，无法取消</t>
-        </is>
-      </c>
+          <t>服务繁忙，请稍后重试</t>
+        </is>
+      </c>
+      <c r="C242" s="0" t="n"/>
     </row>
     <row r="243">
       <c r="A243" s="0" t="inlineStr">
         <is>
-          <t>MatchChallengeSelf</t>
+          <t>MatchTicketMismatch</t>
         </is>
       </c>
       <c r="B243" s="0" t="inlineStr">
         <is>
-          <t>不能挑战自己</t>
+          <t>匹配凭据不匹配</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="0" t="inlineStr">
         <is>
-          <t>MatchChallengeTargetOffline</t>
+          <t>MatchCancelTooLate</t>
         </is>
       </c>
       <c r="B244" s="0" t="inlineStr">
         <is>
-          <t>对方不在线</t>
+          <t>匹配已开始，无法取消</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="0" t="inlineStr">
         <is>
-          <t>MatchChallengeTargetBusy</t>
+          <t>MatchChallengeSelf</t>
         </is>
       </c>
       <c r="B245" s="0" t="inlineStr">
         <is>
-          <t>对方正在战斗中</t>
+          <t>不能挑战自己</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="0" t="inlineStr">
         <is>
-          <t>MatchChallengeSelfBusy</t>
+          <t>MatchChallengeTargetOffline</t>
         </is>
       </c>
       <c r="B246" s="0" t="inlineStr">
         <is>
-          <t>你正在战斗中</t>
+          <t>对方不在线</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="0" t="inlineStr">
         <is>
-          <t>MatchChallengePending</t>
+          <t>MatchChallengeTargetBusy</t>
         </is>
       </c>
       <c r="B247" s="0" t="inlineStr">
         <is>
-          <t>已有待应答的挑战</t>
+          <t>对方正在战斗中</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="0" t="inlineStr">
         <is>
-          <t>MatchChallengeExpired</t>
+          <t>MatchChallengeSelfBusy</t>
         </is>
       </c>
       <c r="B248" s="0" t="inlineStr">
         <is>
-          <t>挑战已过期</t>
+          <t>你正在战斗中</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="0" t="inlineStr">
         <is>
-          <t>MatchChallengeNotTarget</t>
+          <t>MatchChallengePending</t>
         </is>
       </c>
       <c r="B249" s="0" t="inlineStr">
         <is>
-          <t>你不是该挑战的对象</t>
+          <t>已有待应答的挑战</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="0" t="inlineStr">
         <is>
-          <t>MatchSpectateWhileQueued</t>
+          <t>MatchChallengeExpired</t>
         </is>
       </c>
       <c r="B250" s="0" t="inlineStr">
         <is>
-          <t>匹配中无法观战</t>
+          <t>挑战已过期</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="0" t="inlineStr">
         <is>
-          <t>MatchSpectateWhileInBattle</t>
+          <t>MatchChallengeNotTarget</t>
         </is>
       </c>
       <c r="B251" s="0" t="inlineStr">
         <is>
-          <t>战斗中无法观战</t>
+          <t>你不是该挑战的对象</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="0" t="inlineStr">
         <is>
-          <t>MatchAlreadyWatching</t>
+          <t>MatchSpectateWhileQueued</t>
         </is>
       </c>
       <c r="B252" s="0" t="inlineStr">
         <is>
-          <t>已在观战中</t>
+          <t>匹配中无法观战</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="0" t="inlineStr">
         <is>
-          <t>MatchNoWatchableBattle</t>
+          <t>MatchSpectateWhileInBattle</t>
         </is>
       </c>
       <c r="B253" s="0" t="inlineStr">
         <is>
-          <t>当前没有可观战的战斗</t>
+          <t>战斗中无法观战</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="0" t="inlineStr">
         <is>
-          <t>MatchBattleNotWatchable</t>
+          <t>MatchAlreadyWatching</t>
         </is>
       </c>
       <c r="B254" s="0" t="inlineStr">
         <is>
-          <t>该战斗无法观战</t>
+          <t>已在观战中</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="0" t="inlineStr">
         <is>
-          <t>MatchSpectateOffline</t>
+          <t>MatchNoWatchableBattle</t>
         </is>
       </c>
       <c r="B255" s="0" t="inlineStr">
         <is>
-          <t>观战会话已断开</t>
+          <t>当前没有可观战的战斗</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="0" t="inlineStr">
         <is>
-          <t>MatchNotInScene</t>
+          <t>MatchBattleNotWatchable</t>
         </is>
       </c>
       <c r="B256" s="0" t="inlineStr">
         <is>
-          <t>请先进入场景</t>
+          <t>该战斗无法观战</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="0" t="inlineStr">
         <is>
-          <t>// 以下号段为移植域预留，建组时把本行改成组头即可：</t>
+          <t>MatchSpectateOffline</t>
+        </is>
+      </c>
+      <c r="B257" s="0" t="inlineStr">
+        <is>
+          <t>观战会话已断开</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="0" t="inlineStr">
         <is>
-          <t>//   mail_error 17000 / chat_error 18000 / auction_error 19000</t>
+          <t>MatchNotInScene</t>
+        </is>
+      </c>
+      <c r="B258" s="0" t="inlineStr">
+        <is>
+          <t>请先进入场景</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="0" t="inlineStr">
         <is>
-          <t>//   rank_error 21000 / dialogue_error 22000 / battle_result_error 23000 / grant_error 24000</t>
-        </is>
-      </c>
-    </row>
-    <row r="260"/>
+          <t>// 以下号段为移植域预留，建组时把本行改成组头即可：</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="0" t="inlineStr">
+        <is>
+          <t>//   mail_error 17000 / chat_error 18000 / auction_error 19000</t>
+        </is>
+      </c>
+    </row>
     <row r="261">
       <c r="A261" s="0" t="inlineStr">
         <is>
-          <t>//trade_error base=20000 width=1000</t>
-        </is>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" s="0" t="inlineStr">
-        <is>
-          <t>TradeListingNotFound</t>
-        </is>
-      </c>
-      <c r="B262" s="0" t="inlineStr">
-        <is>
-          <t>商品不存在或已下架</t>
-        </is>
-      </c>
-    </row>
+          <t>//   rank_error 21000 / dialogue_error 22000 / battle_result_error 23000 / grant_error 24000</t>
+        </is>
+      </c>
+    </row>
+    <row r="262"/>
     <row r="263">
       <c r="A263" s="0" t="inlineStr">
         <is>
-          <t>TradeHomeZoneUnknown</t>
-        </is>
-      </c>
-      <c r="B263" s="0" t="inlineStr">
-        <is>
-          <t>角色归属区服未确认，暂时无法使用聚宝斋</t>
+          <t>//trade_error base=20000 width=1000</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="0" t="inlineStr">
         <is>
-          <t>TradeFavoriteLimitReached</t>
+          <t>TradeListingNotFound</t>
         </is>
       </c>
       <c r="B264" s="0" t="inlineStr">
         <is>
-          <t>收藏数量已达上限，请先取消部分收藏</t>
+          <t>商品不存在或已下架</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="0" t="inlineStr">
         <is>
+          <t>TradeHomeZoneUnknown</t>
+        </is>
+      </c>
+      <c r="B265" s="0" t="inlineStr">
+        <is>
+          <t>角色归属区服未确认，暂时无法使用聚宝斋</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="0" t="inlineStr">
+        <is>
+          <t>TradeFavoriteLimitReached</t>
+        </is>
+      </c>
+      <c r="B266" s="0" t="inlineStr">
+        <is>
+          <t>收藏数量已达上限，请先取消部分收藏</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="0" t="inlineStr">
+        <is>
           <t>TradeFeatureDisabled</t>
         </is>
       </c>
-      <c r="B265" s="0" t="inlineStr">
+      <c r="B267" s="0" t="inlineStr">
         <is>
           <t>该功能尚未开放</t>
         </is>
       </c>
     </row>
-    <row r="266"/>
-    <row r="267">
-      <c r="A267" t="inlineStr">
+    <row r="268"/>
+    <row r="269">
+      <c r="A269" s="0" t="inlineStr">
         <is>
           <t>TradeOrderNotFound</t>
         </is>
       </c>
-      <c r="B267" t="inlineStr">
+      <c r="B269" s="0" t="inlineStr">
         <is>
           <t>交易订单不存在</t>
         </is>
       </c>
     </row>
-    <row r="268">
-      <c r="A268" t="inlineStr">
+    <row r="270">
+      <c r="A270" s="0" t="inlineStr">
         <is>
           <t>TradeOrderStateConflict</t>
         </is>
       </c>
-      <c r="B268" t="inlineStr">
+      <c r="B270" s="0" t="inlineStr">
         <is>
           <t>订单状态已变化，请刷新</t>
         </is>
       </c>
     </row>
-    <row r="269">
-      <c r="A269" t="inlineStr">
+    <row r="271">
+      <c r="A271" s="0" t="inlineStr">
         <is>
           <t>TradeRequestConflict</t>
         </is>
       </c>
-      <c r="B269" t="inlineStr">
+      <c r="B271" s="0" t="inlineStr">
         <is>
           <t>交易请求编号重复但内容不同</t>
         </is>
       </c>
     </row>
-    <row r="270">
-      <c r="A270" t="inlineStr">
+    <row r="272">
+      <c r="A272" s="0" t="inlineStr">
         <is>
           <t>TradeOrderLimit</t>
         </is>
       </c>
-      <c r="B270" t="inlineStr">
+      <c r="B272" s="0" t="inlineStr">
         <is>
           <t>未完成交易数量已达上限</t>
         </is>
       </c>
     </row>
-    <row r="271">
-      <c r="A271" t="inlineStr">
+    <row r="273">
+      <c r="A273" s="0" t="inlineStr">
         <is>
           <t>TradeCannotTradeSelf</t>
         </is>
       </c>
-      <c r="B271" t="inlineStr">
+      <c r="B273" s="0" t="inlineStr">
         <is>
           <t>不能与自己交易</t>
         </is>
       </c>
     </row>
-    <row r="272">
-      <c r="A272" t="inlineStr">
+    <row r="274">
+      <c r="A274" s="0" t="inlineStr">
         <is>
           <t>TradeCounterpartyUnknown</t>
         </is>
       </c>
-      <c r="B272" t="inlineStr">
+      <c r="B274" s="0" t="inlineStr">
         <is>
           <t>交易对方不存在</t>
         </is>
       </c>
     </row>
-    <row r="273">
-      <c r="A273" t="inlineStr">
+    <row r="275">
+      <c r="A275" s="0" t="inlineStr">
         <is>
           <t>TradeInsufficientAsset</t>
         </is>
       </c>
-      <c r="B273" t="inlineStr">
+      <c r="B275" s="0" t="inlineStr">
         <is>
           <t>可交易资产不足</t>
         </is>
       </c>
     </row>
-    <row r="274">
-      <c r="A274" t="inlineStr">
+    <row r="276">
+      <c r="A276" s="0" t="inlineStr">
         <is>
           <t>TradeBidTooLow</t>
         </is>
       </c>
-      <c r="B274" t="inlineStr">
+      <c r="B276" s="0" t="inlineStr">
         <is>
           <t>出价低于当前最低价</t>
         </is>
       </c>
     </row>
-    <row r="275">
-      <c r="A275" t="inlineStr">
+    <row r="277">
+      <c r="A277" s="0" t="inlineStr">
         <is>
           <t>TradeAuctionEnded</t>
         </is>
       </c>
-      <c r="B275" t="inlineStr">
+      <c r="B277" s="0" t="inlineStr">
         <is>
           <t>拍卖已经结束</t>
         </is>
       </c>
     </row>
-    <row r="276">
-      <c r="A276" t="inlineStr">
+    <row r="278">
+      <c r="A278" s="0" t="inlineStr">
         <is>
           <t>TradeAssetDeliveryPending</t>
         </is>
       </c>
-      <c r="B276" t="inlineStr">
+      <c r="B278" s="0" t="inlineStr">
         <is>
           <t>资产正在到账，请稍后刷新</t>
-        </is>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" t="inlineStr">
-        <is>
-          <t>TradeManualReview</t>
-        </is>
-      </c>
-      <c r="B277" t="inlineStr">
-        <is>
-          <t>交易需要人工核对</t>
-        </is>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" t="inlineStr">
-        <is>
-          <t>TradeAssetNotTradable</t>
-        </is>
-      </c>
-      <c r="B278" t="inlineStr">
-        <is>
-          <t>该资产不可交易</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="0" t="inlineStr">
         <is>
-          <t>//attribute_error base=25000 width=1000</t>
+          <t>TradeManualReview</t>
+        </is>
+      </c>
+      <c r="B279" s="0" t="inlineStr">
+        <is>
+          <t>交易需要人工核对</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="0" t="inlineStr">
         <is>
-          <t>AttributePoolNotFound</t>
+          <t>TradeAssetNotTradable</t>
         </is>
       </c>
       <c r="B280" s="0" t="inlineStr">
         <is>
-          <t>属性池不存在</t>
+          <t>该资产不可交易</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="0" t="inlineStr">
         <is>
-          <t>AttributePoolLocked</t>
-        </is>
-      </c>
-      <c r="B281" s="0" t="inlineStr">
-        <is>
-          <t>该属性池尚未解锁</t>
+          <t>//attribute_error base=25000 width=1000</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="0" t="inlineStr">
         <is>
-          <t>AttributeDimensionNotFound</t>
+          <t>AttributePoolNotFound</t>
         </is>
       </c>
       <c r="B282" s="0" t="inlineStr">
         <is>
-          <t>属性维度不存在</t>
+          <t>属性池不存在</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="0" t="inlineStr">
         <is>
-          <t>AttributePointsNotEnough</t>
+          <t>AttributePoolLocked</t>
         </is>
       </c>
       <c r="B283" s="0" t="inlineStr">
         <is>
-          <t>剩余点数不足</t>
+          <t>该属性池尚未解锁</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="0" t="inlineStr">
         <is>
-          <t>AttributePointsCannotDecrease</t>
+          <t>AttributeDimensionNotFound</t>
         </is>
       </c>
       <c r="B284" s="0" t="inlineStr">
         <is>
-          <t>已分配的点数不能减少,请使用重置</t>
+          <t>属性维度不存在</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="0" t="inlineStr">
         <is>
-          <t>AttributeDimensionCapExceeded</t>
+          <t>AttributePointsNotEnough</t>
         </is>
       </c>
       <c r="B285" s="0" t="inlineStr">
         <is>
-          <t>超过单项可分配上限</t>
+          <t>剩余点数不足</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="0" t="inlineStr">
         <is>
-          <t>AttributeSchemeNotFound</t>
+          <t>AttributePointsCannotDecrease</t>
         </is>
       </c>
       <c r="B286" s="0" t="inlineStr">
         <is>
-          <t>加点方案不存在</t>
+          <t>已分配的点数不能减少,请使用重置</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="0" t="inlineStr">
         <is>
-          <t>AttributeSchemeLimitReached</t>
+          <t>AttributeDimensionCapExceeded</t>
         </is>
       </c>
       <c r="B287" s="0" t="inlineStr">
         <is>
-          <t>加点方案数量已达上限</t>
+          <t>超过单项可分配上限</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="0" t="inlineStr">
         <is>
-          <t>AttributeSchemeSwitchCooldown</t>
+          <t>AttributeSchemeNotFound</t>
         </is>
       </c>
       <c r="B288" s="0" t="inlineStr">
         <is>
-          <t>方案切换冷却中</t>
+          <t>加点方案不存在</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="0" t="inlineStr">
         <is>
-          <t>AttributeSchemeNameInvalid</t>
+          <t>AttributeSchemeLimitReached</t>
         </is>
       </c>
       <c r="B289" s="0" t="inlineStr">
         <is>
-          <t>方案名称不合法</t>
+          <t>加点方案数量已达上限</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="0" t="inlineStr">
         <is>
-          <t>AttributeSchemeAlreadyActive</t>
+          <t>AttributeSchemeSwitchCooldown</t>
         </is>
       </c>
       <c r="B290" s="0" t="inlineStr">
         <is>
-          <t>已经是当前方案</t>
+          <t>方案切换冷却中</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="0" t="inlineStr">
         <is>
-          <t>AttributeInBattle</t>
+          <t>AttributeSchemeNameInvalid</t>
         </is>
       </c>
       <c r="B291" s="0" t="inlineStr">
         <is>
-          <t>战斗中不能修改属性</t>
+          <t>方案名称不合法</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="0" t="inlineStr">
         <is>
-          <t>AttributeGoldNotEnough</t>
+          <t>AttributeSchemeAlreadyActive</t>
         </is>
       </c>
       <c r="B292" s="0" t="inlineStr">
         <is>
-          <t>金币不足</t>
+          <t>已经是当前方案</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="0" t="inlineStr">
         <is>
-          <t>AttributeNoAutoPlan</t>
+          <t>AttributeInBattle</t>
         </is>
       </c>
       <c r="B293" s="0" t="inlineStr">
         <is>
-          <t>没有可用的自动加点方案</t>
+          <t>战斗中不能修改属性</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="0" t="inlineStr">
         <is>
-          <t>AttributeNothingToChange</t>
+          <t>AttributeGoldNotEnough</t>
         </is>
       </c>
       <c r="B294" s="0" t="inlineStr">
         <is>
-          <t>属性没有变化</t>
-        </is>
-      </c>
-    </row>
-    <row r="295"/>
+          <t>金币不足</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="0" t="inlineStr">
+        <is>
+          <t>AttributeNoAutoPlan</t>
+        </is>
+      </c>
+      <c r="B295" s="0" t="inlineStr">
+        <is>
+          <t>没有可用的自动加点方案</t>
+        </is>
+      </c>
+    </row>
     <row r="296">
       <c r="A296" s="0" t="inlineStr">
         <is>
-          <t>//pet_error base=26000 width=1000</t>
-        </is>
-      </c>
-    </row>
-    <row r="297">
-      <c r="A297" s="0" t="inlineStr">
-        <is>
-          <t>PetNotFound</t>
-        </is>
-      </c>
-      <c r="B297" s="0" t="inlineStr">
-        <is>
-          <t>宝宝不存在</t>
-        </is>
-      </c>
-    </row>
+          <t>AttributeNothingToChange</t>
+        </is>
+      </c>
+      <c r="B296" s="0" t="inlineStr">
+        <is>
+          <t>属性没有变化</t>
+        </is>
+      </c>
+    </row>
+    <row r="297"/>
     <row r="298">
       <c r="A298" s="0" t="inlineStr">
         <is>
-          <t>PetTableRowMissing</t>
-        </is>
-      </c>
-      <c r="B298" s="0" t="inlineStr">
-        <is>
-          <t>宝宝数据已失效,请联系客服</t>
+          <t>//pet_error base=26000 width=1000</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="0" t="inlineStr">
         <is>
-          <t>PetSlotFull</t>
+          <t>PetNotFound</t>
         </is>
       </c>
       <c r="B299" s="0" t="inlineStr">
         <is>
-          <t>可携带的宝宝数量已达上限</t>
+          <t>宝宝不存在</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="0" t="inlineStr">
         <is>
-          <t>PetOwnerLevelNotEnough</t>
+          <t>PetTableRowMissing</t>
         </is>
       </c>
       <c r="B300" s="0" t="inlineStr">
         <is>
-          <t>主人等级不足,还不能携带这只宝宝</t>
+          <t>宝宝数据已失效,请联系客服</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="0" t="inlineStr">
         <is>
-          <t>PetAlreadyActive</t>
+          <t>PetSlotFull</t>
         </is>
       </c>
       <c r="B301" s="0" t="inlineStr">
         <is>
-          <t>这只宝宝已经在出战中</t>
+          <t>可携带的宝宝数量已达上限</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="0" t="inlineStr">
         <is>
-          <t>PetNotActive</t>
+          <t>PetOwnerLevelNotEnough</t>
         </is>
       </c>
       <c r="B302" s="0" t="inlineStr">
         <is>
-          <t>当前没有出战的宝宝</t>
+          <t>主人等级不足,还不能携带这只宝宝</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="0" t="inlineStr">
         <is>
-          <t>PetSummonCooldown</t>
+          <t>PetAlreadyActive</t>
         </is>
       </c>
       <c r="B303" s="0" t="inlineStr">
         <is>
-          <t>操作太频繁,请稍后再试</t>
+          <t>这只宝宝已经在出战中</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="0" t="inlineStr">
         <is>
-          <t>PetNameInvalid</t>
+          <t>PetNotActive</t>
         </is>
       </c>
       <c r="B304" s="0" t="inlineStr">
         <is>
-          <t>宝宝名称不合法</t>
+          <t>当前没有出战的宝宝</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="0" t="inlineStr">
         <is>
-          <t>PetInBattle</t>
+          <t>PetSummonCooldown</t>
         </is>
       </c>
       <c r="B305" s="0" t="inlineStr">
         <is>
-          <t>战斗中不能操作宝宝</t>
+          <t>操作太频繁,请稍后再试</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="0" t="inlineStr">
         <is>
-          <t>PetPointsNotEnough</t>
+          <t>PetNameInvalid</t>
         </is>
       </c>
       <c r="B306" s="0" t="inlineStr">
         <is>
-          <t>宝宝剩余点数不足</t>
+          <t>宝宝名称不合法</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="0" t="inlineStr">
         <is>
-          <t>PetPointsCannotDecrease</t>
+          <t>PetInBattle</t>
         </is>
       </c>
       <c r="B307" s="0" t="inlineStr">
         <is>
-          <t>已分配的点数不能减少,请使用洗点</t>
+          <t>战斗中不能操作宝宝</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="0" t="inlineStr">
         <is>
-          <t>PetDimensionCapExceeded</t>
+          <t>PetPointsNotEnough</t>
         </is>
       </c>
       <c r="B308" s="0" t="inlineStr">
         <is>
-          <t>超过单项可分配上限</t>
+          <t>宝宝剩余点数不足</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="0" t="inlineStr">
         <is>
-          <t>PetDimensionNotFound</t>
+          <t>PetPointsCannotDecrease</t>
         </is>
       </c>
       <c r="B309" s="0" t="inlineStr">
         <is>
-          <t>宝宝属性维度不存在</t>
+          <t>已分配的点数不能减少,请使用洗点</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="0" t="inlineStr">
         <is>
-          <t>PetGoldNotEnough</t>
+          <t>PetDimensionCapExceeded</t>
         </is>
       </c>
       <c r="B310" s="0" t="inlineStr">
         <is>
-          <t>金币不足</t>
+          <t>超过单项可分配上限</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="0" t="inlineStr">
         <is>
-          <t>PetNoAutoPlan</t>
+          <t>PetDimensionNotFound</t>
         </is>
       </c>
       <c r="B311" s="0" t="inlineStr">
         <is>
-          <t>没有可用的自动加点方案</t>
+          <t>宝宝属性维度不存在</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="0" t="inlineStr">
         <is>
-          <t>PetNothingToChange</t>
+          <t>PetGoldNotEnough</t>
         </is>
       </c>
       <c r="B312" s="0" t="inlineStr">
         <is>
-          <t>宝宝属性没有变化</t>
+          <t>金币不足</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="0" t="inlineStr">
         <is>
-          <t>PetIdGenerateFailed</t>
+          <t>PetNoAutoPlan</t>
         </is>
       </c>
       <c r="B313" s="0" t="inlineStr">
         <is>
-          <t>宝宝创建失败,请稍后再试</t>
-        </is>
-      </c>
-      <c r="C313" s="0" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="314"/>
+          <t>没有可用的自动加点方案</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="0" t="inlineStr">
+        <is>
+          <t>PetNothingToChange</t>
+        </is>
+      </c>
+      <c r="B314" s="0" t="inlineStr">
+        <is>
+          <t>宝宝属性没有变化</t>
+        </is>
+      </c>
+    </row>
     <row r="315">
       <c r="A315" s="0" t="inlineStr">
         <is>
-          <t>//asset_error base=27000 width=1000</t>
-        </is>
-      </c>
-    </row>
-    <row r="316">
-      <c r="A316" s="0" t="inlineStr">
-        <is>
-          <t>AssetCurrencyInsufficient</t>
-        </is>
-      </c>
-      <c r="B316" s="0" t="inlineStr">
-        <is>
-          <t>货币不足</t>
-        </is>
-      </c>
-    </row>
+          <t>PetIdGenerateFailed</t>
+        </is>
+      </c>
+      <c r="B315" s="0" t="inlineStr">
+        <is>
+          <t>宝宝创建失败,请稍后再试</t>
+        </is>
+      </c>
+      <c r="C315" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="316"/>
     <row r="317">
       <c r="A317" s="0" t="inlineStr">
         <is>
-          <t>AssetBagFull</t>
-        </is>
-      </c>
-      <c r="B317" s="0" t="inlineStr">
-        <is>
-          <t>背包已满，请腾出空间，之后会重试发放；超过时限可能取消</t>
+          <t>//asset_error base=27000 width=1000</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="0" t="inlineStr">
         <is>
-          <t>AssetInBattle</t>
+          <t>AssetCurrencyInsufficient</t>
         </is>
       </c>
       <c r="B318" s="0" t="inlineStr">
         <is>
-          <t>战斗中暂不结算，稍后自动重试；超过时限可能取消</t>
+          <t>货币不足</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="0" t="inlineStr">
         <is>
-          <t>AssetFrozen</t>
+          <t>AssetBagFull</t>
         </is>
       </c>
       <c r="B319" s="0" t="inlineStr">
         <is>
-          <t>角色迁移中，稍后自动重试；超过时限可能取消</t>
+          <t>背包已满，请腾出空间，之后会重试发放；超过时限可能取消</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="0" t="inlineStr">
         <is>
-          <t>AssetInvalidBundle</t>
+          <t>AssetInBattle</t>
         </is>
       </c>
       <c r="B320" s="0" t="inlineStr">
         <is>
-          <t>资产指令无效</t>
-        </is>
-      </c>
-      <c r="C320" s="0" t="n">
-        <v>1</v>
+          <t>战斗中暂不结算，稍后自动重试；超过时限可能取消</t>
+        </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="0" t="inlineStr">
         <is>
-          <t>AssetBlocked</t>
+          <t>AssetFrozen</t>
         </is>
       </c>
       <c r="B321" s="0" t="inlineStr">
         <is>
-          <t>该资产当前被禁止获取</t>
+          <t>角色迁移中，稍后自动重试；超过时限可能取消</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="0" t="inlineStr">
         <is>
-          <t>AssetPlayerNotHere</t>
+          <t>AssetInvalidBundle</t>
         </is>
       </c>
       <c r="B322" s="0" t="inlineStr">
         <is>
-          <t>角色不在线，上线后重试；超过时限可能取消</t>
-        </is>
+          <t>资产指令无效</t>
+        </is>
+      </c>
+      <c r="C322" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="0" t="inlineStr">
         <is>
-          <t>AssetPartialApplied</t>
+          <t>AssetBlocked</t>
         </is>
       </c>
       <c r="B323" s="0" t="inlineStr">
         <is>
-          <t>资产只发放了一部分，已记录，将由客服补偿</t>
-        </is>
-      </c>
-      <c r="C323" s="0" t="n">
-        <v>1</v>
+          <t>该资产当前被禁止获取</t>
+        </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="0" t="inlineStr">
         <is>
-          <t>AssetAuthFailed</t>
+          <t>AssetPlayerNotHere</t>
         </is>
       </c>
       <c r="B324" s="0" t="inlineStr">
         <is>
-          <t>资产指令校验失败</t>
-        </is>
-      </c>
-      <c r="C324" s="0" t="n">
+          <t>角色不在线，上线后重试；超过时限可能取消</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="0" t="inlineStr">
+        <is>
+          <t>AssetPartialApplied</t>
+        </is>
+      </c>
+      <c r="B325" s="0" t="inlineStr">
+        <is>
+          <t>资产只发放了一部分，已记录，将由客服补偿</t>
+        </is>
+      </c>
+      <c r="C325" s="0" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="325"/>
     <row r="326">
       <c r="A326" s="0" t="inlineStr">
         <is>
-          <t>//equip_error base=28000 width=1000</t>
-        </is>
-      </c>
-    </row>
-    <row r="327">
-      <c r="A327" s="0" t="inlineStr">
-        <is>
-          <t>EquipItemNotFound</t>
-        </is>
-      </c>
-      <c r="B327" s="0" t="inlineStr">
-        <is>
-          <t>物品不存在</t>
-        </is>
-      </c>
-    </row>
+          <t>AssetAuthFailed</t>
+        </is>
+      </c>
+      <c r="B326" s="0" t="inlineStr">
+        <is>
+          <t>资产指令校验失败</t>
+        </is>
+      </c>
+      <c r="C326" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="327"/>
     <row r="328">
       <c r="A328" s="0" t="inlineStr">
         <is>
-          <t>EquipNotEquipment</t>
-        </is>
-      </c>
-      <c r="B328" s="0" t="inlineStr">
-        <is>
-          <t>该物品不是装备</t>
+          <t>//equip_error base=28000 width=1000</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="0" t="inlineStr">
         <is>
-          <t>EquipLevelNotEnough</t>
+          <t>EquipItemNotFound</t>
         </is>
       </c>
       <c r="B329" s="0" t="inlineStr">
         <is>
-          <t>等级不足,无法装备</t>
+          <t>物品不存在</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="0" t="inlineStr">
         <is>
-          <t>EquipClassMismatch</t>
+          <t>EquipNotEquipment</t>
         </is>
       </c>
       <c r="B330" s="0" t="inlineStr">
         <is>
-          <t>职业不符,无法装备</t>
+          <t>该物品不是装备</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="0" t="inlineStr">
         <is>
-          <t>EquipNoSlot</t>
+          <t>EquipLevelNotEnough</t>
         </is>
       </c>
       <c r="B331" s="0" t="inlineStr">
         <is>
-          <t>没有可用的装备栏位</t>
+          <t>等级不足,无法装备</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="0" t="inlineStr">
         <is>
-          <t>EquipNotEquipped</t>
+          <t>EquipClassMismatch</t>
         </is>
       </c>
       <c r="B332" s="0" t="inlineStr">
         <is>
-          <t>该装备未穿戴</t>
+          <t>职业不符,无法装备</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="0" t="inlineStr">
         <is>
-          <t>EquipBagFull</t>
+          <t>EquipNoSlot</t>
         </is>
       </c>
       <c r="B333" s="0" t="inlineStr">
         <is>
-          <t>背包已满,无法卸下</t>
+          <t>没有可用的装备栏位</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="0" t="inlineStr">
         <is>
-          <t>EquipInBattle</t>
+          <t>EquipNotEquipped</t>
         </is>
       </c>
       <c r="B334" s="0" t="inlineStr">
         <is>
-          <t>战斗中无法更换装备</t>
+          <t>该装备未穿戴</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="0" t="inlineStr">
         <is>
-          <t>EquipFrozen</t>
+          <t>EquipBagFull</t>
         </is>
       </c>
       <c r="B335" s="0" t="inlineStr">
         <is>
-          <t>当前状态无法更换装备</t>
+          <t>背包已满,无法卸下</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="0" t="inlineStr">
         <is>
-          <t>EquipGrantInvalid</t>
+          <t>EquipInBattle</t>
         </is>
       </c>
       <c r="B336" s="0" t="inlineStr">
         <is>
-          <t>发放参数无效</t>
+          <t>战斗中无法更换装备</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="0" t="inlineStr">
         <is>
-          <t>EquipInternalError</t>
+          <t>EquipFrozen</t>
         </is>
       </c>
       <c r="B337" s="0" t="inlineStr">
         <is>
-          <t>装备操作失败,请稍后再试</t>
-        </is>
-      </c>
-      <c r="C337" s="0" t="n">
-        <v>1</v>
+          <t>当前状态无法更换装备</t>
+        </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="0" t="inlineStr">
         <is>
-          <t>EquipEnhanceUnavailable</t>
+          <t>EquipGrantInvalid</t>
         </is>
       </c>
       <c r="B338" s="0" t="inlineStr">
         <is>
-          <t>该装备无法强化</t>
+          <t>发放参数无效</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" s="0" t="inlineStr">
         <is>
-          <t>EquipEnhanceMaxLevel</t>
+          <t>EquipInternalError</t>
         </is>
       </c>
       <c r="B339" s="0" t="inlineStr">
         <is>
-          <t>已强化到最高等级</t>
-        </is>
+          <t>装备操作失败,请稍后再试</t>
+        </is>
+      </c>
+      <c r="C339" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" s="0" t="inlineStr">
         <is>
-          <t>EquipEnhanceMaterialNotEnough</t>
+          <t>EquipEnhanceUnavailable</t>
         </is>
       </c>
       <c r="B340" s="0" t="inlineStr">
         <is>
-          <t>强化材料不足</t>
+          <t>该装备无法强化</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" s="0" t="inlineStr">
         <is>
-          <t>EquipEnhanceGoldNotEnough</t>
+          <t>EquipEnhanceMaxLevel</t>
         </is>
       </c>
       <c r="B341" s="0" t="inlineStr">
         <is>
-          <t>金币不足,无法强化</t>
+          <t>已强化到最高等级</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="0" t="inlineStr">
         <is>
-          <t>EquipGemNotGem</t>
+          <t>EquipEnhanceMaterialNotEnough</t>
         </is>
       </c>
       <c r="B342" s="0" t="inlineStr">
         <is>
-          <t>该物品不是宝石</t>
+          <t>强化材料不足</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" s="0" t="inlineStr">
         <is>
-          <t>EquipGemNotOwned</t>
+          <t>EquipEnhanceGoldNotEnough</t>
         </is>
       </c>
       <c r="B343" s="0" t="inlineStr">
         <is>
-          <t>背包里没有这颗宝石</t>
+          <t>金币不足,无法强化</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" s="0" t="inlineStr">
         <is>
-          <t>EquipGemSocketInvalid</t>
+          <t>EquipGemNotGem</t>
         </is>
       </c>
       <c r="B344" s="0" t="inlineStr">
         <is>
-          <t>该装备没有这个宝石孔</t>
+          <t>该物品不是宝石</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" s="0" t="inlineStr">
         <is>
-          <t>EquipGemSocketOccupied</t>
+          <t>EquipGemNotOwned</t>
         </is>
       </c>
       <c r="B345" s="0" t="inlineStr">
         <is>
-          <t>该孔位已镶有宝石,请先取下</t>
+          <t>背包里没有这颗宝石</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" s="0" t="inlineStr">
         <is>
-          <t>EquipGemSocketEmpty</t>
+          <t>EquipGemSocketInvalid</t>
         </is>
       </c>
       <c r="B346" s="0" t="inlineStr">
         <is>
-          <t>该孔位没有宝石</t>
+          <t>该装备没有这个宝石孔</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" s="0" t="inlineStr">
         <is>
-          <t>EquipGemTypeMismatch</t>
+          <t>EquipGemSocketOccupied</t>
         </is>
       </c>
       <c r="B347" s="0" t="inlineStr">
         <is>
-          <t>宝石类型与孔位不符</t>
+          <t>该孔位已镶有宝石,请先取下</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" s="0" t="inlineStr">
         <is>
-          <t>EquipGemBagFull</t>
+          <t>EquipGemSocketEmpty</t>
         </is>
       </c>
       <c r="B348" s="0" t="inlineStr">
         <is>
-          <t>背包已满,无法取下宝石</t>
-        </is>
-      </c>
-    </row>
-    <row r="349"/>
+          <t>该孔位没有宝石</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="0" t="inlineStr">
+        <is>
+          <t>EquipGemTypeMismatch</t>
+        </is>
+      </c>
+      <c r="B349" s="0" t="inlineStr">
+        <is>
+          <t>宝石类型与孔位不符</t>
+        </is>
+      </c>
+    </row>
     <row r="350">
       <c r="A350" s="0" t="inlineStr">
         <is>
-          <t>//player_inbox_error base=29000 width=1000</t>
-        </is>
-      </c>
-    </row>
-    <row r="351">
-      <c r="A351" s="0" t="inlineStr">
-        <is>
-          <t>PlayerInboxDisabled</t>
-        </is>
-      </c>
-      <c r="B351" s="0" t="inlineStr">
-        <is>
-          <t>该类收件箱消息暂未开放</t>
-        </is>
-      </c>
-    </row>
+          <t>EquipGemBagFull</t>
+        </is>
+      </c>
+      <c r="B350" s="0" t="inlineStr">
+        <is>
+          <t>背包已满,无法取下宝石</t>
+        </is>
+      </c>
+    </row>
+    <row r="351"/>
     <row r="352">
       <c r="A352" s="0" t="inlineStr">
         <is>
-          <t>PlayerInboxUnknownType</t>
-        </is>
-      </c>
-      <c r="B352" s="0" t="inlineStr">
-        <is>
-          <t>未知的收件箱消息类型</t>
+          <t>//player_inbox_error base=29000 width=1000</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" s="0" t="inlineStr">
         <is>
-          <t>PlayerInboxPlayerNotFound</t>
+          <t>PlayerInboxDisabled</t>
         </is>
       </c>
       <c r="B353" s="0" t="inlineStr">
         <is>
-          <t>玩家不存在</t>
+          <t>该类收件箱消息暂未开放</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" s="0" t="inlineStr">
         <is>
-          <t>PlayerInboxPayloadInvalid</t>
+          <t>PlayerInboxUnknownType</t>
         </is>
       </c>
       <c r="B354" s="0" t="inlineStr">
         <is>
-          <t>收件箱消息内容无效</t>
+          <t>未知的收件箱消息类型</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" s="0" t="inlineStr">
         <is>
-          <t>PlayerInboxPayloadTooLarge</t>
+          <t>PlayerInboxPlayerNotFound</t>
         </is>
       </c>
       <c r="B355" s="0" t="inlineStr">
         <is>
-          <t>收件箱消息内容过大</t>
+          <t>玩家不存在</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" s="0" t="inlineStr">
         <is>
-          <t>PlayerInboxTextTooLong</t>
+          <t>PlayerInboxPayloadInvalid</t>
         </is>
       </c>
       <c r="B356" s="0" t="inlineStr">
         <is>
-          <t>操作人、理由或备注过长</t>
+          <t>收件箱消息内容无效</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" s="0" t="inlineStr">
         <is>
-          <t>PlayerInboxIssuedOutOfWindow</t>
+          <t>PlayerInboxPayloadTooLarge</t>
         </is>
       </c>
       <c r="B357" s="0" t="inlineStr">
         <is>
-          <t>签发时间超出允许范围</t>
+          <t>收件箱消息内容过大</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" s="0" t="inlineStr">
         <is>
-          <t>PlayerInboxFull</t>
+          <t>PlayerInboxTextTooLong</t>
         </is>
       </c>
       <c r="B358" s="0" t="inlineStr">
         <is>
-          <t>该玩家的收件箱已满</t>
+          <t>操作人、理由或备注过长</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" s="0" t="inlineStr">
         <is>
-          <t>PlayerInboxIdempotencyConflict</t>
+          <t>PlayerInboxIssuedOutOfWindow</t>
         </is>
       </c>
       <c r="B359" s="0" t="inlineStr">
         <is>
-          <t>请求号已被不同内容使用</t>
+          <t>签发时间超出允许范围</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="0" t="inlineStr">
         <is>
-          <t>PlayerInboxStaleOwner</t>
+          <t>PlayerInboxFull</t>
         </is>
       </c>
       <c r="B360" s="0" t="inlineStr">
         <is>
-          <t>场景归属已过期</t>
+          <t>该玩家的收件箱已满</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" s="0" t="inlineStr">
         <is>
-          <t>PlayerInboxEpochRequired</t>
+          <t>PlayerInboxIdempotencyConflict</t>
         </is>
       </c>
       <c r="B361" s="0" t="inlineStr">
         <is>
-          <t>缺少场景归属代际</t>
+          <t>请求号已被不同内容使用</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" s="0" t="inlineStr">
         <is>
-          <t>PlayerInboxEpochAhead</t>
+          <t>PlayerInboxStaleOwner</t>
         </is>
       </c>
       <c r="B362" s="0" t="inlineStr">
         <is>
-          <t>场景归属代际超前</t>
+          <t>场景归属已过期</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" s="0" t="inlineStr">
         <is>
-          <t>PlayerInboxItemNotFound</t>
+          <t>PlayerInboxEpochRequired</t>
         </is>
       </c>
       <c r="B363" s="0" t="inlineStr">
         <is>
-          <t>收件箱条目不存在</t>
+          <t>缺少场景归属代际</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" s="0" t="inlineStr">
         <is>
-          <t>PlayerInboxItemStateConflict</t>
+          <t>PlayerInboxEpochAhead</t>
         </is>
       </c>
       <c r="B364" s="0" t="inlineStr">
         <is>
-          <t>收件箱条目当前状态不允许该操作</t>
+          <t>场景归属代际超前</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" s="0" t="inlineStr">
         <is>
+          <t>PlayerInboxItemNotFound</t>
+        </is>
+      </c>
+      <c r="B365" s="0" t="inlineStr">
+        <is>
+          <t>收件箱条目不存在</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="0" t="inlineStr">
+        <is>
+          <t>PlayerInboxItemStateConflict</t>
+        </is>
+      </c>
+      <c r="B366" s="0" t="inlineStr">
+        <is>
+          <t>收件箱条目当前状态不允许该操作</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="0" t="inlineStr">
+        <is>
           <t>PlayerInboxStoreUnavailable</t>
         </is>
       </c>
-      <c r="B365" s="0" t="inlineStr">
+      <c r="B367" s="0" t="inlineStr">
         <is>
           <t>收件箱服务暂不可用,请稍后再试</t>
         </is>
       </c>
-      <c r="C365" s="0" t="n">
+      <c r="C367" s="0" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="366">
-      <c r="A366" t="inlineStr">
+    <row r="368">
+      <c r="A368" s="0" t="inlineStr">
         <is>
           <t>//mail_error base=17000 width=1000</t>
         </is>
       </c>
     </row>
-    <row r="367">
-      <c r="A367" t="inlineStr">
+    <row r="369">
+      <c r="A369" s="0" t="inlineStr">
         <is>
           <t>MailNotFound</t>
         </is>
       </c>
-      <c r="B367" t="inlineStr">
+      <c r="B369" s="0" t="inlineStr">
         <is>
           <t>邮件不存在或已删除</t>
         </is>
       </c>
     </row>
-    <row r="368">
-      <c r="A368" t="inlineStr">
+    <row r="370">
+      <c r="A370" s="0" t="inlineStr">
         <is>
           <t>MailExpired</t>
         </is>
       </c>
-      <c r="B368" t="inlineStr">
+      <c r="B370" s="0" t="inlineStr">
         <is>
           <t>邮件已过期</t>
         </is>
       </c>
     </row>
-    <row r="369">
-      <c r="A369" t="inlineStr">
+    <row r="371">
+      <c r="A371" s="0" t="inlineStr">
         <is>
           <t>MailRecipientBoxFull</t>
         </is>
       </c>
-      <c r="B369" t="inlineStr">
+      <c r="B371" s="0" t="inlineStr">
         <is>
           <t>收件人邮箱已满</t>
         </is>
       </c>
     </row>
-    <row r="370">
-      <c r="A370" t="inlineStr">
+    <row r="372">
+      <c r="A372" s="0" t="inlineStr">
         <is>
           <t>MailAttachmentInvalid</t>
         </is>
       </c>
-      <c r="B370" t="inlineStr">
+      <c r="B372" s="0" t="inlineStr">
         <is>
           <t>邮件附件不合法</t>
         </is>
       </c>
     </row>
-    <row r="371">
-      <c r="A371" t="inlineStr">
+    <row r="373">
+      <c r="A373" s="0" t="inlineStr">
         <is>
           <t>MailRequestConflict</t>
         </is>
       </c>
-      <c r="B371" t="inlineStr">
+      <c r="B373" s="0" t="inlineStr">
         <is>
           <t>发件请求编号重复但内容不同</t>
         </is>
       </c>
     </row>
-    <row r="372">
-      <c r="A372" t="inlineStr">
+    <row r="374">
+      <c r="A374" s="0" t="inlineStr">
         <is>
           <t>MailSystemMailLimit</t>
         </is>
       </c>
-      <c r="B372" t="inlineStr">
+      <c r="B374" s="0" t="inlineStr">
         <is>
           <t>有效系统邮件数量已达上限</t>
         </is>
       </c>
     </row>
-    <row r="373">
-      <c r="A373" t="inlineStr">
+    <row r="375">
+      <c r="A375" s="0" t="inlineStr">
         <is>
           <t>MailClaimPending</t>
         </is>
       </c>
-      <c r="B373" t="inlineStr">
+      <c r="B375" s="0" t="inlineStr">
         <is>
           <t>附件正在到账，请稍后刷新</t>
         </is>
       </c>
     </row>
-    <row r="374">
-      <c r="A374" t="inlineStr">
+    <row r="376">
+      <c r="A376" s="0" t="inlineStr">
         <is>
           <t>MailClaimManual</t>
         </is>
       </c>
-      <c r="B374" t="inlineStr">
+      <c r="B376" s="0" t="inlineStr">
         <is>
           <t>附件到账需人工核对</t>
         </is>
       </c>
     </row>
-    <row r="375">
-      <c r="A375" t="inlineStr">
+    <row r="377">
+      <c r="A377" s="0" t="inlineStr">
         <is>
           <t>MailAttachmentProtected</t>
         </is>
       </c>
-      <c r="B375" t="inlineStr">
+      <c r="B377" s="0" t="inlineStr">
         <is>
           <t>该邮件仍有待处理附件，暂不能删除</t>
         </is>
       </c>
     </row>
-    <row r="376"/>
-    <row r="377">
-      <c r="A377" t="inlineStr">
+    <row r="378"/>
+    <row r="379">
+      <c r="A379" s="0" t="inlineStr">
         <is>
           <t>//rank_error base=21000 width=1000</t>
         </is>
       </c>
     </row>
-    <row r="378">
-      <c r="A378" t="inlineStr">
+    <row r="380">
+      <c r="A380" s="0" t="inlineStr">
         <is>
           <t>RankBoardNotFound</t>
         </is>
       </c>
-      <c r="B378" t="inlineStr">
+      <c r="B380" s="0" t="inlineStr">
         <is>
           <t>排行榜不存在</t>
         </is>
       </c>
     </row>
-    <row r="379">
-      <c r="A379" t="inlineStr">
+    <row r="381">
+      <c r="A381" s="0" t="inlineStr">
         <is>
           <t>RankGenerationClosed</t>
         </is>
       </c>
-      <c r="B379" t="inlineStr">
+      <c r="B381" s="0" t="inlineStr">
         <is>
           <t>排行榜本期已封榜</t>
         </is>
       </c>
     </row>
-    <row r="380">
-      <c r="A380" t="inlineStr">
+    <row r="382">
+      <c r="A382" s="0" t="inlineStr">
         <is>
           <t>RankRequestConflict</t>
         </is>
       </c>
-      <c r="B380" t="inlineStr">
+      <c r="B382" s="0" t="inlineStr">
         <is>
           <t>排行榜请求编号重复但内容不同</t>
         </is>
       </c>
     </row>
-    <row r="381">
-      <c r="A381" t="inlineStr">
+    <row r="383">
+      <c r="A383" s="0" t="inlineStr">
         <is>
           <t>RankSettlementPending</t>
         </is>
       </c>
-      <c r="B381" t="inlineStr">
+      <c r="B383" s="0" t="inlineStr">
         <is>
           <t>排行榜结算处理中</t>
         </is>
       </c>
     </row>
-    <row r="382"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/tip/Tip.xlsx
+++ b/data/tip/Tip.xlsx
@@ -1020,7 +1020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C377"/>
+  <dimension ref="A1:C384"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="8" customWidth="1" style="2" min="3" max="3"/>
@@ -2728,2358 +2728,2443 @@
     <row r="168">
       <c r="A168" s="0" t="inlineStr">
         <is>
-          <t>//buff_error base=8000 width=1000</t>
+          <t>SkillNotInClass</t>
+        </is>
+      </c>
+      <c r="B168" s="0" t="inlineStr">
+        <is>
+          <t>该技能不属于当前职业</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="0" t="inlineStr">
         <is>
-          <t>BuffMaxBuffStack</t>
+          <t>SkillRankChanged</t>
         </is>
       </c>
       <c r="B169" s="0" t="inlineStr">
         <is>
-          <t>buff层数已经最大</t>
+          <t>技能等级已变化,请刷新后再试</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="0" t="inlineStr">
         <is>
-          <t>BuffTargetImmuneToBuff</t>
+          <t>SkillUpgradeCountInvalid</t>
         </is>
       </c>
       <c r="B170" s="0" t="inlineStr">
         <is>
-          <t>目标免疫buff</t>
+          <t>修习次数只能是 1 次或 10 次</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="0" t="inlineStr">
         <is>
-          <t>//entity_error base=9000 width=1000</t>
+          <t>SkillLevelNotEnough</t>
+        </is>
+      </c>
+      <c r="B171" s="0" t="inlineStr">
+        <is>
+          <t>角色等级不足,暂不能继续修习</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="0" t="inlineStr">
         <is>
-          <t>EntityTransformNotFound</t>
+          <t>SkillMaxRankReached</t>
         </is>
       </c>
       <c r="B172" s="0" t="inlineStr">
         <is>
-          <t>未找到实体的Transfor组件</t>
-        </is>
-      </c>
-      <c r="C172" s="0" t="n">
-        <v>1</v>
+          <t>技能已修至最高重</t>
+        </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="0" t="inlineStr">
         <is>
-          <t>//actor_action_error base=10000 width=1000</t>
+          <t>SkillGoldNotEnough</t>
+        </is>
+      </c>
+      <c r="B173" s="0" t="inlineStr">
+        <is>
+          <t>银两不足</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="0" t="inlineStr">
         <is>
-          <t>ActorActionStateActionCannotBePerformedWhileInTeamFollowMode</t>
+          <t>SkillUpgradeBusy</t>
         </is>
       </c>
       <c r="B174" s="0" t="inlineStr">
         <is>
-          <t>正在组队跟随中</t>
+          <t>战斗中或角色迁移中不能修习技能</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="0" t="inlineStr">
         <is>
-          <t>//mount_error base=11000 width=1000</t>
+          <t>//buff_error base=8000 width=1000</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="0" t="inlineStr">
         <is>
-          <t>MountNotMounted</t>
+          <t>BuffMaxBuffStack</t>
         </is>
       </c>
       <c r="B176" s="0" t="inlineStr">
         <is>
-          <t>当前不在坐骑上</t>
+          <t>buff层数已经最大</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="0" t="inlineStr">
         <is>
-          <t>//reward_error base=12000 width=1000</t>
+          <t>BuffTargetImmuneToBuff</t>
+        </is>
+      </c>
+      <c r="B177" s="0" t="inlineStr">
+        <is>
+          <t>目标免疫buff</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="0" t="inlineStr">
         <is>
-          <t>RewardAlreadyClaimed</t>
-        </is>
-      </c>
-      <c r="B178" s="0" t="inlineStr">
-        <is>
-          <t>该奖励已经领取过了</t>
+          <t>//entity_error base=9000 width=1000</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="0" t="inlineStr">
         <is>
-          <t>//cross_server_error base=13000 width=1000</t>
-        </is>
+          <t>EntityTransformNotFound</t>
+        </is>
+      </c>
+      <c r="B179" s="0" t="inlineStr">
+        <is>
+          <t>未找到实体的Transfor组件</t>
+        </is>
+      </c>
+      <c r="C179" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="0" t="inlineStr">
         <is>
-          <t>SceneTransferInProgress</t>
-        </is>
-      </c>
-      <c r="B180" s="0" t="inlineStr"/>
+          <t>//actor_action_error base=10000 width=1000</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="0" t="inlineStr">
         <is>
-          <t>//guild_error base=14000 width=1000</t>
+          <t>ActorActionStateActionCannotBePerformedWhileInTeamFollowMode</t>
+        </is>
+      </c>
+      <c r="B181" s="0" t="inlineStr">
+        <is>
+          <t>正在组队跟随中</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="0" t="inlineStr">
         <is>
-          <t>GuildAlreadyInGuild</t>
-        </is>
-      </c>
-      <c r="B182" s="0" t="inlineStr">
-        <is>
-          <t>已加入公会</t>
+          <t>//mount_error base=11000 width=1000</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="0" t="inlineStr">
         <is>
-          <t>GuildNotFound</t>
+          <t>MountNotMounted</t>
         </is>
       </c>
       <c r="B183" s="0" t="inlineStr">
         <is>
-          <t>公会不存在</t>
+          <t>当前不在坐骑上</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="0" t="inlineStr">
         <is>
-          <t>GuildNotInGuild</t>
-        </is>
-      </c>
-      <c r="B184" s="0" t="inlineStr">
-        <is>
-          <t>尚未加入公会</t>
+          <t>//reward_error base=12000 width=1000</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="0" t="inlineStr">
         <is>
-          <t>GuildFull</t>
+          <t>RewardAlreadyClaimed</t>
         </is>
       </c>
       <c r="B185" s="0" t="inlineStr">
         <is>
-          <t>公会人数已满</t>
+          <t>该奖励已经领取过了</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="0" t="inlineStr">
         <is>
-          <t>GuildLeaderCantLeave</t>
-        </is>
-      </c>
-      <c r="B186" s="0" t="inlineStr">
-        <is>
-          <t>会长不能退出公会</t>
+          <t>//cross_server_error base=13000 width=1000</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="0" t="inlineStr">
         <is>
-          <t>GuildNotLeader</t>
-        </is>
-      </c>
-      <c r="B187" s="0" t="inlineStr">
-        <is>
-          <t>只有会长可以执行该操作</t>
-        </is>
-      </c>
+          <t>SceneTransferInProgress</t>
+        </is>
+      </c>
+      <c r="B187" s="0" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" s="0" t="inlineStr">
         <is>
-          <t>GuildNoPermission</t>
-        </is>
-      </c>
-      <c r="B188" s="0" t="inlineStr">
-        <is>
-          <t>权限不足</t>
+          <t>//guild_error base=14000 width=1000</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="0" t="inlineStr">
         <is>
-          <t>GuildNotRanked</t>
+          <t>GuildAlreadyInGuild</t>
         </is>
       </c>
       <c r="B189" s="0" t="inlineStr">
         <is>
-          <t>暂未上榜</t>
+          <t>已加入公会</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="0" t="inlineStr">
         <is>
-          <t>GuildIdGenUnavailable</t>
+          <t>GuildNotFound</t>
         </is>
       </c>
       <c r="B190" s="0" t="inlineStr">
         <is>
-          <t>服务繁忙，请稍后重试</t>
-        </is>
-      </c>
-      <c r="C190" s="0" t="n">
-        <v>1</v>
+          <t>公会不存在</t>
+        </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="0" t="inlineStr">
         <is>
-          <t>GuildNameInvalid</t>
+          <t>GuildNotInGuild</t>
         </is>
       </c>
       <c r="B191" s="0" t="inlineStr">
         <is>
-          <t>公会名称无效（1-24 个字，不能包含控制字符）</t>
+          <t>尚未加入公会</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="0" t="inlineStr">
         <is>
-          <t>GuildNameTaken</t>
+          <t>GuildFull</t>
         </is>
       </c>
       <c r="B192" s="0" t="inlineStr">
         <is>
-          <t>公会名称已被使用</t>
+          <t>公会人数已满</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="0" t="inlineStr">
         <is>
-          <t>GuildAnnouncementTooLong</t>
+          <t>GuildLeaderCantLeave</t>
         </is>
       </c>
       <c r="B193" s="0" t="inlineStr">
         <is>
-          <t>公会公告过长</t>
+          <t>会长不能退出公会</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="0" t="inlineStr">
         <is>
-          <t>GuildHomeZoneUnknown</t>
+          <t>GuildNotLeader</t>
         </is>
       </c>
       <c r="B194" s="0" t="inlineStr">
         <is>
-          <t>角色归属区服未确认，暂时无法使用公会</t>
+          <t>只有会长可以执行该操作</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="0" t="inlineStr">
         <is>
-          <t>GuildZoneMerging</t>
+          <t>GuildNoPermission</t>
         </is>
       </c>
       <c r="B195" s="0" t="inlineStr">
         <is>
-          <t>区服合并维护中，帮会操作暂停，请稍后再试</t>
+          <t>权限不足</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="0" t="inlineStr">
         <is>
-          <t>GuildTargetNotMember</t>
+          <t>GuildNotRanked</t>
         </is>
       </c>
       <c r="B196" s="0" t="inlineStr">
         <is>
-          <t>对方已不在本帮会</t>
+          <t>暂未上榜</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="0" t="inlineStr">
         <is>
-          <t>GuildCannotTargetSelf</t>
+          <t>GuildIdGenUnavailable</t>
         </is>
       </c>
       <c r="B197" s="0" t="inlineStr">
         <is>
-          <t>不能对自己执行此操作</t>
-        </is>
+          <t>服务繁忙，请稍后重试</t>
+        </is>
+      </c>
+      <c r="C197" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="0" t="inlineStr">
         <is>
-          <t>GuildRankTooLow</t>
+          <t>GuildNameInvalid</t>
         </is>
       </c>
       <c r="B198" s="0" t="inlineStr">
         <is>
-          <t>帮会职位不足，无法执行此操作</t>
+          <t>公会名称无效（1-24 个字，不能包含控制字符）</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="0" t="inlineStr">
         <is>
-          <t>GuildOfficerLimit</t>
+          <t>GuildNameTaken</t>
         </is>
       </c>
       <c r="B199" s="0" t="inlineStr">
         <is>
-          <t>长老人数已达当前帮会等级上限</t>
+          <t>公会名称已被使用</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="0" t="inlineStr">
         <is>
-          <t>GuildApplicationNotFound</t>
+          <t>GuildAnnouncementTooLong</t>
         </is>
       </c>
       <c r="B200" s="0" t="inlineStr">
         <is>
-          <t>入帮申请不存在或已失效</t>
+          <t>公会公告过长</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="0" t="inlineStr">
         <is>
-          <t>GuildApplicationLimit</t>
+          <t>GuildHomeZoneUnknown</t>
         </is>
       </c>
       <c r="B201" s="0" t="inlineStr">
         <is>
-          <t>同时进行中的入帮申请已达上限</t>
+          <t>角色归属区服未确认，暂时无法使用公会</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="0" t="inlineStr">
         <is>
-          <t>GuildApplicationQueueFull</t>
+          <t>GuildZoneMerging</t>
         </is>
       </c>
       <c r="B202" s="0" t="inlineStr">
         <is>
-          <t>该帮会待审申请已满，请稍后再试</t>
+          <t>区服合并维护中，帮会操作暂停，请稍后再试</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="0" t="inlineStr">
         <is>
-          <t>GuildBusyRetry</t>
+          <t>GuildTargetNotMember</t>
         </is>
       </c>
       <c r="B203" s="0" t="inlineStr">
         <is>
-          <t>帮会操作繁忙，请稍后重试</t>
+          <t>对方已不在本帮会</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="0" t="inlineStr">
         <is>
-          <t>GuildFundsInsufficient</t>
+          <t>GuildCannotTargetSelf</t>
         </is>
       </c>
       <c r="B204" s="0" t="inlineStr">
         <is>
-          <t>帮会资金不足</t>
+          <t>不能对自己执行此操作</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="0" t="inlineStr">
         <is>
-          <t>GuildMaxLevel</t>
+          <t>GuildRankTooLow</t>
         </is>
       </c>
       <c r="B205" s="0" t="inlineStr">
         <is>
-          <t>帮会已达最高等级</t>
+          <t>帮会职位不足，无法执行此操作</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="0" t="inlineStr">
         <is>
-          <t>GuildDonateLimit</t>
+          <t>GuildOfficerLimit</t>
         </is>
       </c>
       <c r="B206" s="0" t="inlineStr">
         <is>
-          <t>今日该项捐献次数已用完</t>
+          <t>长老人数已达当前帮会等级上限</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="0" t="inlineStr">
         <is>
-          <t>GuildCurrencyInsufficient</t>
+          <t>GuildApplicationNotFound</t>
         </is>
       </c>
       <c r="B207" s="0" t="inlineStr">
         <is>
-          <t>货币不足，无法捐献</t>
+          <t>入帮申请不存在或已失效</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="0" t="inlineStr">
         <is>
-          <t>GuildAssetPending</t>
+          <t>GuildApplicationLimit</t>
         </is>
       </c>
       <c r="B208" s="0" t="inlineStr">
         <is>
-          <t>有未结算的帮会资产操作，请稍后再试</t>
+          <t>同时进行中的入帮申请已达上限</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="0" t="inlineStr">
         <is>
-          <t>GuildAssetRejected</t>
+          <t>GuildApplicationQueueFull</t>
         </is>
       </c>
       <c r="B209" s="0" t="inlineStr">
         <is>
-          <t>资产结算失败，本次操作已撤销</t>
+          <t>该帮会待审申请已满，请稍后再试</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="0" t="inlineStr">
         <is>
-          <t>GuildShopGoodsNotFound</t>
+          <t>GuildBusyRetry</t>
         </is>
       </c>
       <c r="B210" s="0" t="inlineStr">
         <is>
-          <t>兑换商品不存在</t>
+          <t>帮会操作繁忙，请稍后重试</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="0" t="inlineStr">
         <is>
-          <t>GuildShopLevelTooLow</t>
+          <t>GuildFundsInsufficient</t>
         </is>
       </c>
       <c r="B211" s="0" t="inlineStr">
         <is>
-          <t>帮会等级不足</t>
+          <t>帮会资金不足</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="0" t="inlineStr">
         <is>
-          <t>GuildShopLimit</t>
+          <t>GuildMaxLevel</t>
         </is>
       </c>
       <c r="B212" s="0" t="inlineStr">
         <is>
-          <t>已达限购数量</t>
+          <t>帮会已达最高等级</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="0" t="inlineStr">
         <is>
-          <t>GuildContributionInsufficient</t>
+          <t>GuildDonateLimit</t>
         </is>
       </c>
       <c r="B213" s="0" t="inlineStr">
         <is>
-          <t>可用帮贡不足</t>
+          <t>今日该项捐献次数已用完</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="0" t="inlineStr">
         <is>
-          <t>GuildActivityNotOpen</t>
+          <t>GuildCurrencyInsufficient</t>
         </is>
       </c>
       <c r="B214" s="0" t="inlineStr">
         <is>
-          <t>该活动暂未开放</t>
+          <t>货币不足，无法捐献</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="0" t="inlineStr">
         <is>
-          <t>GuildActivityAlreadyClaimed</t>
+          <t>GuildAssetPending</t>
         </is>
       </c>
       <c r="B215" s="0" t="inlineStr">
         <is>
-          <t>今日已参与，明日 5:00 后再来</t>
+          <t>有未结算的帮会资产操作，请稍后再试</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="0" t="inlineStr">
         <is>
-          <t>GuildActivityThresholdNotReached</t>
+          <t>GuildAssetRejected</t>
         </is>
       </c>
       <c r="B216" s="0" t="inlineStr">
         <is>
-          <t>同时在线的帮会成员不足，请稍后再试</t>
+          <t>资产结算失败，本次操作已撤销</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="0" t="inlineStr">
         <is>
-          <t>GuildTrialTeamInvalid</t>
+          <t>GuildShopGoodsNotFound</t>
         </is>
       </c>
       <c r="B217" s="0" t="inlineStr">
         <is>
-          <t>历练队伍名单无效，请刷新后重试</t>
+          <t>兑换商品不存在</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="0" t="inlineStr">
         <is>
-          <t>GuildActivityLevelTooLow</t>
+          <t>GuildShopLevelTooLow</t>
         </is>
       </c>
       <c r="B218" s="0" t="inlineStr">
         <is>
-          <t>帮会等级不足，暂时无法参与该活动</t>
+          <t>帮会等级不足</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="0" t="inlineStr">
         <is>
-          <t>GuildActivityJoinTooRecent</t>
+          <t>GuildShopLimit</t>
         </is>
       </c>
       <c r="B219" s="0" t="inlineStr">
         <is>
-          <t>入帮时间不足，暂时无法参与帮会活动</t>
+          <t>已达限购数量</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="0" t="inlineStr">
         <is>
-          <t>GuildTrialInviteExpired</t>
+          <t>GuildContributionInsufficient</t>
         </is>
       </c>
       <c r="B220" s="0" t="inlineStr">
         <is>
-          <t>历练邀请已失效</t>
+          <t>可用帮贡不足</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="0" t="inlineStr">
         <is>
-          <t>GuildTrialInviteDeclined</t>
+          <t>GuildActivityNotOpen</t>
         </is>
       </c>
       <c r="B221" s="0" t="inlineStr">
         <is>
-          <t>有成员婉拒或发起人取消，本次历练已取消</t>
+          <t>该活动暂未开放</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="0" t="inlineStr">
         <is>
-          <t>GuildTrialInviteCooldown</t>
+          <t>GuildActivityAlreadyClaimed</t>
         </is>
       </c>
       <c r="B222" s="0" t="inlineStr">
         <is>
-          <t>发起历练太频繁，请稍后再试</t>
+          <t>今日已参与，明日 5:00 后再来</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="0" t="inlineStr">
         <is>
-          <t>GuildTrialServiceBusy</t>
+          <t>GuildActivityThresholdNotReached</t>
         </is>
       </c>
       <c r="B223" s="0" t="inlineStr">
         <is>
-          <t>历练服务繁忙，请稍后再试</t>
-        </is>
-      </c>
-      <c r="C223" s="0" t="n">
-        <v>1</v>
+          <t>同时在线的帮会成员不足，请稍后再试</t>
+        </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="0" t="inlineStr">
         <is>
-          <t>//friend_error base=15000 width=1000</t>
+          <t>GuildTrialTeamInvalid</t>
+        </is>
+      </c>
+      <c r="B224" s="0" t="inlineStr">
+        <is>
+          <t>历练队伍名单无效，请刷新后重试</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="0" t="inlineStr">
         <is>
-          <t>FriendCannotAddSelf</t>
+          <t>GuildActivityLevelTooLow</t>
         </is>
       </c>
       <c r="B225" s="0" t="inlineStr">
         <is>
-          <t>不能添加自己为好友</t>
+          <t>帮会等级不足，暂时无法参与该活动</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="0" t="inlineStr">
         <is>
-          <t>FriendAlreadyFriends</t>
+          <t>GuildActivityJoinTooRecent</t>
         </is>
       </c>
       <c r="B226" s="0" t="inlineStr">
         <is>
-          <t>你们已经是好友了</t>
+          <t>入帮时间不足，暂时无法参与帮会活动</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="0" t="inlineStr">
         <is>
-          <t>FriendListFull</t>
+          <t>GuildTrialInviteExpired</t>
         </is>
       </c>
       <c r="B227" s="0" t="inlineStr">
         <is>
-          <t>好友列表已满</t>
+          <t>历练邀请已失效</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="0" t="inlineStr">
         <is>
-          <t>FriendRequestAlreadySent</t>
+          <t>GuildTrialInviteDeclined</t>
         </is>
       </c>
       <c r="B228" s="0" t="inlineStr">
         <is>
-          <t>已发送过好友申请</t>
+          <t>有成员婉拒或发起人取消，本次历练已取消</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="0" t="inlineStr">
         <is>
-          <t>FriendTargetListFull</t>
+          <t>GuildTrialInviteCooldown</t>
         </is>
       </c>
       <c r="B229" s="0" t="inlineStr">
         <is>
-          <t>对方好友列表已满</t>
+          <t>发起历练太频繁，请稍后再试</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="0" t="inlineStr">
         <is>
-          <t>FriendNoPendingRequest</t>
+          <t>GuildTrialServiceBusy</t>
         </is>
       </c>
       <c r="B230" s="0" t="inlineStr">
         <is>
-          <t>没有待处理的好友申请</t>
-        </is>
+          <t>历练服务繁忙，请稍后再试</t>
+        </is>
+      </c>
+      <c r="C230" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="0" t="inlineStr">
         <is>
-          <t>FriendTooManyPending</t>
-        </is>
-      </c>
-      <c r="B231" s="0" t="inlineStr">
-        <is>
-          <t>待处理的申请过多</t>
+          <t>//friend_error base=15000 width=1000</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="0" t="inlineStr">
         <is>
-          <t>FriendBlocked</t>
+          <t>FriendCannotAddSelf</t>
         </is>
       </c>
       <c r="B232" s="0" t="inlineStr">
         <is>
-          <t>无法添加该玩家为好友</t>
+          <t>不能添加自己为好友</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="0" t="inlineStr">
         <is>
-          <t>FriendBlockListFull</t>
+          <t>FriendAlreadyFriends</t>
         </is>
       </c>
       <c r="B233" s="0" t="inlineStr">
         <is>
-          <t>黑名单已满</t>
+          <t>你们已经是好友了</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="0" t="inlineStr">
         <is>
-          <t>FriendTargetInboxFull</t>
+          <t>FriendListFull</t>
         </is>
       </c>
       <c r="B234" s="0" t="inlineStr">
         <is>
-          <t>对方的好友申请已满</t>
+          <t>好友列表已满</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="0" t="inlineStr">
         <is>
-          <t>//match_error base=16000 width=1000</t>
+          <t>FriendRequestAlreadySent</t>
+        </is>
+      </c>
+      <c r="B235" s="0" t="inlineStr">
+        <is>
+          <t>已发送过好友申请</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="0" t="inlineStr">
         <is>
-          <t>MatchInBattle</t>
+          <t>FriendTargetListFull</t>
         </is>
       </c>
       <c r="B236" s="0" t="inlineStr">
         <is>
-          <t>你正在战斗中</t>
+          <t>对方好友列表已满</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="0" t="inlineStr">
         <is>
-          <t>MatchAlreadyQueued</t>
+          <t>FriendNoPendingRequest</t>
         </is>
       </c>
       <c r="B237" s="0" t="inlineStr">
         <is>
-          <t>已在匹配队列中</t>
+          <t>没有待处理的好友申请</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="0" t="inlineStr">
         <is>
-          <t>MatchModeNotOpen</t>
+          <t>FriendTooManyPending</t>
         </is>
       </c>
       <c r="B238" s="0" t="inlineStr">
         <is>
-          <t>该匹配模式暂未开放</t>
+          <t>待处理的申请过多</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="0" t="inlineStr">
         <is>
-          <t>MatchTeamSizeNotConfigured</t>
+          <t>FriendBlocked</t>
         </is>
       </c>
       <c r="B239" s="0" t="inlineStr">
         <is>
-          <t>队伍人数未配置</t>
+          <t>无法添加该玩家为好友</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="0" t="inlineStr">
         <is>
-          <t>MatchInternal</t>
+          <t>FriendBlockListFull</t>
         </is>
       </c>
       <c r="B240" s="0" t="inlineStr">
         <is>
-          <t>服务繁忙，请稍后重试</t>
-        </is>
-      </c>
-      <c r="C240" s="0" t="n"/>
+          <t>黑名单已满</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="0" t="inlineStr">
         <is>
-          <t>MatchTicketMismatch</t>
+          <t>FriendTargetInboxFull</t>
         </is>
       </c>
       <c r="B241" s="0" t="inlineStr">
         <is>
-          <t>匹配凭据不匹配</t>
+          <t>对方的好友申请已满</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="0" t="inlineStr">
         <is>
-          <t>MatchCancelTooLate</t>
-        </is>
-      </c>
-      <c r="B242" s="0" t="inlineStr">
-        <is>
-          <t>匹配已开始，无法取消</t>
+          <t>//match_error base=16000 width=1000</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="0" t="inlineStr">
         <is>
-          <t>MatchChallengeSelf</t>
+          <t>MatchInBattle</t>
         </is>
       </c>
       <c r="B243" s="0" t="inlineStr">
         <is>
-          <t>不能挑战自己</t>
+          <t>你正在战斗中</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="0" t="inlineStr">
         <is>
-          <t>MatchChallengeTargetOffline</t>
+          <t>MatchAlreadyQueued</t>
         </is>
       </c>
       <c r="B244" s="0" t="inlineStr">
         <is>
-          <t>对方不在线</t>
+          <t>已在匹配队列中</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="0" t="inlineStr">
         <is>
-          <t>MatchChallengeTargetBusy</t>
+          <t>MatchModeNotOpen</t>
         </is>
       </c>
       <c r="B245" s="0" t="inlineStr">
         <is>
-          <t>对方正在战斗中</t>
+          <t>该匹配模式暂未开放</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="0" t="inlineStr">
         <is>
-          <t>MatchChallengeSelfBusy</t>
+          <t>MatchTeamSizeNotConfigured</t>
         </is>
       </c>
       <c r="B246" s="0" t="inlineStr">
         <is>
-          <t>你正在战斗中</t>
+          <t>队伍人数未配置</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="0" t="inlineStr">
         <is>
-          <t>MatchChallengePending</t>
+          <t>MatchInternal</t>
         </is>
       </c>
       <c r="B247" s="0" t="inlineStr">
         <is>
-          <t>已有待应答的挑战</t>
-        </is>
-      </c>
+          <t>服务繁忙，请稍后重试</t>
+        </is>
+      </c>
+      <c r="C247" s="0" t="n"/>
     </row>
     <row r="248">
       <c r="A248" s="0" t="inlineStr">
         <is>
-          <t>MatchChallengeExpired</t>
+          <t>MatchTicketMismatch</t>
         </is>
       </c>
       <c r="B248" s="0" t="inlineStr">
         <is>
-          <t>挑战已过期</t>
+          <t>匹配凭据不匹配</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="0" t="inlineStr">
         <is>
-          <t>MatchChallengeNotTarget</t>
+          <t>MatchCancelTooLate</t>
         </is>
       </c>
       <c r="B249" s="0" t="inlineStr">
         <is>
-          <t>你不是该挑战的对象</t>
+          <t>匹配已开始，无法取消</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="0" t="inlineStr">
         <is>
-          <t>MatchSpectateWhileQueued</t>
+          <t>MatchChallengeSelf</t>
         </is>
       </c>
       <c r="B250" s="0" t="inlineStr">
         <is>
-          <t>匹配中无法观战</t>
+          <t>不能挑战自己</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="0" t="inlineStr">
         <is>
-          <t>MatchSpectateWhileInBattle</t>
+          <t>MatchChallengeTargetOffline</t>
         </is>
       </c>
       <c r="B251" s="0" t="inlineStr">
         <is>
-          <t>战斗中无法观战</t>
+          <t>对方不在线</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="0" t="inlineStr">
         <is>
-          <t>MatchAlreadyWatching</t>
+          <t>MatchChallengeTargetBusy</t>
         </is>
       </c>
       <c r="B252" s="0" t="inlineStr">
         <is>
-          <t>已在观战中</t>
+          <t>对方正在战斗中</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="0" t="inlineStr">
         <is>
-          <t>MatchNoWatchableBattle</t>
+          <t>MatchChallengeSelfBusy</t>
         </is>
       </c>
       <c r="B253" s="0" t="inlineStr">
         <is>
-          <t>当前没有可观战的战斗</t>
+          <t>你正在战斗中</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="0" t="inlineStr">
         <is>
-          <t>MatchBattleNotWatchable</t>
+          <t>MatchChallengePending</t>
         </is>
       </c>
       <c r="B254" s="0" t="inlineStr">
         <is>
-          <t>该战斗无法观战</t>
+          <t>已有待应答的挑战</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="0" t="inlineStr">
         <is>
-          <t>MatchSpectateOffline</t>
+          <t>MatchChallengeExpired</t>
         </is>
       </c>
       <c r="B255" s="0" t="inlineStr">
         <is>
-          <t>观战会话已断开</t>
+          <t>挑战已过期</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="0" t="inlineStr">
         <is>
-          <t>MatchNotInScene</t>
+          <t>MatchChallengeNotTarget</t>
         </is>
       </c>
       <c r="B256" s="0" t="inlineStr">
         <is>
-          <t>请先进入场景</t>
+          <t>你不是该挑战的对象</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="0" t="inlineStr">
         <is>
-          <t>// 以下号段为移植域预留，建组时把本行改成组头即可：</t>
+          <t>MatchSpectateWhileQueued</t>
+        </is>
+      </c>
+      <c r="B257" s="0" t="inlineStr">
+        <is>
+          <t>匹配中无法观战</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="0" t="inlineStr">
         <is>
-          <t>//   chat_error 18000 / auction_error 19000(mail_error 17000 已建组,在表尾)</t>
+          <t>MatchSpectateWhileInBattle</t>
+        </is>
+      </c>
+      <c r="B258" s="0" t="inlineStr">
+        <is>
+          <t>战斗中无法观战</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="0" t="inlineStr">
         <is>
-          <t>//   rank_error 21000 / dialogue_error 22000 / battle_result_error 23000 / grant_error 24000</t>
-        </is>
-      </c>
-    </row>
-    <row r="260"/>
+          <t>MatchAlreadyWatching</t>
+        </is>
+      </c>
+      <c r="B259" s="0" t="inlineStr">
+        <is>
+          <t>已在观战中</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="0" t="inlineStr">
+        <is>
+          <t>MatchNoWatchableBattle</t>
+        </is>
+      </c>
+      <c r="B260" s="0" t="inlineStr">
+        <is>
+          <t>当前没有可观战的战斗</t>
+        </is>
+      </c>
+    </row>
     <row r="261">
       <c r="A261" s="0" t="inlineStr">
         <is>
-          <t>//trade_error base=20000 width=1000</t>
+          <t>MatchBattleNotWatchable</t>
+        </is>
+      </c>
+      <c r="B261" s="0" t="inlineStr">
+        <is>
+          <t>该战斗无法观战</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="0" t="inlineStr">
         <is>
-          <t>TradeListingNotFound</t>
+          <t>MatchSpectateOffline</t>
         </is>
       </c>
       <c r="B262" s="0" t="inlineStr">
         <is>
-          <t>商品不存在或已下架</t>
+          <t>观战会话已断开</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="0" t="inlineStr">
         <is>
-          <t>TradeHomeZoneUnknown</t>
+          <t>MatchNotInScene</t>
         </is>
       </c>
       <c r="B263" s="0" t="inlineStr">
         <is>
-          <t>角色归属区服未确认，暂时无法使用聚宝斋</t>
+          <t>请先进入场景</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="0" t="inlineStr">
         <is>
-          <t>TradeFavoriteLimitReached</t>
-        </is>
-      </c>
-      <c r="B264" s="0" t="inlineStr">
-        <is>
-          <t>收藏数量已达上限，请先取消部分收藏</t>
+          <t>// 以下号段为移植域预留，建组时把本行改成组头即可：</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="0" t="inlineStr">
         <is>
-          <t>TradeFeatureDisabled</t>
-        </is>
-      </c>
-      <c r="B265" s="0" t="inlineStr">
-        <is>
-          <t>该功能尚未开放</t>
-        </is>
-      </c>
-    </row>
-    <row r="266"/>
-    <row r="267">
-      <c r="A267" s="0" t="inlineStr">
-        <is>
-          <t>//attribute_error base=25000 width=1000</t>
-        </is>
-      </c>
-    </row>
+          <t>//   chat_error 18000 / auction_error 19000(mail_error 17000 已建组,在表尾)</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="0" t="inlineStr">
+        <is>
+          <t>//   rank_error 21000 / dialogue_error 22000 / battle_result_error 23000 / grant_error 24000</t>
+        </is>
+      </c>
+    </row>
+    <row r="267"/>
     <row r="268">
       <c r="A268" s="0" t="inlineStr">
         <is>
-          <t>AttributePoolNotFound</t>
-        </is>
-      </c>
-      <c r="B268" s="0" t="inlineStr">
-        <is>
-          <t>属性池不存在</t>
+          <t>//trade_error base=20000 width=1000</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="0" t="inlineStr">
         <is>
-          <t>AttributePoolLocked</t>
+          <t>TradeListingNotFound</t>
         </is>
       </c>
       <c r="B269" s="0" t="inlineStr">
         <is>
-          <t>该属性池尚未解锁</t>
+          <t>商品不存在或已下架</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="0" t="inlineStr">
         <is>
-          <t>AttributeDimensionNotFound</t>
+          <t>TradeHomeZoneUnknown</t>
         </is>
       </c>
       <c r="B270" s="0" t="inlineStr">
         <is>
-          <t>属性维度不存在</t>
+          <t>角色归属区服未确认，暂时无法使用聚宝斋</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="0" t="inlineStr">
         <is>
-          <t>AttributePointsNotEnough</t>
+          <t>TradeFavoriteLimitReached</t>
         </is>
       </c>
       <c r="B271" s="0" t="inlineStr">
         <is>
-          <t>剩余点数不足</t>
+          <t>收藏数量已达上限，请先取消部分收藏</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="0" t="inlineStr">
         <is>
-          <t>AttributePointsCannotDecrease</t>
+          <t>TradeFeatureDisabled</t>
         </is>
       </c>
       <c r="B272" s="0" t="inlineStr">
         <is>
-          <t>已分配的点数不能减少,请使用重置</t>
-        </is>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" s="0" t="inlineStr">
-        <is>
-          <t>AttributeDimensionCapExceeded</t>
-        </is>
-      </c>
-      <c r="B273" s="0" t="inlineStr">
-        <is>
-          <t>超过单项可分配上限</t>
-        </is>
-      </c>
-    </row>
+          <t>该功能尚未开放</t>
+        </is>
+      </c>
+    </row>
+    <row r="273"/>
     <row r="274">
       <c r="A274" s="0" t="inlineStr">
         <is>
-          <t>AttributeSchemeNotFound</t>
-        </is>
-      </c>
-      <c r="B274" s="0" t="inlineStr">
-        <is>
-          <t>加点方案不存在</t>
+          <t>//attribute_error base=25000 width=1000</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="0" t="inlineStr">
         <is>
-          <t>AttributeSchemeLimitReached</t>
+          <t>AttributePoolNotFound</t>
         </is>
       </c>
       <c r="B275" s="0" t="inlineStr">
         <is>
-          <t>加点方案数量已达上限</t>
+          <t>属性池不存在</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="0" t="inlineStr">
         <is>
-          <t>AttributeSchemeSwitchCooldown</t>
+          <t>AttributePoolLocked</t>
         </is>
       </c>
       <c r="B276" s="0" t="inlineStr">
         <is>
-          <t>方案切换冷却中</t>
+          <t>该属性池尚未解锁</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="0" t="inlineStr">
         <is>
-          <t>AttributeSchemeNameInvalid</t>
+          <t>AttributeDimensionNotFound</t>
         </is>
       </c>
       <c r="B277" s="0" t="inlineStr">
         <is>
-          <t>方案名称不合法</t>
+          <t>属性维度不存在</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="0" t="inlineStr">
         <is>
-          <t>AttributeSchemeAlreadyActive</t>
+          <t>AttributePointsNotEnough</t>
         </is>
       </c>
       <c r="B278" s="0" t="inlineStr">
         <is>
-          <t>已经是当前方案</t>
+          <t>剩余点数不足</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="0" t="inlineStr">
         <is>
-          <t>AttributeInBattle</t>
+          <t>AttributePointsCannotDecrease</t>
         </is>
       </c>
       <c r="B279" s="0" t="inlineStr">
         <is>
-          <t>战斗中不能修改属性</t>
+          <t>已分配的点数不能减少,请使用重置</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="0" t="inlineStr">
         <is>
-          <t>AttributeGoldNotEnough</t>
+          <t>AttributeDimensionCapExceeded</t>
         </is>
       </c>
       <c r="B280" s="0" t="inlineStr">
         <is>
-          <t>金币不足</t>
+          <t>超过单项可分配上限</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="0" t="inlineStr">
         <is>
-          <t>AttributeNoAutoPlan</t>
+          <t>AttributeSchemeNotFound</t>
         </is>
       </c>
       <c r="B281" s="0" t="inlineStr">
         <is>
-          <t>没有可用的自动加点方案</t>
+          <t>加点方案不存在</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="0" t="inlineStr">
         <is>
-          <t>AttributeNothingToChange</t>
+          <t>AttributeSchemeLimitReached</t>
         </is>
       </c>
       <c r="B282" s="0" t="inlineStr">
         <is>
-          <t>属性没有变化</t>
-        </is>
-      </c>
-    </row>
-    <row r="283"/>
+          <t>加点方案数量已达上限</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="0" t="inlineStr">
+        <is>
+          <t>AttributeSchemeSwitchCooldown</t>
+        </is>
+      </c>
+      <c r="B283" s="0" t="inlineStr">
+        <is>
+          <t>方案切换冷却中</t>
+        </is>
+      </c>
+    </row>
     <row r="284">
       <c r="A284" s="0" t="inlineStr">
         <is>
-          <t>//pet_error base=26000 width=1000</t>
+          <t>AttributeSchemeNameInvalid</t>
+        </is>
+      </c>
+      <c r="B284" s="0" t="inlineStr">
+        <is>
+          <t>方案名称不合法</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="0" t="inlineStr">
         <is>
-          <t>PetNotFound</t>
+          <t>AttributeSchemeAlreadyActive</t>
         </is>
       </c>
       <c r="B285" s="0" t="inlineStr">
         <is>
-          <t>宝宝不存在</t>
+          <t>已经是当前方案</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="0" t="inlineStr">
         <is>
-          <t>PetTableRowMissing</t>
+          <t>AttributeInBattle</t>
         </is>
       </c>
       <c r="B286" s="0" t="inlineStr">
         <is>
-          <t>宝宝数据已失效,请联系客服</t>
+          <t>战斗中不能修改属性</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="0" t="inlineStr">
         <is>
-          <t>PetSlotFull</t>
+          <t>AttributeGoldNotEnough</t>
         </is>
       </c>
       <c r="B287" s="0" t="inlineStr">
         <is>
-          <t>可携带的宝宝数量已达上限</t>
+          <t>金币不足</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="0" t="inlineStr">
         <is>
-          <t>PetOwnerLevelNotEnough</t>
+          <t>AttributeNoAutoPlan</t>
         </is>
       </c>
       <c r="B288" s="0" t="inlineStr">
         <is>
-          <t>主人等级不足,还不能携带这只宝宝</t>
+          <t>没有可用的自动加点方案</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="0" t="inlineStr">
         <is>
-          <t>PetAlreadyActive</t>
+          <t>AttributeNothingToChange</t>
         </is>
       </c>
       <c r="B289" s="0" t="inlineStr">
         <is>
-          <t>这只宝宝已经在出战中</t>
-        </is>
-      </c>
-    </row>
-    <row r="290">
-      <c r="A290" s="0" t="inlineStr">
-        <is>
-          <t>PetNotActive</t>
-        </is>
-      </c>
-      <c r="B290" s="0" t="inlineStr">
-        <is>
-          <t>当前没有出战的宝宝</t>
-        </is>
-      </c>
-    </row>
+          <t>属性没有变化</t>
+        </is>
+      </c>
+    </row>
+    <row r="290"/>
     <row r="291">
       <c r="A291" s="0" t="inlineStr">
         <is>
-          <t>PetSummonCooldown</t>
-        </is>
-      </c>
-      <c r="B291" s="0" t="inlineStr">
-        <is>
-          <t>操作太频繁,请稍后再试</t>
+          <t>//pet_error base=26000 width=1000</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="0" t="inlineStr">
         <is>
-          <t>PetNameInvalid</t>
+          <t>PetNotFound</t>
         </is>
       </c>
       <c r="B292" s="0" t="inlineStr">
         <is>
-          <t>宝宝名称不合法</t>
+          <t>宝宝不存在</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="0" t="inlineStr">
         <is>
-          <t>PetInBattle</t>
+          <t>PetTableRowMissing</t>
         </is>
       </c>
       <c r="B293" s="0" t="inlineStr">
         <is>
-          <t>战斗中不能操作宝宝</t>
+          <t>宝宝数据已失效,请联系客服</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="0" t="inlineStr">
         <is>
-          <t>PetPointsNotEnough</t>
+          <t>PetSlotFull</t>
         </is>
       </c>
       <c r="B294" s="0" t="inlineStr">
         <is>
-          <t>宝宝剩余点数不足</t>
+          <t>可携带的宝宝数量已达上限</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="0" t="inlineStr">
         <is>
-          <t>PetPointsCannotDecrease</t>
+          <t>PetOwnerLevelNotEnough</t>
         </is>
       </c>
       <c r="B295" s="0" t="inlineStr">
         <is>
-          <t>已分配的点数不能减少,请使用洗点</t>
+          <t>主人等级不足,还不能携带这只宝宝</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="0" t="inlineStr">
         <is>
-          <t>PetDimensionCapExceeded</t>
+          <t>PetAlreadyActive</t>
         </is>
       </c>
       <c r="B296" s="0" t="inlineStr">
         <is>
-          <t>超过单项可分配上限</t>
+          <t>这只宝宝已经在出战中</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="0" t="inlineStr">
         <is>
-          <t>PetDimensionNotFound</t>
+          <t>PetNotActive</t>
         </is>
       </c>
       <c r="B297" s="0" t="inlineStr">
         <is>
-          <t>宝宝属性维度不存在</t>
+          <t>当前没有出战的宝宝</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="0" t="inlineStr">
         <is>
-          <t>PetGoldNotEnough</t>
+          <t>PetSummonCooldown</t>
         </is>
       </c>
       <c r="B298" s="0" t="inlineStr">
         <is>
-          <t>金币不足</t>
+          <t>操作太频繁,请稍后再试</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="0" t="inlineStr">
         <is>
-          <t>PetNoAutoPlan</t>
+          <t>PetNameInvalid</t>
         </is>
       </c>
       <c r="B299" s="0" t="inlineStr">
         <is>
-          <t>没有可用的自动加点方案</t>
+          <t>宝宝名称不合法</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="0" t="inlineStr">
         <is>
-          <t>PetNothingToChange</t>
+          <t>PetInBattle</t>
         </is>
       </c>
       <c r="B300" s="0" t="inlineStr">
         <is>
-          <t>宝宝属性没有变化</t>
+          <t>战斗中不能操作宝宝</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="0" t="inlineStr">
         <is>
-          <t>PetIdGenerateFailed</t>
+          <t>PetPointsNotEnough</t>
         </is>
       </c>
       <c r="B301" s="0" t="inlineStr">
         <is>
-          <t>宝宝创建失败,请稍后再试</t>
-        </is>
-      </c>
-      <c r="C301" s="0" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="302"/>
+          <t>宝宝剩余点数不足</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="0" t="inlineStr">
+        <is>
+          <t>PetPointsCannotDecrease</t>
+        </is>
+      </c>
+      <c r="B302" s="0" t="inlineStr">
+        <is>
+          <t>已分配的点数不能减少,请使用洗点</t>
+        </is>
+      </c>
+    </row>
     <row r="303">
       <c r="A303" s="0" t="inlineStr">
         <is>
-          <t>//asset_error base=27000 width=1000</t>
+          <t>PetDimensionCapExceeded</t>
+        </is>
+      </c>
+      <c r="B303" s="0" t="inlineStr">
+        <is>
+          <t>超过单项可分配上限</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="0" t="inlineStr">
         <is>
-          <t>AssetCurrencyInsufficient</t>
+          <t>PetDimensionNotFound</t>
         </is>
       </c>
       <c r="B304" s="0" t="inlineStr">
         <is>
-          <t>货币不足</t>
+          <t>宝宝属性维度不存在</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="0" t="inlineStr">
         <is>
-          <t>AssetBagFull</t>
+          <t>PetGoldNotEnough</t>
         </is>
       </c>
       <c r="B305" s="0" t="inlineStr">
         <is>
-          <t>背包已满，请腾出空间，之后会重试发放；超过时限可能取消</t>
+          <t>金币不足</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="0" t="inlineStr">
         <is>
-          <t>AssetInBattle</t>
+          <t>PetNoAutoPlan</t>
         </is>
       </c>
       <c r="B306" s="0" t="inlineStr">
         <is>
-          <t>战斗中暂不结算，稍后自动重试；超过时限可能取消</t>
+          <t>没有可用的自动加点方案</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="0" t="inlineStr">
         <is>
-          <t>AssetFrozen</t>
+          <t>PetNothingToChange</t>
         </is>
       </c>
       <c r="B307" s="0" t="inlineStr">
         <is>
-          <t>角色迁移中，稍后自动重试；超过时限可能取消</t>
+          <t>宝宝属性没有变化</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="0" t="inlineStr">
         <is>
-          <t>AssetInvalidBundle</t>
+          <t>PetIdGenerateFailed</t>
         </is>
       </c>
       <c r="B308" s="0" t="inlineStr">
         <is>
-          <t>资产指令无效</t>
+          <t>宝宝创建失败,请稍后再试</t>
         </is>
       </c>
       <c r="C308" s="0" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="309">
-      <c r="A309" s="0" t="inlineStr">
-        <is>
-          <t>AssetBlocked</t>
-        </is>
-      </c>
-      <c r="B309" s="0" t="inlineStr">
-        <is>
-          <t>该资产当前被禁止获取</t>
-        </is>
-      </c>
-    </row>
+    <row r="309"/>
     <row r="310">
       <c r="A310" s="0" t="inlineStr">
         <is>
-          <t>AssetPlayerNotHere</t>
-        </is>
-      </c>
-      <c r="B310" s="0" t="inlineStr">
-        <is>
-          <t>角色不在线，上线后重试；超过时限可能取消</t>
+          <t>//asset_error base=27000 width=1000</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="0" t="inlineStr">
         <is>
-          <t>AssetPartialApplied</t>
+          <t>AssetCurrencyInsufficient</t>
         </is>
       </c>
       <c r="B311" s="0" t="inlineStr">
         <is>
-          <t>资产只发放了一部分，已记录，将由客服补偿</t>
-        </is>
-      </c>
-      <c r="C311" s="0" t="n">
-        <v>1</v>
+          <t>货币不足</t>
+        </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="0" t="inlineStr">
         <is>
-          <t>AssetAuthFailed</t>
+          <t>AssetBagFull</t>
         </is>
       </c>
       <c r="B312" s="0" t="inlineStr">
         <is>
-          <t>资产指令校验失败</t>
-        </is>
-      </c>
-      <c r="C312" s="0" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="313"/>
+          <t>背包已满，请腾出空间，之后会重试发放；超过时限可能取消</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="0" t="inlineStr">
+        <is>
+          <t>AssetInBattle</t>
+        </is>
+      </c>
+      <c r="B313" s="0" t="inlineStr">
+        <is>
+          <t>战斗中暂不结算，稍后自动重试；超过时限可能取消</t>
+        </is>
+      </c>
+    </row>
     <row r="314">
       <c r="A314" s="0" t="inlineStr">
         <is>
-          <t>//equip_error base=28000 width=1000</t>
+          <t>AssetFrozen</t>
+        </is>
+      </c>
+      <c r="B314" s="0" t="inlineStr">
+        <is>
+          <t>角色迁移中，稍后自动重试；超过时限可能取消</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="0" t="inlineStr">
         <is>
-          <t>EquipItemNotFound</t>
+          <t>AssetInvalidBundle</t>
         </is>
       </c>
       <c r="B315" s="0" t="inlineStr">
         <is>
-          <t>物品不存在</t>
-        </is>
+          <t>资产指令无效</t>
+        </is>
+      </c>
+      <c r="C315" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="0" t="inlineStr">
         <is>
-          <t>EquipNotEquipment</t>
+          <t>AssetBlocked</t>
         </is>
       </c>
       <c r="B316" s="0" t="inlineStr">
         <is>
-          <t>该物品不是装备</t>
+          <t>该资产当前被禁止获取</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="0" t="inlineStr">
         <is>
-          <t>EquipLevelNotEnough</t>
+          <t>AssetPlayerNotHere</t>
         </is>
       </c>
       <c r="B317" s="0" t="inlineStr">
         <is>
-          <t>等级不足,无法装备</t>
+          <t>角色不在线，上线后重试；超过时限可能取消</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="0" t="inlineStr">
         <is>
-          <t>EquipClassMismatch</t>
+          <t>AssetPartialApplied</t>
         </is>
       </c>
       <c r="B318" s="0" t="inlineStr">
         <is>
-          <t>职业不符,无法装备</t>
-        </is>
+          <t>资产只发放了一部分，已记录，将由客服补偿</t>
+        </is>
+      </c>
+      <c r="C318" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="0" t="inlineStr">
         <is>
-          <t>EquipNoSlot</t>
+          <t>AssetAuthFailed</t>
         </is>
       </c>
       <c r="B319" s="0" t="inlineStr">
         <is>
-          <t>没有可用的装备栏位</t>
-        </is>
-      </c>
-    </row>
-    <row r="320">
-      <c r="A320" s="0" t="inlineStr">
-        <is>
-          <t>EquipNotEquipped</t>
-        </is>
-      </c>
-      <c r="B320" s="0" t="inlineStr">
-        <is>
-          <t>该装备未穿戴</t>
-        </is>
-      </c>
-    </row>
+          <t>资产指令校验失败</t>
+        </is>
+      </c>
+      <c r="C319" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="320"/>
     <row r="321">
       <c r="A321" s="0" t="inlineStr">
         <is>
-          <t>EquipBagFull</t>
-        </is>
-      </c>
-      <c r="B321" s="0" t="inlineStr">
-        <is>
-          <t>背包已满,无法卸下</t>
+          <t>//equip_error base=28000 width=1000</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="0" t="inlineStr">
         <is>
-          <t>EquipInBattle</t>
+          <t>EquipItemNotFound</t>
         </is>
       </c>
       <c r="B322" s="0" t="inlineStr">
         <is>
-          <t>战斗中无法更换装备</t>
+          <t>物品不存在</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="0" t="inlineStr">
         <is>
-          <t>EquipFrozen</t>
+          <t>EquipNotEquipment</t>
         </is>
       </c>
       <c r="B323" s="0" t="inlineStr">
         <is>
-          <t>当前状态无法更换装备</t>
+          <t>该物品不是装备</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="0" t="inlineStr">
         <is>
-          <t>EquipGrantInvalid</t>
+          <t>EquipLevelNotEnough</t>
         </is>
       </c>
       <c r="B324" s="0" t="inlineStr">
         <is>
-          <t>发放参数无效</t>
+          <t>等级不足,无法装备</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="0" t="inlineStr">
         <is>
-          <t>EquipInternalError</t>
+          <t>EquipClassMismatch</t>
         </is>
       </c>
       <c r="B325" s="0" t="inlineStr">
         <is>
-          <t>装备操作失败,请稍后再试</t>
-        </is>
-      </c>
-      <c r="C325" s="0" t="n">
-        <v>1</v>
+          <t>职业不符,无法装备</t>
+        </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="0" t="inlineStr">
         <is>
-          <t>EquipEnhanceUnavailable</t>
+          <t>EquipNoSlot</t>
         </is>
       </c>
       <c r="B326" s="0" t="inlineStr">
         <is>
-          <t>该装备无法强化</t>
+          <t>没有可用的装备栏位</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="0" t="inlineStr">
         <is>
-          <t>EquipEnhanceMaxLevel</t>
+          <t>EquipNotEquipped</t>
         </is>
       </c>
       <c r="B327" s="0" t="inlineStr">
         <is>
-          <t>已强化到最高等级</t>
+          <t>该装备未穿戴</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="0" t="inlineStr">
         <is>
-          <t>EquipEnhanceMaterialNotEnough</t>
+          <t>EquipBagFull</t>
         </is>
       </c>
       <c r="B328" s="0" t="inlineStr">
         <is>
-          <t>强化材料不足</t>
+          <t>背包已满,无法卸下</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="0" t="inlineStr">
         <is>
-          <t>EquipEnhanceGoldNotEnough</t>
+          <t>EquipInBattle</t>
         </is>
       </c>
       <c r="B329" s="0" t="inlineStr">
         <is>
-          <t>金币不足,无法强化</t>
+          <t>战斗中无法更换装备</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="0" t="inlineStr">
         <is>
-          <t>EquipGemNotGem</t>
+          <t>EquipFrozen</t>
         </is>
       </c>
       <c r="B330" s="0" t="inlineStr">
         <is>
-          <t>该物品不是宝石</t>
+          <t>当前状态无法更换装备</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="0" t="inlineStr">
         <is>
-          <t>EquipGemNotOwned</t>
+          <t>EquipGrantInvalid</t>
         </is>
       </c>
       <c r="B331" s="0" t="inlineStr">
         <is>
-          <t>背包里没有这颗宝石</t>
+          <t>发放参数无效</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="0" t="inlineStr">
         <is>
-          <t>EquipGemSocketInvalid</t>
+          <t>EquipInternalError</t>
         </is>
       </c>
       <c r="B332" s="0" t="inlineStr">
         <is>
-          <t>该装备没有这个宝石孔</t>
-        </is>
+          <t>装备操作失败,请稍后再试</t>
+        </is>
+      </c>
+      <c r="C332" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="0" t="inlineStr">
         <is>
-          <t>EquipGemSocketOccupied</t>
+          <t>EquipEnhanceUnavailable</t>
         </is>
       </c>
       <c r="B333" s="0" t="inlineStr">
         <is>
-          <t>该孔位已镶有宝石,请先取下</t>
+          <t>该装备无法强化</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="0" t="inlineStr">
         <is>
-          <t>EquipGemSocketEmpty</t>
+          <t>EquipEnhanceMaxLevel</t>
         </is>
       </c>
       <c r="B334" s="0" t="inlineStr">
         <is>
-          <t>该孔位没有宝石</t>
+          <t>已强化到最高等级</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="0" t="inlineStr">
         <is>
-          <t>EquipGemTypeMismatch</t>
+          <t>EquipEnhanceMaterialNotEnough</t>
         </is>
       </c>
       <c r="B335" s="0" t="inlineStr">
         <is>
-          <t>宝石类型与孔位不符</t>
+          <t>强化材料不足</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="0" t="inlineStr">
         <is>
-          <t>EquipGemBagFull</t>
+          <t>EquipEnhanceGoldNotEnough</t>
         </is>
       </c>
       <c r="B336" s="0" t="inlineStr">
         <is>
-          <t>背包已满,无法取下宝石</t>
-        </is>
-      </c>
-    </row>
-    <row r="337"/>
+          <t>金币不足,无法强化</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="0" t="inlineStr">
+        <is>
+          <t>EquipGemNotGem</t>
+        </is>
+      </c>
+      <c r="B337" s="0" t="inlineStr">
+        <is>
+          <t>该物品不是宝石</t>
+        </is>
+      </c>
+    </row>
     <row r="338">
       <c r="A338" s="0" t="inlineStr">
         <is>
-          <t>//player_inbox_error base=29000 width=1000</t>
+          <t>EquipGemNotOwned</t>
+        </is>
+      </c>
+      <c r="B338" s="0" t="inlineStr">
+        <is>
+          <t>背包里没有这颗宝石</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" s="0" t="inlineStr">
         <is>
-          <t>PlayerInboxDisabled</t>
+          <t>EquipGemSocketInvalid</t>
         </is>
       </c>
       <c r="B339" s="0" t="inlineStr">
         <is>
-          <t>该类收件箱消息暂未开放</t>
+          <t>该装备没有这个宝石孔</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" s="0" t="inlineStr">
         <is>
-          <t>PlayerInboxUnknownType</t>
+          <t>EquipGemSocketOccupied</t>
         </is>
       </c>
       <c r="B340" s="0" t="inlineStr">
         <is>
-          <t>未知的收件箱消息类型</t>
+          <t>该孔位已镶有宝石,请先取下</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" s="0" t="inlineStr">
         <is>
-          <t>PlayerInboxPlayerNotFound</t>
+          <t>EquipGemSocketEmpty</t>
         </is>
       </c>
       <c r="B341" s="0" t="inlineStr">
         <is>
-          <t>玩家不存在</t>
+          <t>该孔位没有宝石</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="0" t="inlineStr">
         <is>
-          <t>PlayerInboxPayloadInvalid</t>
+          <t>EquipGemTypeMismatch</t>
         </is>
       </c>
       <c r="B342" s="0" t="inlineStr">
         <is>
-          <t>收件箱消息内容无效</t>
+          <t>宝石类型与孔位不符</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" s="0" t="inlineStr">
         <is>
-          <t>PlayerInboxPayloadTooLarge</t>
+          <t>EquipGemBagFull</t>
         </is>
       </c>
       <c r="B343" s="0" t="inlineStr">
         <is>
-          <t>收件箱消息内容过大</t>
-        </is>
-      </c>
-    </row>
-    <row r="344">
-      <c r="A344" s="0" t="inlineStr">
-        <is>
-          <t>PlayerInboxTextTooLong</t>
-        </is>
-      </c>
-      <c r="B344" s="0" t="inlineStr">
-        <is>
-          <t>操作人、理由或备注过长</t>
-        </is>
-      </c>
-    </row>
+          <t>背包已满,无法取下宝石</t>
+        </is>
+      </c>
+    </row>
+    <row r="344"/>
     <row r="345">
       <c r="A345" s="0" t="inlineStr">
         <is>
-          <t>PlayerInboxIssuedOutOfWindow</t>
-        </is>
-      </c>
-      <c r="B345" s="0" t="inlineStr">
-        <is>
-          <t>签发时间超出允许范围</t>
+          <t>//player_inbox_error base=29000 width=1000</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" s="0" t="inlineStr">
         <is>
-          <t>PlayerInboxFull</t>
+          <t>PlayerInboxDisabled</t>
         </is>
       </c>
       <c r="B346" s="0" t="inlineStr">
         <is>
-          <t>该玩家的收件箱已满</t>
+          <t>该类收件箱消息暂未开放</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" s="0" t="inlineStr">
         <is>
-          <t>PlayerInboxIdempotencyConflict</t>
+          <t>PlayerInboxUnknownType</t>
         </is>
       </c>
       <c r="B347" s="0" t="inlineStr">
         <is>
-          <t>请求号已被不同内容使用</t>
+          <t>未知的收件箱消息类型</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" s="0" t="inlineStr">
         <is>
-          <t>PlayerInboxStaleOwner</t>
+          <t>PlayerInboxPlayerNotFound</t>
         </is>
       </c>
       <c r="B348" s="0" t="inlineStr">
         <is>
-          <t>场景归属已过期</t>
+          <t>玩家不存在</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" s="0" t="inlineStr">
         <is>
-          <t>PlayerInboxEpochRequired</t>
+          <t>PlayerInboxPayloadInvalid</t>
         </is>
       </c>
       <c r="B349" s="0" t="inlineStr">
         <is>
-          <t>缺少场景归属代际</t>
+          <t>收件箱消息内容无效</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" s="0" t="inlineStr">
         <is>
-          <t>PlayerInboxEpochAhead</t>
+          <t>PlayerInboxPayloadTooLarge</t>
         </is>
       </c>
       <c r="B350" s="0" t="inlineStr">
         <is>
-          <t>场景归属代际超前</t>
+          <t>收件箱消息内容过大</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" s="0" t="inlineStr">
         <is>
-          <t>PlayerInboxItemNotFound</t>
+          <t>PlayerInboxTextTooLong</t>
         </is>
       </c>
       <c r="B351" s="0" t="inlineStr">
         <is>
-          <t>收件箱条目不存在</t>
+          <t>操作人、理由或备注过长</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" s="0" t="inlineStr">
         <is>
-          <t>PlayerInboxItemStateConflict</t>
+          <t>PlayerInboxIssuedOutOfWindow</t>
         </is>
       </c>
       <c r="B352" s="0" t="inlineStr">
         <is>
-          <t>收件箱条目当前状态不允许该操作</t>
+          <t>签发时间超出允许范围</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" s="0" t="inlineStr">
         <is>
-          <t>PlayerInboxStoreUnavailable</t>
+          <t>PlayerInboxFull</t>
         </is>
       </c>
       <c r="B353" s="0" t="inlineStr">
         <is>
-          <t>收件箱服务暂不可用,请稍后再试</t>
-        </is>
-      </c>
-      <c r="C353" s="0" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="354"/>
+          <t>该玩家的收件箱已满</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="0" t="inlineStr">
+        <is>
+          <t>PlayerInboxIdempotencyConflict</t>
+        </is>
+      </c>
+      <c r="B354" s="0" t="inlineStr">
+        <is>
+          <t>请求号已被不同内容使用</t>
+        </is>
+      </c>
+    </row>
     <row r="355">
       <c r="A355" s="0" t="inlineStr">
         <is>
-          <t>//mail_error base=17000 width=1000</t>
+          <t>PlayerInboxStaleOwner</t>
+        </is>
+      </c>
+      <c r="B355" s="0" t="inlineStr">
+        <is>
+          <t>场景归属已过期</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" s="0" t="inlineStr">
         <is>
-          <t>MailClaimNotOpen</t>
+          <t>PlayerInboxEpochRequired</t>
         </is>
       </c>
       <c r="B356" s="0" t="inlineStr">
         <is>
-          <t>附件领取暂未开放</t>
+          <t>缺少场景归属代际</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" s="0" t="inlineStr">
         <is>
-          <t>MailNotFound</t>
+          <t>PlayerInboxEpochAhead</t>
         </is>
       </c>
       <c r="B357" s="0" t="inlineStr">
         <is>
-          <t>邮件不存在或已删除</t>
+          <t>场景归属代际超前</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" s="0" t="inlineStr">
         <is>
-          <t>MailExpired</t>
+          <t>PlayerInboxItemNotFound</t>
         </is>
       </c>
       <c r="B358" s="0" t="inlineStr">
         <is>
-          <t>邮件已过期</t>
+          <t>收件箱条目不存在</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" s="0" t="inlineStr">
         <is>
-          <t>MailRecipientBoxFull</t>
+          <t>PlayerInboxItemStateConflict</t>
         </is>
       </c>
       <c r="B359" s="0" t="inlineStr">
         <is>
-          <t>收件人邮箱已满</t>
+          <t>收件箱条目当前状态不允许该操作</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="0" t="inlineStr">
         <is>
-          <t>MailAttachmentNotOpen</t>
+          <t>PlayerInboxStoreUnavailable</t>
         </is>
       </c>
       <c r="B360" s="0" t="inlineStr">
         <is>
-          <t>当前环境不允许发送带附件的邮件</t>
-        </is>
-      </c>
-    </row>
-    <row r="361">
-      <c r="A361" s="0" t="inlineStr">
-        <is>
-          <t>MailAttachmentInvalid</t>
-        </is>
-      </c>
-      <c r="B361" s="0" t="inlineStr">
-        <is>
-          <t>邮件附件不合法</t>
-        </is>
-      </c>
-    </row>
+          <t>收件箱服务暂不可用,请稍后再试</t>
+        </is>
+      </c>
+      <c r="C360" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="361"/>
     <row r="362">
       <c r="A362" s="0" t="inlineStr">
         <is>
-          <t>MailRequestConflict</t>
-        </is>
-      </c>
-      <c r="B362" s="0" t="inlineStr">
-        <is>
-          <t>发件请求编号重复但内容不同</t>
+          <t>//mail_error base=17000 width=1000</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" s="0" t="inlineStr">
         <is>
+          <t>MailClaimNotOpen</t>
+        </is>
+      </c>
+      <c r="B363" s="0" t="inlineStr">
+        <is>
+          <t>附件领取暂未开放</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="0" t="inlineStr">
+        <is>
+          <t>MailNotFound</t>
+        </is>
+      </c>
+      <c r="B364" s="0" t="inlineStr">
+        <is>
+          <t>邮件不存在或已删除</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="0" t="inlineStr">
+        <is>
+          <t>MailExpired</t>
+        </is>
+      </c>
+      <c r="B365" s="0" t="inlineStr">
+        <is>
+          <t>邮件已过期</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="0" t="inlineStr">
+        <is>
+          <t>MailRecipientBoxFull</t>
+        </is>
+      </c>
+      <c r="B366" s="0" t="inlineStr">
+        <is>
+          <t>收件人邮箱已满</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="0" t="inlineStr">
+        <is>
+          <t>MailAttachmentNotOpen</t>
+        </is>
+      </c>
+      <c r="B367" s="0" t="inlineStr">
+        <is>
+          <t>当前环境不允许发送带附件的邮件</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="0" t="inlineStr">
+        <is>
+          <t>MailAttachmentInvalid</t>
+        </is>
+      </c>
+      <c r="B368" s="0" t="inlineStr">
+        <is>
+          <t>邮件附件不合法</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="0" t="inlineStr">
+        <is>
+          <t>MailRequestConflict</t>
+        </is>
+      </c>
+      <c r="B369" s="0" t="inlineStr">
+        <is>
+          <t>发件请求编号重复但内容不同</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="0" t="inlineStr">
+        <is>
           <t>MailSystemMailLimit</t>
         </is>
       </c>
-      <c r="B363" s="0" t="inlineStr">
+      <c r="B370" s="0" t="inlineStr">
         <is>
           <t>有效系统邮件数量已达上限</t>
         </is>
       </c>
     </row>
-    <row r="365">
-      <c r="A365" t="inlineStr">
+    <row r="371"/>
+    <row r="372">
+      <c r="A372" s="0" t="inlineStr">
         <is>
           <t>//mystery_merchant_error base=30000 width=1000</t>
         </is>
       </c>
     </row>
-    <row r="366">
-      <c r="A366" t="inlineStr">
+    <row r="373">
+      <c r="A373" s="0" t="inlineStr">
         <is>
           <t>MysteryMerchantNotPresent</t>
         </is>
       </c>
-      <c r="B366" t="inlineStr">
+      <c r="B373" s="0" t="inlineStr">
         <is>
           <t>神秘商人现在不在,请留意下次出现的公告</t>
         </is>
       </c>
     </row>
-    <row r="367">
-      <c r="A367" t="inlineStr">
+    <row r="374">
+      <c r="A374" s="0" t="inlineStr">
         <is>
           <t>MysteryMerchantNotHere</t>
         </is>
       </c>
-      <c r="B367" t="inlineStr">
+      <c r="B374" s="0" t="inlineStr">
         <is>
           <t>神秘商人不在这条线上</t>
         </is>
       </c>
     </row>
-    <row r="368">
-      <c r="A368" t="inlineStr">
+    <row r="375">
+      <c r="A375" s="0" t="inlineStr">
         <is>
           <t>MysteryMerchantTooFar</t>
         </is>
       </c>
-      <c r="B368" t="inlineStr">
+      <c r="B375" s="0" t="inlineStr">
         <is>
           <t>离神秘商人太远了,走近一些再买</t>
         </is>
       </c>
     </row>
-    <row r="369">
-      <c r="A369" t="inlineStr">
+    <row r="376">
+      <c r="A376" s="0" t="inlineStr">
         <is>
           <t>MysteryMerchantShelfChanged</t>
         </is>
       </c>
-      <c r="B369" t="inlineStr">
+      <c r="B376" s="0" t="inlineStr">
         <is>
           <t>货架已经更新,请重新查看</t>
         </is>
       </c>
     </row>
-    <row r="370">
-      <c r="A370" t="inlineStr">
+    <row r="377">
+      <c r="A377" s="0" t="inlineStr">
         <is>
           <t>MysteryMerchantLimitReached</t>
         </is>
       </c>
-      <c r="B370" t="inlineStr">
+      <c r="B377" s="0" t="inlineStr">
         <is>
           <t>这件商品本轮已达限购数量</t>
         </is>
       </c>
     </row>
-    <row r="371">
-      <c r="A371" t="inlineStr">
+    <row r="378">
+      <c r="A378" s="0" t="inlineStr">
         <is>
           <t>MysteryMerchantCurrencyNotEnough</t>
         </is>
       </c>
-      <c r="B371" t="inlineStr">
+      <c r="B378" s="0" t="inlineStr">
         <is>
           <t>货币不足,无法购买</t>
         </is>
       </c>
     </row>
-    <row r="372">
-      <c r="A372" t="inlineStr">
+    <row r="379">
+      <c r="A379" s="0" t="inlineStr">
         <is>
           <t>MysteryMerchantBagFull</t>
         </is>
       </c>
-      <c r="B372" t="inlineStr">
+      <c r="B379" s="0" t="inlineStr">
         <is>
           <t>背包已满,无法购买</t>
         </is>
       </c>
     </row>
-    <row r="373">
-      <c r="A373" t="inlineStr">
+    <row r="380">
+      <c r="A380" s="0" t="inlineStr">
         <is>
           <t>MysteryMerchantInBattle</t>
         </is>
       </c>
-      <c r="B373" t="inlineStr">
+      <c r="B380" s="0" t="inlineStr">
         <is>
           <t>战斗中不能购买</t>
         </is>
       </c>
     </row>
-    <row r="374">
-      <c r="A374" t="inlineStr">
+    <row r="381">
+      <c r="A381" s="0" t="inlineStr">
         <is>
           <t>MysteryMerchantFrozen</t>
         </is>
       </c>
-      <c r="B374" t="inlineStr">
+      <c r="B381" s="0" t="inlineStr">
         <is>
           <t>角色正在跨区传送,暂时不能购买</t>
         </is>
       </c>
     </row>
-    <row r="375">
-      <c r="A375" t="inlineStr">
+    <row r="382">
+      <c r="A382" s="0" t="inlineStr">
         <is>
           <t>MysteryMerchantInvalidCount</t>
         </is>
       </c>
-      <c r="B375" t="inlineStr">
+      <c r="B382" s="0" t="inlineStr">
         <is>
           <t>购买数量无效</t>
         </is>
       </c>
     </row>
-    <row r="376">
-      <c r="A376" t="inlineStr">
+    <row r="383">
+      <c r="A383" s="0" t="inlineStr">
         <is>
           <t>MysteryMerchantItemBlocked</t>
         </is>
       </c>
-      <c r="B376" t="inlineStr">
+      <c r="B383" s="0" t="inlineStr">
         <is>
           <t>这件商品暂时无法购买</t>
         </is>
       </c>
     </row>
-    <row r="377">
-      <c r="A377" t="inlineStr">
+    <row r="384">
+      <c r="A384" s="0" t="inlineStr">
         <is>
           <t>MysteryMerchantInternalError</t>
         </is>
       </c>
-      <c r="B377" t="inlineStr">
+      <c r="B384" s="0" t="inlineStr">
         <is>
           <t>神秘商人暂时无法交易,请稍后再试</t>
         </is>
       </c>
-      <c r="C377" t="n">
+      <c r="C384" s="0" t="n">
         <v>1</v>
       </c>
     </row>

--- a/data/tip/Tip.xlsx
+++ b/data/tip/Tip.xlsx
@@ -959,7 +959,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C406"/>
+  <dimension ref="A1:C407"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="57" customWidth="1" style="2" min="1" max="1"/>
@@ -2697,84 +2697,84 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" t="inlineStr">
+      <c r="A170" s="0" t="inlineStr">
         <is>
           <t>SkillNotInClass</t>
         </is>
       </c>
-      <c r="B170" t="inlineStr">
+      <c r="B170" s="0" t="inlineStr">
         <is>
           <t>该技能不属于当前职业</t>
         </is>
       </c>
     </row>
     <row r="171">
-      <c r="A171" t="inlineStr">
+      <c r="A171" s="0" t="inlineStr">
         <is>
           <t>SkillRankChanged</t>
         </is>
       </c>
-      <c r="B171" t="inlineStr">
+      <c r="B171" s="0" t="inlineStr">
         <is>
           <t>技能等级已变化,请刷新后再试</t>
         </is>
       </c>
     </row>
     <row r="172">
-      <c r="A172" t="inlineStr">
+      <c r="A172" s="0" t="inlineStr">
         <is>
           <t>SkillUpgradeCountInvalid</t>
         </is>
       </c>
-      <c r="B172" t="inlineStr">
+      <c r="B172" s="0" t="inlineStr">
         <is>
           <t>修习次数只能是 1 次或 10 次</t>
         </is>
       </c>
     </row>
     <row r="173">
-      <c r="A173" t="inlineStr">
+      <c r="A173" s="0" t="inlineStr">
         <is>
           <t>SkillLevelNotEnough</t>
         </is>
       </c>
-      <c r="B173" t="inlineStr">
+      <c r="B173" s="0" t="inlineStr">
         <is>
           <t>角色等级不足,暂不能继续修习</t>
         </is>
       </c>
     </row>
     <row r="174">
-      <c r="A174" t="inlineStr">
+      <c r="A174" s="0" t="inlineStr">
         <is>
           <t>SkillMaxRankReached</t>
         </is>
       </c>
-      <c r="B174" t="inlineStr">
+      <c r="B174" s="0" t="inlineStr">
         <is>
           <t>技能已修至最高重</t>
         </is>
       </c>
     </row>
     <row r="175">
-      <c r="A175" t="inlineStr">
+      <c r="A175" s="0" t="inlineStr">
         <is>
           <t>SkillGoldNotEnough</t>
         </is>
       </c>
-      <c r="B175" t="inlineStr">
+      <c r="B175" s="0" t="inlineStr">
         <is>
           <t>银两不足</t>
         </is>
       </c>
     </row>
     <row r="176">
-      <c r="A176" t="inlineStr">
+      <c r="A176" s="0" t="inlineStr">
         <is>
           <t>SkillUpgradeBusy</t>
         </is>
       </c>
-      <c r="B176" t="inlineStr">
+      <c r="B176" s="0" t="inlineStr">
         <is>
           <t>战斗中或角色迁移中不能修习技能</t>
         </is>
@@ -3810,1572 +3810,1584 @@
       </c>
     </row>
     <row r="266">
-      <c r="A266" s="0" t="inlineStr">
-        <is>
-          <t>// 以下号段为移植域预留，建组时把本行改成组头即可：</t>
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>MatchSpectateFull</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>观战人数已满</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="0" t="inlineStr">
         <is>
-          <t>//   mail_error 17000 / chat_error 18000 / auction_error 19000</t>
+          <t>// 以下号段为移植域预留，建组时把本行改成组头即可：</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="0" t="inlineStr">
         <is>
+          <t>//   mail_error 17000 / chat_error 18000 / auction_error 19000</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="0" t="inlineStr">
+        <is>
           <t>//   rank_error 21000 / dialogue_error 22000 / battle_result_error 23000 / grant_error 24000</t>
         </is>
       </c>
     </row>
-    <row r="269"/>
-    <row r="270">
-      <c r="A270" s="0" t="inlineStr">
-        <is>
-          <t>//trade_error base=20000 width=1000</t>
-        </is>
-      </c>
-    </row>
+    <row r="270"/>
     <row r="271">
       <c r="A271" s="0" t="inlineStr">
         <is>
-          <t>TradeListingNotFound</t>
-        </is>
-      </c>
-      <c r="B271" s="0" t="inlineStr">
-        <is>
-          <t>商品不存在或已下架</t>
+          <t>//trade_error base=20000 width=1000</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="0" t="inlineStr">
         <is>
-          <t>TradeHomeZoneUnknown</t>
+          <t>TradeListingNotFound</t>
         </is>
       </c>
       <c r="B272" s="0" t="inlineStr">
         <is>
-          <t>角色归属区服未确认，暂时无法使用聚宝斋</t>
+          <t>商品不存在或已下架</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="0" t="inlineStr">
         <is>
-          <t>TradeFavoriteLimitReached</t>
+          <t>TradeHomeZoneUnknown</t>
         </is>
       </c>
       <c r="B273" s="0" t="inlineStr">
         <is>
-          <t>收藏数量已达上限，请先取消部分收藏</t>
+          <t>角色归属区服未确认，暂时无法使用聚宝斋</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="0" t="inlineStr">
         <is>
+          <t>TradeFavoriteLimitReached</t>
+        </is>
+      </c>
+      <c r="B274" s="0" t="inlineStr">
+        <is>
+          <t>收藏数量已达上限，请先取消部分收藏</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="0" t="inlineStr">
+        <is>
           <t>TradeFeatureDisabled</t>
         </is>
       </c>
-      <c r="B274" s="0" t="inlineStr">
+      <c r="B275" s="0" t="inlineStr">
         <is>
           <t>该功能尚未开放</t>
         </is>
       </c>
     </row>
-    <row r="275"/>
-    <row r="276">
-      <c r="A276" s="0" t="inlineStr">
-        <is>
-          <t>TradeOrderNotFound</t>
-        </is>
-      </c>
-      <c r="B276" s="0" t="inlineStr">
-        <is>
-          <t>交易订单不存在</t>
-        </is>
-      </c>
-    </row>
+    <row r="276"/>
     <row r="277">
       <c r="A277" s="0" t="inlineStr">
         <is>
-          <t>TradeOrderStateConflict</t>
+          <t>TradeOrderNotFound</t>
         </is>
       </c>
       <c r="B277" s="0" t="inlineStr">
         <is>
-          <t>订单状态已变化，请刷新</t>
+          <t>交易订单不存在</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="0" t="inlineStr">
         <is>
-          <t>TradeRequestConflict</t>
+          <t>TradeOrderStateConflict</t>
         </is>
       </c>
       <c r="B278" s="0" t="inlineStr">
         <is>
-          <t>交易请求编号重复但内容不同</t>
+          <t>订单状态已变化，请刷新</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="0" t="inlineStr">
         <is>
-          <t>TradeOrderLimit</t>
+          <t>TradeRequestConflict</t>
         </is>
       </c>
       <c r="B279" s="0" t="inlineStr">
         <is>
-          <t>未完成交易数量已达上限</t>
+          <t>交易请求编号重复但内容不同</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="0" t="inlineStr">
         <is>
-          <t>TradeCannotTradeSelf</t>
+          <t>TradeOrderLimit</t>
         </is>
       </c>
       <c r="B280" s="0" t="inlineStr">
         <is>
-          <t>不能与自己交易</t>
+          <t>未完成交易数量已达上限</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="0" t="inlineStr">
         <is>
-          <t>TradeCounterpartyUnknown</t>
+          <t>TradeCannotTradeSelf</t>
         </is>
       </c>
       <c r="B281" s="0" t="inlineStr">
         <is>
-          <t>交易对方不存在</t>
+          <t>不能与自己交易</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="0" t="inlineStr">
         <is>
-          <t>TradeInsufficientAsset</t>
+          <t>TradeCounterpartyUnknown</t>
         </is>
       </c>
       <c r="B282" s="0" t="inlineStr">
         <is>
-          <t>可交易资产不足</t>
+          <t>交易对方不存在</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="0" t="inlineStr">
         <is>
-          <t>TradeBidTooLow</t>
+          <t>TradeInsufficientAsset</t>
         </is>
       </c>
       <c r="B283" s="0" t="inlineStr">
         <is>
-          <t>出价低于当前最低价</t>
+          <t>可交易资产不足</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="0" t="inlineStr">
         <is>
-          <t>TradeAuctionEnded</t>
+          <t>TradeBidTooLow</t>
         </is>
       </c>
       <c r="B284" s="0" t="inlineStr">
         <is>
-          <t>拍卖已经结束</t>
+          <t>出价低于当前最低价</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="0" t="inlineStr">
         <is>
-          <t>TradeAssetDeliveryPending</t>
+          <t>TradeAuctionEnded</t>
         </is>
       </c>
       <c r="B285" s="0" t="inlineStr">
         <is>
-          <t>资产正在到账，请稍后刷新</t>
+          <t>拍卖已经结束</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="0" t="inlineStr">
         <is>
-          <t>TradeManualReview</t>
+          <t>TradeAssetDeliveryPending</t>
         </is>
       </c>
       <c r="B286" s="0" t="inlineStr">
         <is>
-          <t>交易需要人工核对</t>
+          <t>资产正在到账，请稍后刷新</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="0" t="inlineStr">
         <is>
-          <t>TradeAssetNotTradable</t>
+          <t>TradeManualReview</t>
         </is>
       </c>
       <c r="B287" s="0" t="inlineStr">
         <is>
-          <t>该资产不可交易</t>
+          <t>交易需要人工核对</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="0" t="inlineStr">
         <is>
-          <t>//attribute_error base=25000 width=1000</t>
+          <t>TradeAssetNotTradable</t>
+        </is>
+      </c>
+      <c r="B288" s="0" t="inlineStr">
+        <is>
+          <t>该资产不可交易</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="0" t="inlineStr">
         <is>
-          <t>AttributePoolNotFound</t>
-        </is>
-      </c>
-      <c r="B289" s="0" t="inlineStr">
-        <is>
-          <t>属性池不存在</t>
+          <t>//attribute_error base=25000 width=1000</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="0" t="inlineStr">
         <is>
-          <t>AttributePoolLocked</t>
+          <t>AttributePoolNotFound</t>
         </is>
       </c>
       <c r="B290" s="0" t="inlineStr">
         <is>
-          <t>该属性池尚未解锁</t>
+          <t>属性池不存在</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="0" t="inlineStr">
         <is>
-          <t>AttributeDimensionNotFound</t>
+          <t>AttributePoolLocked</t>
         </is>
       </c>
       <c r="B291" s="0" t="inlineStr">
         <is>
-          <t>属性维度不存在</t>
+          <t>该属性池尚未解锁</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="0" t="inlineStr">
         <is>
-          <t>AttributePointsNotEnough</t>
+          <t>AttributeDimensionNotFound</t>
         </is>
       </c>
       <c r="B292" s="0" t="inlineStr">
         <is>
-          <t>剩余点数不足</t>
+          <t>属性维度不存在</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="0" t="inlineStr">
         <is>
-          <t>AttributePointsCannotDecrease</t>
+          <t>AttributePointsNotEnough</t>
         </is>
       </c>
       <c r="B293" s="0" t="inlineStr">
         <is>
-          <t>已分配的点数不能减少,请使用重置</t>
+          <t>剩余点数不足</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="0" t="inlineStr">
         <is>
-          <t>AttributeDimensionCapExceeded</t>
+          <t>AttributePointsCannotDecrease</t>
         </is>
       </c>
       <c r="B294" s="0" t="inlineStr">
         <is>
-          <t>超过单项可分配上限</t>
+          <t>已分配的点数不能减少,请使用重置</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="0" t="inlineStr">
         <is>
-          <t>AttributeSchemeNotFound</t>
+          <t>AttributeDimensionCapExceeded</t>
         </is>
       </c>
       <c r="B295" s="0" t="inlineStr">
         <is>
-          <t>加点方案不存在</t>
+          <t>超过单项可分配上限</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="0" t="inlineStr">
         <is>
-          <t>AttributeSchemeLimitReached</t>
+          <t>AttributeSchemeNotFound</t>
         </is>
       </c>
       <c r="B296" s="0" t="inlineStr">
         <is>
-          <t>加点方案数量已达上限</t>
+          <t>加点方案不存在</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="0" t="inlineStr">
         <is>
-          <t>AttributeSchemeSwitchCooldown</t>
+          <t>AttributeSchemeLimitReached</t>
         </is>
       </c>
       <c r="B297" s="0" t="inlineStr">
         <is>
-          <t>方案切换冷却中</t>
+          <t>加点方案数量已达上限</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="0" t="inlineStr">
         <is>
-          <t>AttributeSchemeNameInvalid</t>
+          <t>AttributeSchemeSwitchCooldown</t>
         </is>
       </c>
       <c r="B298" s="0" t="inlineStr">
         <is>
-          <t>方案名称不合法</t>
+          <t>方案切换冷却中</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="0" t="inlineStr">
         <is>
-          <t>AttributeSchemeAlreadyActive</t>
+          <t>AttributeSchemeNameInvalid</t>
         </is>
       </c>
       <c r="B299" s="0" t="inlineStr">
         <is>
-          <t>已经是当前方案</t>
+          <t>方案名称不合法</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="0" t="inlineStr">
         <is>
-          <t>AttributeInBattle</t>
+          <t>AttributeSchemeAlreadyActive</t>
         </is>
       </c>
       <c r="B300" s="0" t="inlineStr">
         <is>
-          <t>战斗中不能修改属性</t>
+          <t>已经是当前方案</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="0" t="inlineStr">
         <is>
-          <t>AttributeGoldNotEnough</t>
+          <t>AttributeInBattle</t>
         </is>
       </c>
       <c r="B301" s="0" t="inlineStr">
         <is>
-          <t>金币不足</t>
+          <t>战斗中不能修改属性</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="0" t="inlineStr">
         <is>
-          <t>AttributeNoAutoPlan</t>
+          <t>AttributeGoldNotEnough</t>
         </is>
       </c>
       <c r="B302" s="0" t="inlineStr">
         <is>
-          <t>没有可用的自动加点方案</t>
+          <t>金币不足</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="0" t="inlineStr">
         <is>
+          <t>AttributeNoAutoPlan</t>
+        </is>
+      </c>
+      <c r="B303" s="0" t="inlineStr">
+        <is>
+          <t>没有可用的自动加点方案</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="0" t="inlineStr">
+        <is>
           <t>AttributeNothingToChange</t>
         </is>
       </c>
-      <c r="B303" s="0" t="inlineStr">
+      <c r="B304" s="0" t="inlineStr">
         <is>
           <t>属性没有变化</t>
         </is>
       </c>
     </row>
-    <row r="304"/>
-    <row r="305">
-      <c r="A305" s="0" t="inlineStr">
-        <is>
-          <t>//pet_error base=26000 width=1000</t>
-        </is>
-      </c>
-    </row>
+    <row r="305"/>
     <row r="306">
       <c r="A306" s="0" t="inlineStr">
         <is>
-          <t>PetNotFound</t>
-        </is>
-      </c>
-      <c r="B306" s="0" t="inlineStr">
-        <is>
-          <t>宝宝不存在</t>
+          <t>//pet_error base=26000 width=1000</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="0" t="inlineStr">
         <is>
-          <t>PetTableRowMissing</t>
+          <t>PetNotFound</t>
         </is>
       </c>
       <c r="B307" s="0" t="inlineStr">
         <is>
-          <t>宝宝数据已失效,请联系客服</t>
+          <t>宝宝不存在</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="0" t="inlineStr">
         <is>
-          <t>PetSlotFull</t>
+          <t>PetTableRowMissing</t>
         </is>
       </c>
       <c r="B308" s="0" t="inlineStr">
         <is>
-          <t>可携带的宝宝数量已达上限</t>
+          <t>宝宝数据已失效,请联系客服</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="0" t="inlineStr">
         <is>
-          <t>PetOwnerLevelNotEnough</t>
+          <t>PetSlotFull</t>
         </is>
       </c>
       <c r="B309" s="0" t="inlineStr">
         <is>
-          <t>主人等级不足,还不能携带这只宝宝</t>
+          <t>可携带的宝宝数量已达上限</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="0" t="inlineStr">
         <is>
-          <t>PetAlreadyActive</t>
+          <t>PetOwnerLevelNotEnough</t>
         </is>
       </c>
       <c r="B310" s="0" t="inlineStr">
         <is>
-          <t>这只宝宝已经在出战中</t>
+          <t>主人等级不足,还不能携带这只宝宝</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="0" t="inlineStr">
         <is>
-          <t>PetNotActive</t>
+          <t>PetAlreadyActive</t>
         </is>
       </c>
       <c r="B311" s="0" t="inlineStr">
         <is>
-          <t>当前没有出战的宝宝</t>
+          <t>这只宝宝已经在出战中</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="0" t="inlineStr">
         <is>
-          <t>PetSummonCooldown</t>
+          <t>PetNotActive</t>
         </is>
       </c>
       <c r="B312" s="0" t="inlineStr">
         <is>
-          <t>操作太频繁,请稍后再试</t>
+          <t>当前没有出战的宝宝</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="0" t="inlineStr">
         <is>
-          <t>PetNameInvalid</t>
+          <t>PetSummonCooldown</t>
         </is>
       </c>
       <c r="B313" s="0" t="inlineStr">
         <is>
-          <t>宝宝名称不合法</t>
+          <t>操作太频繁,请稍后再试</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="0" t="inlineStr">
         <is>
-          <t>PetInBattle</t>
+          <t>PetNameInvalid</t>
         </is>
       </c>
       <c r="B314" s="0" t="inlineStr">
         <is>
-          <t>战斗中不能操作宝宝</t>
+          <t>宝宝名称不合法</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="0" t="inlineStr">
         <is>
-          <t>PetPointsNotEnough</t>
+          <t>PetInBattle</t>
         </is>
       </c>
       <c r="B315" s="0" t="inlineStr">
         <is>
-          <t>宝宝剩余点数不足</t>
+          <t>战斗中不能操作宝宝</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="0" t="inlineStr">
         <is>
-          <t>PetPointsCannotDecrease</t>
+          <t>PetPointsNotEnough</t>
         </is>
       </c>
       <c r="B316" s="0" t="inlineStr">
         <is>
-          <t>已分配的点数不能减少,请使用洗点</t>
+          <t>宝宝剩余点数不足</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="0" t="inlineStr">
         <is>
-          <t>PetDimensionCapExceeded</t>
+          <t>PetPointsCannotDecrease</t>
         </is>
       </c>
       <c r="B317" s="0" t="inlineStr">
         <is>
-          <t>超过单项可分配上限</t>
+          <t>已分配的点数不能减少,请使用洗点</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="0" t="inlineStr">
         <is>
-          <t>PetDimensionNotFound</t>
+          <t>PetDimensionCapExceeded</t>
         </is>
       </c>
       <c r="B318" s="0" t="inlineStr">
         <is>
-          <t>宝宝属性维度不存在</t>
+          <t>超过单项可分配上限</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="0" t="inlineStr">
         <is>
-          <t>PetGoldNotEnough</t>
+          <t>PetDimensionNotFound</t>
         </is>
       </c>
       <c r="B319" s="0" t="inlineStr">
         <is>
-          <t>金币不足</t>
+          <t>宝宝属性维度不存在</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="0" t="inlineStr">
         <is>
-          <t>PetNoAutoPlan</t>
+          <t>PetGoldNotEnough</t>
         </is>
       </c>
       <c r="B320" s="0" t="inlineStr">
         <is>
-          <t>没有可用的自动加点方案</t>
+          <t>金币不足</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="0" t="inlineStr">
         <is>
-          <t>PetNothingToChange</t>
+          <t>PetNoAutoPlan</t>
         </is>
       </c>
       <c r="B321" s="0" t="inlineStr">
         <is>
-          <t>宝宝属性没有变化</t>
+          <t>没有可用的自动加点方案</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="0" t="inlineStr">
         <is>
+          <t>PetNothingToChange</t>
+        </is>
+      </c>
+      <c r="B322" s="0" t="inlineStr">
+        <is>
+          <t>宝宝属性没有变化</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="0" t="inlineStr">
+        <is>
           <t>PetIdGenerateFailed</t>
         </is>
       </c>
-      <c r="B322" s="0" t="inlineStr">
+      <c r="B323" s="0" t="inlineStr">
         <is>
           <t>宝宝创建失败,请稍后再试</t>
         </is>
       </c>
-      <c r="C322" s="0" t="n">
+      <c r="C323" s="0" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="323"/>
-    <row r="324">
-      <c r="A324" s="0" t="inlineStr">
-        <is>
-          <t>//asset_error base=27000 width=1000</t>
-        </is>
-      </c>
-    </row>
+    <row r="324"/>
     <row r="325">
       <c r="A325" s="0" t="inlineStr">
         <is>
-          <t>AssetCurrencyInsufficient</t>
-        </is>
-      </c>
-      <c r="B325" s="0" t="inlineStr">
-        <is>
-          <t>货币不足</t>
+          <t>//asset_error base=27000 width=1000</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="0" t="inlineStr">
         <is>
-          <t>AssetBagFull</t>
+          <t>AssetCurrencyInsufficient</t>
         </is>
       </c>
       <c r="B326" s="0" t="inlineStr">
         <is>
-          <t>背包已满，请腾出空间，之后会重试发放；超过时限可能取消</t>
+          <t>货币不足</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="0" t="inlineStr">
         <is>
-          <t>AssetInBattle</t>
+          <t>AssetBagFull</t>
         </is>
       </c>
       <c r="B327" s="0" t="inlineStr">
         <is>
-          <t>战斗中暂不结算，稍后自动重试；超过时限可能取消</t>
+          <t>背包已满，请腾出空间，之后会重试发放；超过时限可能取消</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="0" t="inlineStr">
         <is>
-          <t>AssetFrozen</t>
+          <t>AssetInBattle</t>
         </is>
       </c>
       <c r="B328" s="0" t="inlineStr">
         <is>
-          <t>角色迁移中，稍后自动重试；超过时限可能取消</t>
+          <t>战斗中暂不结算，稍后自动重试；超过时限可能取消</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="0" t="inlineStr">
         <is>
-          <t>AssetInvalidBundle</t>
+          <t>AssetFrozen</t>
         </is>
       </c>
       <c r="B329" s="0" t="inlineStr">
         <is>
-          <t>资产指令无效</t>
-        </is>
-      </c>
-      <c r="C329" s="0" t="n">
-        <v>1</v>
+          <t>角色迁移中，稍后自动重试；超过时限可能取消</t>
+        </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="0" t="inlineStr">
         <is>
-          <t>AssetBlocked</t>
+          <t>AssetInvalidBundle</t>
         </is>
       </c>
       <c r="B330" s="0" t="inlineStr">
         <is>
-          <t>该资产当前被禁止获取</t>
-        </is>
+          <t>资产指令无效</t>
+        </is>
+      </c>
+      <c r="C330" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="0" t="inlineStr">
         <is>
-          <t>AssetPlayerNotHere</t>
+          <t>AssetBlocked</t>
         </is>
       </c>
       <c r="B331" s="0" t="inlineStr">
         <is>
-          <t>角色不在线，上线后重试；超过时限可能取消</t>
+          <t>该资产当前被禁止获取</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="0" t="inlineStr">
         <is>
-          <t>AssetPartialApplied</t>
+          <t>AssetPlayerNotHere</t>
         </is>
       </c>
       <c r="B332" s="0" t="inlineStr">
         <is>
-          <t>资产只发放了一部分，已记录，将由客服补偿</t>
-        </is>
-      </c>
-      <c r="C332" s="0" t="n">
-        <v>1</v>
+          <t>角色不在线，上线后重试；超过时限可能取消</t>
+        </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="0" t="inlineStr">
         <is>
-          <t>AssetAuthFailed</t>
+          <t>AssetPartialApplied</t>
         </is>
       </c>
       <c r="B333" s="0" t="inlineStr">
         <is>
-          <t>资产指令校验失败</t>
+          <t>资产只发放了一部分，已记录，将由客服补偿</t>
         </is>
       </c>
       <c r="C333" s="0" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="334"/>
-    <row r="335">
-      <c r="A335" s="0" t="inlineStr">
-        <is>
-          <t>//equip_error base=28000 width=1000</t>
-        </is>
-      </c>
-    </row>
+    <row r="334">
+      <c r="A334" s="0" t="inlineStr">
+        <is>
+          <t>AssetAuthFailed</t>
+        </is>
+      </c>
+      <c r="B334" s="0" t="inlineStr">
+        <is>
+          <t>资产指令校验失败</t>
+        </is>
+      </c>
+      <c r="C334" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="335"/>
     <row r="336">
       <c r="A336" s="0" t="inlineStr">
         <is>
-          <t>EquipItemNotFound</t>
-        </is>
-      </c>
-      <c r="B336" s="0" t="inlineStr">
-        <is>
-          <t>物品不存在</t>
+          <t>//equip_error base=28000 width=1000</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="0" t="inlineStr">
         <is>
-          <t>EquipNotEquipment</t>
+          <t>EquipItemNotFound</t>
         </is>
       </c>
       <c r="B337" s="0" t="inlineStr">
         <is>
-          <t>该物品不是装备</t>
+          <t>物品不存在</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="0" t="inlineStr">
         <is>
-          <t>EquipLevelNotEnough</t>
+          <t>EquipNotEquipment</t>
         </is>
       </c>
       <c r="B338" s="0" t="inlineStr">
         <is>
-          <t>等级不足,无法装备</t>
+          <t>该物品不是装备</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" s="0" t="inlineStr">
         <is>
-          <t>EquipClassMismatch</t>
+          <t>EquipLevelNotEnough</t>
         </is>
       </c>
       <c r="B339" s="0" t="inlineStr">
         <is>
-          <t>职业不符,无法装备</t>
+          <t>等级不足,无法装备</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" s="0" t="inlineStr">
         <is>
-          <t>EquipNoSlot</t>
+          <t>EquipClassMismatch</t>
         </is>
       </c>
       <c r="B340" s="0" t="inlineStr">
         <is>
-          <t>没有可用的装备栏位</t>
+          <t>职业不符,无法装备</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" s="0" t="inlineStr">
         <is>
-          <t>EquipNotEquipped</t>
+          <t>EquipNoSlot</t>
         </is>
       </c>
       <c r="B341" s="0" t="inlineStr">
         <is>
-          <t>该装备未穿戴</t>
+          <t>没有可用的装备栏位</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="0" t="inlineStr">
         <is>
-          <t>EquipBagFull</t>
+          <t>EquipNotEquipped</t>
         </is>
       </c>
       <c r="B342" s="0" t="inlineStr">
         <is>
-          <t>背包已满,无法卸下</t>
+          <t>该装备未穿戴</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" s="0" t="inlineStr">
         <is>
-          <t>EquipInBattle</t>
+          <t>EquipBagFull</t>
         </is>
       </c>
       <c r="B343" s="0" t="inlineStr">
         <is>
-          <t>战斗中无法更换装备</t>
+          <t>背包已满,无法卸下</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" s="0" t="inlineStr">
         <is>
-          <t>EquipFrozen</t>
+          <t>EquipInBattle</t>
         </is>
       </c>
       <c r="B344" s="0" t="inlineStr">
         <is>
-          <t>当前状态无法更换装备</t>
+          <t>战斗中无法更换装备</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" s="0" t="inlineStr">
         <is>
-          <t>EquipGrantInvalid</t>
+          <t>EquipFrozen</t>
         </is>
       </c>
       <c r="B345" s="0" t="inlineStr">
         <is>
-          <t>发放参数无效</t>
+          <t>当前状态无法更换装备</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" s="0" t="inlineStr">
         <is>
-          <t>EquipInternalError</t>
+          <t>EquipGrantInvalid</t>
         </is>
       </c>
       <c r="B346" s="0" t="inlineStr">
         <is>
-          <t>装备操作失败,请稍后再试</t>
-        </is>
-      </c>
-      <c r="C346" s="0" t="n">
-        <v>1</v>
+          <t>发放参数无效</t>
+        </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" s="0" t="inlineStr">
         <is>
-          <t>EquipEnhanceUnavailable</t>
+          <t>EquipInternalError</t>
         </is>
       </c>
       <c r="B347" s="0" t="inlineStr">
         <is>
-          <t>该装备无法强化</t>
-        </is>
+          <t>装备操作失败,请稍后再试</t>
+        </is>
+      </c>
+      <c r="C347" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" s="0" t="inlineStr">
         <is>
-          <t>EquipEnhanceMaxLevel</t>
+          <t>EquipEnhanceUnavailable</t>
         </is>
       </c>
       <c r="B348" s="0" t="inlineStr">
         <is>
-          <t>已强化到最高等级</t>
+          <t>该装备无法强化</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" s="0" t="inlineStr">
         <is>
-          <t>EquipEnhanceMaterialNotEnough</t>
+          <t>EquipEnhanceMaxLevel</t>
         </is>
       </c>
       <c r="B349" s="0" t="inlineStr">
         <is>
-          <t>强化材料不足</t>
+          <t>已强化到最高等级</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" s="0" t="inlineStr">
         <is>
-          <t>EquipEnhanceGoldNotEnough</t>
+          <t>EquipEnhanceMaterialNotEnough</t>
         </is>
       </c>
       <c r="B350" s="0" t="inlineStr">
         <is>
-          <t>金币不足,无法强化</t>
+          <t>强化材料不足</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" s="0" t="inlineStr">
         <is>
-          <t>EquipGemNotGem</t>
+          <t>EquipEnhanceGoldNotEnough</t>
         </is>
       </c>
       <c r="B351" s="0" t="inlineStr">
         <is>
-          <t>该物品不是宝石</t>
+          <t>金币不足,无法强化</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" s="0" t="inlineStr">
         <is>
-          <t>EquipGemNotOwned</t>
+          <t>EquipGemNotGem</t>
         </is>
       </c>
       <c r="B352" s="0" t="inlineStr">
         <is>
-          <t>背包里没有这颗宝石</t>
+          <t>该物品不是宝石</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" s="0" t="inlineStr">
         <is>
-          <t>EquipGemSocketInvalid</t>
+          <t>EquipGemNotOwned</t>
         </is>
       </c>
       <c r="B353" s="0" t="inlineStr">
         <is>
-          <t>该装备没有这个宝石孔</t>
+          <t>背包里没有这颗宝石</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" s="0" t="inlineStr">
         <is>
-          <t>EquipGemSocketOccupied</t>
+          <t>EquipGemSocketInvalid</t>
         </is>
       </c>
       <c r="B354" s="0" t="inlineStr">
         <is>
-          <t>该孔位已镶有宝石,请先取下</t>
+          <t>该装备没有这个宝石孔</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" s="0" t="inlineStr">
         <is>
-          <t>EquipGemSocketEmpty</t>
+          <t>EquipGemSocketOccupied</t>
         </is>
       </c>
       <c r="B355" s="0" t="inlineStr">
         <is>
-          <t>该孔位没有宝石</t>
+          <t>该孔位已镶有宝石,请先取下</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" s="0" t="inlineStr">
         <is>
-          <t>EquipGemTypeMismatch</t>
+          <t>EquipGemSocketEmpty</t>
         </is>
       </c>
       <c r="B356" s="0" t="inlineStr">
         <is>
-          <t>宝石类型与孔位不符</t>
+          <t>该孔位没有宝石</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" s="0" t="inlineStr">
         <is>
+          <t>EquipGemTypeMismatch</t>
+        </is>
+      </c>
+      <c r="B357" s="0" t="inlineStr">
+        <is>
+          <t>宝石类型与孔位不符</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="0" t="inlineStr">
+        <is>
           <t>EquipGemBagFull</t>
         </is>
       </c>
-      <c r="B357" s="0" t="inlineStr">
+      <c r="B358" s="0" t="inlineStr">
         <is>
           <t>背包已满,无法取下宝石</t>
         </is>
       </c>
     </row>
-    <row r="358"/>
-    <row r="359">
-      <c r="A359" s="0" t="inlineStr">
-        <is>
-          <t>//player_inbox_error base=29000 width=1000</t>
-        </is>
-      </c>
-    </row>
+    <row r="359"/>
     <row r="360">
       <c r="A360" s="0" t="inlineStr">
         <is>
-          <t>PlayerInboxDisabled</t>
-        </is>
-      </c>
-      <c r="B360" s="0" t="inlineStr">
-        <is>
-          <t>该类收件箱消息暂未开放</t>
+          <t>//player_inbox_error base=29000 width=1000</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" s="0" t="inlineStr">
         <is>
-          <t>PlayerInboxUnknownType</t>
+          <t>PlayerInboxDisabled</t>
         </is>
       </c>
       <c r="B361" s="0" t="inlineStr">
         <is>
-          <t>未知的收件箱消息类型</t>
+          <t>该类收件箱消息暂未开放</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" s="0" t="inlineStr">
         <is>
-          <t>PlayerInboxPlayerNotFound</t>
+          <t>PlayerInboxUnknownType</t>
         </is>
       </c>
       <c r="B362" s="0" t="inlineStr">
         <is>
-          <t>玩家不存在</t>
+          <t>未知的收件箱消息类型</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" s="0" t="inlineStr">
         <is>
-          <t>PlayerInboxPayloadInvalid</t>
+          <t>PlayerInboxPlayerNotFound</t>
         </is>
       </c>
       <c r="B363" s="0" t="inlineStr">
         <is>
-          <t>收件箱消息内容无效</t>
+          <t>玩家不存在</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" s="0" t="inlineStr">
         <is>
-          <t>PlayerInboxPayloadTooLarge</t>
+          <t>PlayerInboxPayloadInvalid</t>
         </is>
       </c>
       <c r="B364" s="0" t="inlineStr">
         <is>
-          <t>收件箱消息内容过大</t>
+          <t>收件箱消息内容无效</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" s="0" t="inlineStr">
         <is>
-          <t>PlayerInboxTextTooLong</t>
+          <t>PlayerInboxPayloadTooLarge</t>
         </is>
       </c>
       <c r="B365" s="0" t="inlineStr">
         <is>
-          <t>操作人、理由或备注过长</t>
+          <t>收件箱消息内容过大</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" s="0" t="inlineStr">
         <is>
-          <t>PlayerInboxIssuedOutOfWindow</t>
+          <t>PlayerInboxTextTooLong</t>
         </is>
       </c>
       <c r="B366" s="0" t="inlineStr">
         <is>
-          <t>签发时间超出允许范围</t>
+          <t>操作人、理由或备注过长</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" s="0" t="inlineStr">
         <is>
-          <t>PlayerInboxFull</t>
+          <t>PlayerInboxIssuedOutOfWindow</t>
         </is>
       </c>
       <c r="B367" s="0" t="inlineStr">
         <is>
-          <t>该玩家的收件箱已满</t>
+          <t>签发时间超出允许范围</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" s="0" t="inlineStr">
         <is>
-          <t>PlayerInboxIdempotencyConflict</t>
+          <t>PlayerInboxFull</t>
         </is>
       </c>
       <c r="B368" s="0" t="inlineStr">
         <is>
-          <t>请求号已被不同内容使用</t>
+          <t>该玩家的收件箱已满</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" s="0" t="inlineStr">
         <is>
-          <t>PlayerInboxStaleOwner</t>
+          <t>PlayerInboxIdempotencyConflict</t>
         </is>
       </c>
       <c r="B369" s="0" t="inlineStr">
         <is>
-          <t>场景归属已过期</t>
+          <t>请求号已被不同内容使用</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" s="0" t="inlineStr">
         <is>
-          <t>PlayerInboxEpochRequired</t>
+          <t>PlayerInboxStaleOwner</t>
         </is>
       </c>
       <c r="B370" s="0" t="inlineStr">
         <is>
-          <t>缺少场景归属代际</t>
+          <t>场景归属已过期</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" s="0" t="inlineStr">
         <is>
-          <t>PlayerInboxEpochAhead</t>
+          <t>PlayerInboxEpochRequired</t>
         </is>
       </c>
       <c r="B371" s="0" t="inlineStr">
         <is>
-          <t>场景归属代际超前</t>
+          <t>缺少场景归属代际</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" s="0" t="inlineStr">
         <is>
-          <t>PlayerInboxItemNotFound</t>
+          <t>PlayerInboxEpochAhead</t>
         </is>
       </c>
       <c r="B372" s="0" t="inlineStr">
         <is>
-          <t>收件箱条目不存在</t>
+          <t>场景归属代际超前</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" s="0" t="inlineStr">
         <is>
-          <t>PlayerInboxItemStateConflict</t>
+          <t>PlayerInboxItemNotFound</t>
         </is>
       </c>
       <c r="B373" s="0" t="inlineStr">
         <is>
-          <t>收件箱条目当前状态不允许该操作</t>
+          <t>收件箱条目不存在</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" s="0" t="inlineStr">
         <is>
-          <t>PlayerInboxStoreUnavailable</t>
+          <t>PlayerInboxItemStateConflict</t>
         </is>
       </c>
       <c r="B374" s="0" t="inlineStr">
         <is>
-          <t>收件箱服务暂不可用,请稍后再试</t>
-        </is>
-      </c>
-      <c r="C374" s="0" t="n">
-        <v>1</v>
+          <t>收件箱条目当前状态不允许该操作</t>
+        </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" s="0" t="inlineStr">
         <is>
-          <t>//mail_error base=17000 width=1000</t>
-        </is>
+          <t>PlayerInboxStoreUnavailable</t>
+        </is>
+      </c>
+      <c r="B375" s="0" t="inlineStr">
+        <is>
+          <t>收件箱服务暂不可用,请稍后再试</t>
+        </is>
+      </c>
+      <c r="C375" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" s="0" t="inlineStr">
         <is>
-          <t>MailNotFound</t>
-        </is>
-      </c>
-      <c r="B376" s="0" t="inlineStr">
-        <is>
-          <t>邮件不存在或已删除</t>
+          <t>//mail_error base=17000 width=1000</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" s="0" t="inlineStr">
         <is>
-          <t>MailExpired</t>
+          <t>MailNotFound</t>
         </is>
       </c>
       <c r="B377" s="0" t="inlineStr">
         <is>
-          <t>邮件已过期</t>
+          <t>邮件不存在或已删除</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" s="0" t="inlineStr">
         <is>
-          <t>MailRecipientBoxFull</t>
+          <t>MailExpired</t>
         </is>
       </c>
       <c r="B378" s="0" t="inlineStr">
         <is>
-          <t>收件人邮箱已满</t>
+          <t>邮件已过期</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" s="0" t="inlineStr">
         <is>
-          <t>MailAttachmentInvalid</t>
+          <t>MailRecipientBoxFull</t>
         </is>
       </c>
       <c r="B379" s="0" t="inlineStr">
         <is>
-          <t>邮件附件不合法</t>
+          <t>收件人邮箱已满</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" s="0" t="inlineStr">
         <is>
-          <t>MailRequestConflict</t>
+          <t>MailAttachmentInvalid</t>
         </is>
       </c>
       <c r="B380" s="0" t="inlineStr">
         <is>
-          <t>发件请求编号重复但内容不同</t>
+          <t>邮件附件不合法</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" s="0" t="inlineStr">
         <is>
-          <t>MailSystemMailLimit</t>
+          <t>MailRequestConflict</t>
         </is>
       </c>
       <c r="B381" s="0" t="inlineStr">
         <is>
-          <t>有效系统邮件数量已达上限</t>
+          <t>发件请求编号重复但内容不同</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" s="0" t="inlineStr">
         <is>
-          <t>MailClaimPending</t>
+          <t>MailSystemMailLimit</t>
         </is>
       </c>
       <c r="B382" s="0" t="inlineStr">
         <is>
-          <t>附件正在到账，请稍后刷新</t>
+          <t>有效系统邮件数量已达上限</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" s="0" t="inlineStr">
         <is>
-          <t>MailClaimManual</t>
+          <t>MailClaimPending</t>
         </is>
       </c>
       <c r="B383" s="0" t="inlineStr">
         <is>
-          <t>附件到账需人工核对</t>
+          <t>附件正在到账，请稍后刷新</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" s="0" t="inlineStr">
         <is>
-          <t>MailAttachmentProtected</t>
+          <t>MailClaimManual</t>
         </is>
       </c>
       <c r="B384" s="0" t="inlineStr">
         <is>
-          <t>该邮件仍有待处理附件，暂不能删除</t>
+          <t>附件到账需人工核对</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" s="0" t="inlineStr">
         <is>
-          <t>MailClaimNotOpen</t>
+          <t>MailAttachmentProtected</t>
         </is>
       </c>
       <c r="B385" s="0" t="inlineStr">
         <is>
-          <t>附件领取暂未开放</t>
+          <t>该邮件仍有待处理附件，暂不能删除</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" s="0" t="inlineStr">
         <is>
+          <t>MailClaimNotOpen</t>
+        </is>
+      </c>
+      <c r="B386" s="0" t="inlineStr">
+        <is>
+          <t>附件领取暂未开放</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="0" t="inlineStr">
+        <is>
           <t>MailAttachmentNotOpen</t>
         </is>
       </c>
-      <c r="B386" s="0" t="inlineStr">
+      <c r="B387" s="0" t="inlineStr">
         <is>
           <t>当前环境不允许发送带附件的邮件</t>
         </is>
       </c>
     </row>
-    <row r="387">
-      <c r="A387" s="0" t="n"/>
-      <c r="B387" s="0" t="n"/>
-    </row>
     <row r="388">
-      <c r="A388" s="0" t="inlineStr">
-        <is>
-          <t>//rank_error base=21000 width=1000</t>
-        </is>
-      </c>
+      <c r="A388" s="0" t="n"/>
       <c r="B388" s="0" t="n"/>
     </row>
     <row r="389">
       <c r="A389" s="0" t="inlineStr">
         <is>
-          <t>RankBoardNotFound</t>
-        </is>
-      </c>
-      <c r="B389" s="0" t="inlineStr">
-        <is>
-          <t>排行榜不存在</t>
-        </is>
-      </c>
+          <t>//rank_error base=21000 width=1000</t>
+        </is>
+      </c>
+      <c r="B389" s="0" t="n"/>
     </row>
     <row r="390">
       <c r="A390" s="0" t="inlineStr">
         <is>
-          <t>RankGenerationClosed</t>
+          <t>RankBoardNotFound</t>
         </is>
       </c>
       <c r="B390" s="0" t="inlineStr">
         <is>
-          <t>排行榜本期已封榜</t>
+          <t>排行榜不存在</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" s="0" t="inlineStr">
         <is>
-          <t>RankRequestConflict</t>
+          <t>RankGenerationClosed</t>
         </is>
       </c>
       <c r="B391" s="0" t="inlineStr">
         <is>
-          <t>排行榜请求编号重复但内容不同</t>
+          <t>排行榜本期已封榜</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" s="0" t="inlineStr">
         <is>
+          <t>RankRequestConflict</t>
+        </is>
+      </c>
+      <c r="B392" s="0" t="inlineStr">
+        <is>
+          <t>排行榜请求编号重复但内容不同</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="0" t="inlineStr">
+        <is>
           <t>RankSettlementPending</t>
         </is>
       </c>
-      <c r="B392" s="0" t="inlineStr">
+      <c r="B393" s="0" t="inlineStr">
         <is>
           <t>排行榜结算处理中</t>
         </is>
       </c>
     </row>
-    <row r="393"/>
-    <row r="394">
-      <c r="A394" s="0" t="inlineStr">
-        <is>
-          <t>//mystery_merchant_error base=30000 width=1000</t>
-        </is>
-      </c>
-      <c r="B394" s="0" t="n"/>
-    </row>
+    <row r="394"/>
     <row r="395">
       <c r="A395" s="0" t="inlineStr">
         <is>
-          <t>MysteryMerchantNotPresent</t>
-        </is>
-      </c>
-      <c r="B395" s="0" t="inlineStr">
-        <is>
-          <t>神秘商人现在不在,请留意下次出现的公告</t>
-        </is>
-      </c>
+          <t>//mystery_merchant_error base=30000 width=1000</t>
+        </is>
+      </c>
+      <c r="B395" s="0" t="n"/>
     </row>
     <row r="396">
       <c r="A396" s="0" t="inlineStr">
         <is>
-          <t>MysteryMerchantNotHere</t>
+          <t>MysteryMerchantNotPresent</t>
         </is>
       </c>
       <c r="B396" s="0" t="inlineStr">
         <is>
-          <t>神秘商人不在这条线上</t>
+          <t>神秘商人现在不在,请留意下次出现的公告</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" s="0" t="inlineStr">
         <is>
-          <t>MysteryMerchantTooFar</t>
+          <t>MysteryMerchantNotHere</t>
         </is>
       </c>
       <c r="B397" s="0" t="inlineStr">
         <is>
-          <t>离神秘商人太远了,走近一些再买</t>
+          <t>神秘商人不在这条线上</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" s="0" t="inlineStr">
         <is>
-          <t>MysteryMerchantShelfChanged</t>
+          <t>MysteryMerchantTooFar</t>
         </is>
       </c>
       <c r="B398" s="0" t="inlineStr">
         <is>
-          <t>货架已经更新,请重新查看</t>
+          <t>离神秘商人太远了,走近一些再买</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" s="0" t="inlineStr">
         <is>
-          <t>MysteryMerchantLimitReached</t>
+          <t>MysteryMerchantShelfChanged</t>
         </is>
       </c>
       <c r="B399" s="0" t="inlineStr">
         <is>
-          <t>这件商品本轮已达限购数量</t>
+          <t>货架已经更新,请重新查看</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" s="0" t="inlineStr">
         <is>
-          <t>MysteryMerchantCurrencyNotEnough</t>
+          <t>MysteryMerchantLimitReached</t>
         </is>
       </c>
       <c r="B400" s="0" t="inlineStr">
         <is>
-          <t>货币不足,无法购买</t>
+          <t>这件商品本轮已达限购数量</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" s="0" t="inlineStr">
         <is>
-          <t>MysteryMerchantBagFull</t>
+          <t>MysteryMerchantCurrencyNotEnough</t>
         </is>
       </c>
       <c r="B401" s="0" t="inlineStr">
         <is>
-          <t>背包已满,无法购买</t>
+          <t>货币不足,无法购买</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" s="0" t="inlineStr">
         <is>
-          <t>MysteryMerchantInBattle</t>
+          <t>MysteryMerchantBagFull</t>
         </is>
       </c>
       <c r="B402" s="0" t="inlineStr">
         <is>
-          <t>战斗中不能购买</t>
+          <t>背包已满,无法购买</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" s="0" t="inlineStr">
         <is>
-          <t>MysteryMerchantFrozen</t>
+          <t>MysteryMerchantInBattle</t>
         </is>
       </c>
       <c r="B403" s="0" t="inlineStr">
         <is>
-          <t>角色正在跨区传送,暂时不能购买</t>
+          <t>战斗中不能购买</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" s="0" t="inlineStr">
         <is>
-          <t>MysteryMerchantInvalidCount</t>
+          <t>MysteryMerchantFrozen</t>
         </is>
       </c>
       <c r="B404" s="0" t="inlineStr">
         <is>
-          <t>购买数量无效</t>
+          <t>角色正在跨区传送,暂时不能购买</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" s="0" t="inlineStr">
         <is>
-          <t>MysteryMerchantItemBlocked</t>
+          <t>MysteryMerchantInvalidCount</t>
         </is>
       </c>
       <c r="B405" s="0" t="inlineStr">
         <is>
-          <t>这件商品暂时无法购买</t>
+          <t>购买数量无效</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" s="0" t="inlineStr">
         <is>
+          <t>MysteryMerchantItemBlocked</t>
+        </is>
+      </c>
+      <c r="B406" s="0" t="inlineStr">
+        <is>
+          <t>这件商品暂时无法购买</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="0" t="inlineStr">
+        <is>
           <t>MysteryMerchantInternalError</t>
         </is>
       </c>
-      <c r="B406" s="0" t="inlineStr">
+      <c r="B407" s="0" t="inlineStr">
         <is>
           <t>神秘商人暂时无法交易,请稍后再试</t>
         </is>
       </c>
-      <c r="C406" t="n">
+      <c r="C407" s="0" t="n">
         <v>1</v>
       </c>
     </row>
